--- a/content/assessment-packages/TEMPLATE/sonartra_report_first_fully_authored_import_TEMPLATE.xlsx
+++ b/content/assessment-packages/TEMPLATE/sonartra_report_first_fully_authored_import_TEMPLATE.xlsx
@@ -76,7 +76,7 @@
   <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -84,27 +84,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF16352E"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -119,9 +105,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -451,82 +436,3880 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="UTF-8" standalone="yes"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"><dimension ref="A1:L2"/><cols><col min="1" max="1" width="18.83203125" customWidth="1"/><col min="2" max="2" width="14.83203125" customWidth="1"/><col min="3" max="3" width="20.83203125" customWidth="1"/><col min="4" max="4" width="26.83203125" customWidth="1"/><col min="5" max="5" width="14.83203125" customWidth="1"/><col min="6" max="6" width="14.83203125" customWidth="1"/><col min="7" max="7" width="14.83203125" customWidth="1"/><col min="8" max="8" width="16.83203125" customWidth="1"/><col min="9" max="9" width="20.83203125" customWidth="1"/><col min="10" max="10" width="14.83203125" customWidth="1"/><col min="11" max="11" width="14.83203125" customWidth="1"/><col min="12" max="12" width="20.83203125" customWidth="1"/></cols><sheetData><row r="1"><c r="A1" s="1" s="1" t="str"><v>assessment_key</v></c><c r="B1" s="1" s="1" t="str"><v>version</v></c><c r="C1" s="1" s="1" t="str"><v>assessment_title</v></c><c r="D1" s="1" s="1" t="str"><v>assessment_description</v></c><c r="E1" s="1" s="1" t="str"><v>model</v></c><c r="F1" s="1" s="1" t="str"><v>mode</v></c><c r="G1" s="1" s="1" t="str"><v>domain_key</v></c><c r="H1" s="1" s="1" t="str"><v>domain_title</v></c><c r="I1" s="1" s="1" t="str"><v>lifecycle_status</v></c><c r="J1" s="1" s="1" t="str"><v>status</v></c><c r="K1" s="1" s="1" t="str"><v>lookup_key</v></c><c r="L1" s="1" s="1" t="str"><v>result_model_key</v></c></row><row r="2"><c r="A2" t="str"><v>{{assessment_key}}</v></c><c r="B2" t="str"><v>{{version}}</v></c><c r="C2" t="str"><v>{{assessment_title}}</v></c><c r="D2" t="str"><v>{{user_facing_assessment_description}}</v></c><c r="E2" t="str"><v>ranked_pattern</v></c><c r="F2" t="str"><v>single_domain</v></c><c r="G2" t="str"><v>{{domain_key}}</v></c><c r="H2" t="str"><v>{{domain_title}}</v></c><c r="I2" t="str"><v>DRAFT</v></c><c r="J2" t="str"><v>active</v></c><c r="K2" t="str"><v>metadata::{{assessment_key}}::{{version}}</v></c><c r="L2" t="str"><v>ranked_pattern</v></c></row></sheetData><autoFilter ref="A1:L2"/><ignoredErrors><ignoredError numberStoredAsText="1" sqref="A1:L2"/></ignoredErrors></worksheet>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L2"/>
+  <cols>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" customWidth="1"/>
+    <col min="4" max="4" width="26.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="16.83203125" customWidth="1"/>
+    <col min="9" max="9" width="20.83203125" customWidth="1"/>
+    <col min="10" max="10" width="14.83203125" customWidth="1"/>
+    <col min="11" max="11" width="14.83203125" customWidth="1"/>
+    <col min="12" max="12" width="20.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>assessment_key</v>
+      </c>
+      <c r="B1" t="str">
+        <v>version</v>
+      </c>
+      <c r="C1" t="str">
+        <v>assessment_title</v>
+      </c>
+      <c r="D1" t="str">
+        <v>assessment_description</v>
+      </c>
+      <c r="E1" t="str">
+        <v>model</v>
+      </c>
+      <c r="F1" t="str">
+        <v>mode</v>
+      </c>
+      <c r="G1" t="str">
+        <v>domain_key</v>
+      </c>
+      <c r="H1" t="str">
+        <v>domain_title</v>
+      </c>
+      <c r="I1" t="str">
+        <v>lifecycle_status</v>
+      </c>
+      <c r="J1" t="str">
+        <v>status</v>
+      </c>
+      <c r="K1" t="str">
+        <v>lookup_key</v>
+      </c>
+      <c r="L1" t="str">
+        <v>result_model_key</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>{{assessment_key}}</v>
+      </c>
+      <c r="B2" t="str">
+        <v>{{version}}</v>
+      </c>
+      <c r="C2" t="str">
+        <v>{{assessment_title}}</v>
+      </c>
+      <c r="D2" t="str">
+        <v>{{user_facing_assessment_description}}</v>
+      </c>
+      <c r="E2" t="str">
+        <v>ranked_pattern</v>
+      </c>
+      <c r="F2" t="str">
+        <v>single_domain</v>
+      </c>
+      <c r="G2" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="H2" t="str">
+        <v>{{domain_title}}</v>
+      </c>
+      <c r="I2" t="str">
+        <v>DRAFT</v>
+      </c>
+      <c r="J2" t="str">
+        <v>active</v>
+      </c>
+      <c r="K2" t="str">
+        <v>metadata::{{assessment_key}}::{{version}}</v>
+      </c>
+      <c r="L2" t="str">
+        <v>ranked_pattern</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:L2"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+  </ignoredErrors>
+</worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="UTF-8" standalone="yes"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"><dimension ref="A1:M1"/><cols><col min="1" max="1" width="14.83203125" customWidth="1"/><col min="2" max="2" width="15.83203125" customWidth="1"/><col min="3" max="3" width="15.83203125" customWidth="1"/><col min="4" max="4" width="21.83203125" customWidth="1"/><col min="5" max="5" width="21.83203125" customWidth="1"/><col min="6" max="6" width="21.83203125" customWidth="1"/><col min="7" max="7" width="21.83203125" customWidth="1"/><col min="8" max="8" width="19.83203125" customWidth="1"/><col min="9" max="9" width="18.83203125" customWidth="1"/><col min="10" max="10" width="19.83203125" customWidth="1"/><col min="11" max="11" width="20.83203125" customWidth="1"/><col min="12" max="12" width="14.83203125" customWidth="1"/><col min="13" max="13" width="14.83203125" customWidth="1"/></cols><sheetData><row r="1"><c r="A1" s="1" s="1" t="str"><v>domain_key</v></c><c r="B1" s="1" s="1" t="str"><v>pattern_key</v></c><c r="C1" s="1" s="1" t="str"><v>score_shape</v></c><c r="D1" s="1" s="1" t="str"><v>rank_1_signal_key</v></c><c r="E1" s="1" s="1" t="str"><v>rank_2_signal_key</v></c><c r="F1" s="1" s="1" t="str"><v>rank_3_signal_key</v></c><c r="G1" s="1" s="1" t="str"><v>rank_4_signal_key</v></c><c r="H1" s="1" s="1" t="str"><v>mechanics_title</v></c><c r="I1" s="1" s="1" t="str"><v>core_mechanism</v></c><c r="J1" s="1" s="1" t="str"><v>why_it_shows_up</v></c><c r="K1" s="1" s="1" t="str"><v>what_it_protects</v></c><c r="L1" s="1" s="1" t="str"><v>status</v></c><c r="M1" s="1" s="1" t="str"><v>lookup_key</v></c></row></sheetData><autoFilter ref="A1:M1"/><ignoredErrors><ignoredError numberStoredAsText="1" sqref="A1:M1"/></ignoredErrors></worksheet>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M1"/>
+  <cols>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="21.83203125" customWidth="1"/>
+    <col min="5" max="5" width="21.83203125" customWidth="1"/>
+    <col min="6" max="6" width="21.83203125" customWidth="1"/>
+    <col min="7" max="7" width="21.83203125" customWidth="1"/>
+    <col min="8" max="8" width="19.83203125" customWidth="1"/>
+    <col min="9" max="9" width="18.83203125" customWidth="1"/>
+    <col min="10" max="10" width="19.83203125" customWidth="1"/>
+    <col min="11" max="11" width="20.83203125" customWidth="1"/>
+    <col min="12" max="12" width="14.83203125" customWidth="1"/>
+    <col min="13" max="13" width="14.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>domain_key</v>
+      </c>
+      <c r="B1" t="str">
+        <v>pattern_key</v>
+      </c>
+      <c r="C1" t="str">
+        <v>score_shape</v>
+      </c>
+      <c r="D1" t="str">
+        <v>rank_1_signal_key</v>
+      </c>
+      <c r="E1" t="str">
+        <v>rank_2_signal_key</v>
+      </c>
+      <c r="F1" t="str">
+        <v>rank_3_signal_key</v>
+      </c>
+      <c r="G1" t="str">
+        <v>rank_4_signal_key</v>
+      </c>
+      <c r="H1" t="str">
+        <v>mechanics_title</v>
+      </c>
+      <c r="I1" t="str">
+        <v>core_mechanism</v>
+      </c>
+      <c r="J1" t="str">
+        <v>why_it_shows_up</v>
+      </c>
+      <c r="K1" t="str">
+        <v>what_it_protects</v>
+      </c>
+      <c r="L1" t="str">
+        <v>status</v>
+      </c>
+      <c r="M1" t="str">
+        <v>lookup_key</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:M1"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:M1"/>
+  </ignoredErrors>
+</worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="UTF-8" standalone="yes"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"><dimension ref="A1:N1"/><cols><col min="1" max="1" width="14.83203125" customWidth="1"/><col min="2" max="2" width="15.83203125" customWidth="1"/><col min="3" max="3" width="15.83203125" customWidth="1"/><col min="4" max="4" width="21.83203125" customWidth="1"/><col min="5" max="5" width="21.83203125" customWidth="1"/><col min="6" max="6" width="21.83203125" customWidth="1"/><col min="7" max="7" width="21.83203125" customWidth="1"/><col min="8" max="8" width="19.83203125" customWidth="1"/><col min="9" max="9" width="14.83203125" customWidth="1"/><col min="10" max="10" width="14.83203125" customWidth="1"/><col min="11" max="11" width="14.83203125" customWidth="1"/><col min="12" max="12" width="18.83203125" customWidth="1"/><col min="13" max="13" width="14.83203125" customWidth="1"/><col min="14" max="14" width="14.83203125" customWidth="1"/></cols><sheetData><row r="1"><c r="A1" s="1" s="1" t="str"><v>domain_key</v></c><c r="B1" s="1" s="1" t="str"><v>pattern_key</v></c><c r="C1" s="1" s="1" t="str"><v>score_shape</v></c><c r="D1" s="1" s="1" t="str"><v>rank_1_signal_key</v></c><c r="E1" s="1" s="1" t="str"><v>rank_2_signal_key</v></c><c r="F1" s="1" s="1" t="str"><v>rank_3_signal_key</v></c><c r="G1" s="1" s="1" t="str"><v>rank_4_signal_key</v></c><c r="H1" s="1" s="1" t="str"><v>synthesis_title</v></c><c r="I1" s="1" s="1" t="str"><v>gift</v></c><c r="J1" s="1" s="1" t="str"><v>trap</v></c><c r="K1" s="1" s="1" t="str"><v>takeaway</v></c><c r="L1" s="1" s="1" t="str"><v>synthesis_text</v></c><c r="M1" s="1" s="1" t="str"><v>status</v></c><c r="N1" s="1" s="1" t="str"><v>lookup_key</v></c></row></sheetData><autoFilter ref="A1:N1"/><ignoredErrors><ignoredError numberStoredAsText="1" sqref="A1:N1"/></ignoredErrors></worksheet>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:N1"/>
+  <cols>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="21.83203125" customWidth="1"/>
+    <col min="5" max="5" width="21.83203125" customWidth="1"/>
+    <col min="6" max="6" width="21.83203125" customWidth="1"/>
+    <col min="7" max="7" width="21.83203125" customWidth="1"/>
+    <col min="8" max="8" width="19.83203125" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" customWidth="1"/>
+    <col min="10" max="10" width="14.83203125" customWidth="1"/>
+    <col min="11" max="11" width="14.83203125" customWidth="1"/>
+    <col min="12" max="12" width="18.83203125" customWidth="1"/>
+    <col min="13" max="13" width="14.83203125" customWidth="1"/>
+    <col min="14" max="14" width="14.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>domain_key</v>
+      </c>
+      <c r="B1" t="str">
+        <v>pattern_key</v>
+      </c>
+      <c r="C1" t="str">
+        <v>score_shape</v>
+      </c>
+      <c r="D1" t="str">
+        <v>rank_1_signal_key</v>
+      </c>
+      <c r="E1" t="str">
+        <v>rank_2_signal_key</v>
+      </c>
+      <c r="F1" t="str">
+        <v>rank_3_signal_key</v>
+      </c>
+      <c r="G1" t="str">
+        <v>rank_4_signal_key</v>
+      </c>
+      <c r="H1" t="str">
+        <v>synthesis_title</v>
+      </c>
+      <c r="I1" t="str">
+        <v>gift</v>
+      </c>
+      <c r="J1" t="str">
+        <v>trap</v>
+      </c>
+      <c r="K1" t="str">
+        <v>takeaway</v>
+      </c>
+      <c r="L1" t="str">
+        <v>synthesis_text</v>
+      </c>
+      <c r="M1" t="str">
+        <v>status</v>
+      </c>
+      <c r="N1" t="str">
+        <v>lookup_key</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:N1"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:N1"/>
+  </ignoredErrors>
+</worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="UTF-8" standalone="yes"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"><dimension ref="A1:I1"/><cols><col min="1" max="1" width="14.83203125" customWidth="1"/><col min="2" max="2" width="15.83203125" customWidth="1"/><col min="3" max="3" width="16.83203125" customWidth="1"/><col min="4" max="4" width="14.83203125" customWidth="1"/><col min="5" max="5" width="18.83203125" customWidth="1"/><col min="6" max="6" width="17.83203125" customWidth="1"/><col min="7" max="7" width="21.83203125" customWidth="1"/><col min="8" max="8" width="14.83203125" customWidth="1"/><col min="9" max="9" width="14.83203125" customWidth="1"/></cols><sheetData><row r="1"><c r="A1" s="1" s="1" t="str"><v>domain_key</v></c><c r="B1" s="1" s="1" t="str"><v>pattern_key</v></c><c r="C1" s="1" s="1" t="str"><v>strength_key</v></c><c r="D1" s="1" s="1" t="str"><v>priority</v></c><c r="E1" s="1" s="1" t="str"><v>strength_title</v></c><c r="F1" s="1" s="1" t="str"><v>strength_text</v></c><c r="G1" s="1" s="1" t="str"><v>linked_signal_key</v></c><c r="H1" s="1" s="1" t="str"><v>status</v></c><c r="I1" s="1" s="1" t="str"><v>lookup_key</v></c></row></sheetData><autoFilter ref="A1:I1"/><ignoredErrors><ignoredError numberStoredAsText="1" sqref="A1:I1"/></ignoredErrors></worksheet>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I1"/>
+  <cols>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" customWidth="1"/>
+    <col min="6" max="6" width="17.83203125" customWidth="1"/>
+    <col min="7" max="7" width="21.83203125" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>domain_key</v>
+      </c>
+      <c r="B1" t="str">
+        <v>pattern_key</v>
+      </c>
+      <c r="C1" t="str">
+        <v>strength_key</v>
+      </c>
+      <c r="D1" t="str">
+        <v>priority</v>
+      </c>
+      <c r="E1" t="str">
+        <v>strength_title</v>
+      </c>
+      <c r="F1" t="str">
+        <v>strength_text</v>
+      </c>
+      <c r="G1" t="str">
+        <v>linked_signal_key</v>
+      </c>
+      <c r="H1" t="str">
+        <v>status</v>
+      </c>
+      <c r="I1" t="str">
+        <v>lookup_key</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I1"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I1"/>
+  </ignoredErrors>
+</worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="UTF-8" standalone="yes"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"><dimension ref="A1:I1"/><cols><col min="1" max="1" width="14.83203125" customWidth="1"/><col min="2" max="2" width="15.83203125" customWidth="1"/><col min="3" max="3" width="17.83203125" customWidth="1"/><col min="4" max="4" width="14.83203125" customWidth="1"/><col min="5" max="5" width="19.83203125" customWidth="1"/><col min="6" max="6" width="18.83203125" customWidth="1"/><col min="7" max="7" width="28.83203125" customWidth="1"/><col min="8" max="8" width="14.83203125" customWidth="1"/><col min="9" max="9" width="14.83203125" customWidth="1"/></cols><sheetData><row r="1"><c r="A1" s="1" s="1" t="str"><v>domain_key</v></c><c r="B1" s="1" s="1" t="str"><v>pattern_key</v></c><c r="C1" s="1" s="1" t="str"><v>narrowing_key</v></c><c r="D1" s="1" s="1" t="str"><v>priority</v></c><c r="E1" s="1" s="1" t="str"><v>narrowing_title</v></c><c r="F1" s="1" s="1" t="str"><v>narrowing_text</v></c><c r="G1" s="1" s="1" t="str"><v>missing_range_signal_key</v></c><c r="H1" s="1" s="1" t="str"><v>status</v></c><c r="I1" s="1" s="1" t="str"><v>lookup_key</v></c></row></sheetData><autoFilter ref="A1:I1"/><ignoredErrors><ignoredError numberStoredAsText="1" sqref="A1:I1"/></ignoredErrors></worksheet>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I1"/>
+  <cols>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" customWidth="1"/>
+    <col min="3" max="3" width="17.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="19.83203125" customWidth="1"/>
+    <col min="6" max="6" width="18.83203125" customWidth="1"/>
+    <col min="7" max="7" width="28.83203125" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>domain_key</v>
+      </c>
+      <c r="B1" t="str">
+        <v>pattern_key</v>
+      </c>
+      <c r="C1" t="str">
+        <v>narrowing_key</v>
+      </c>
+      <c r="D1" t="str">
+        <v>priority</v>
+      </c>
+      <c r="E1" t="str">
+        <v>narrowing_title</v>
+      </c>
+      <c r="F1" t="str">
+        <v>narrowing_text</v>
+      </c>
+      <c r="G1" t="str">
+        <v>missing_range_signal_key</v>
+      </c>
+      <c r="H1" t="str">
+        <v>status</v>
+      </c>
+      <c r="I1" t="str">
+        <v>lookup_key</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I1"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I1"/>
+  </ignoredErrors>
+</worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="UTF-8" standalone="yes"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"><dimension ref="A1:I1"/><cols><col min="1" max="1" width="14.83203125" customWidth="1"/><col min="2" max="2" width="15.83203125" customWidth="1"/><col min="3" max="3" width="19.83203125" customWidth="1"/><col min="4" max="4" width="14.83203125" customWidth="1"/><col min="5" max="5" width="21.83203125" customWidth="1"/><col min="6" max="6" width="20.83203125" customWidth="1"/><col min="7" max="7" width="21.83203125" customWidth="1"/><col min="8" max="8" width="14.83203125" customWidth="1"/><col min="9" max="9" width="14.83203125" customWidth="1"/></cols><sheetData><row r="1"><c r="A1" s="1" s="1" t="str"><v>domain_key</v></c><c r="B1" s="1" s="1" t="str"><v>pattern_key</v></c><c r="C1" s="1" s="1" t="str"><v>application_key</v></c><c r="D1" s="1" s="1" t="str"><v>priority</v></c><c r="E1" s="1" s="1" t="str"><v>application_title</v></c><c r="F1" s="1" s="1" t="str"><v>application_text</v></c><c r="G1" s="1" s="1" t="str"><v>linked_signal_key</v></c><c r="H1" s="1" s="1" t="str"><v>status</v></c><c r="I1" s="1" s="1" t="str"><v>lookup_key</v></c></row></sheetData><autoFilter ref="A1:I1"/><ignoredErrors><ignoredError numberStoredAsText="1" sqref="A1:I1"/></ignoredErrors></worksheet>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I1"/>
+  <cols>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" customWidth="1"/>
+    <col min="3" max="3" width="19.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="21.83203125" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" customWidth="1"/>
+    <col min="7" max="7" width="21.83203125" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>domain_key</v>
+      </c>
+      <c r="B1" t="str">
+        <v>pattern_key</v>
+      </c>
+      <c r="C1" t="str">
+        <v>application_key</v>
+      </c>
+      <c r="D1" t="str">
+        <v>priority</v>
+      </c>
+      <c r="E1" t="str">
+        <v>application_title</v>
+      </c>
+      <c r="F1" t="str">
+        <v>application_text</v>
+      </c>
+      <c r="G1" t="str">
+        <v>linked_signal_key</v>
+      </c>
+      <c r="H1" t="str">
+        <v>status</v>
+      </c>
+      <c r="I1" t="str">
+        <v>lookup_key</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I1"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I1"/>
+  </ignoredErrors>
+</worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="UTF-8" standalone="yes"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"><dimension ref="A1:N1"/><cols><col min="1" max="1" width="14.83203125" customWidth="1"/><col min="2" max="2" width="15.83203125" customWidth="1"/><col min="3" max="3" width="15.83203125" customWidth="1"/><col min="4" max="4" width="19.83203125" customWidth="1"/><col min="5" max="5" width="14.83203125" customWidth="1"/><col min="6" max="6" width="14.83203125" customWidth="1"/><col min="7" max="7" width="20.83203125" customWidth="1"/><col min="8" max="8" width="18.83203125" customWidth="1"/><col min="9" max="9" width="14.83203125" customWidth="1"/><col min="10" max="10" width="14.83203125" customWidth="1"/><col min="11" max="11" width="21.83203125" customWidth="1"/><col min="12" max="12" width="21.83203125" customWidth="1"/><col min="13" max="13" width="21.83203125" customWidth="1"/><col min="14" max="14" width="21.83203125" customWidth="1"/></cols><sheetData><row r="1"><c r="A1" s="1" s="1" t="str"><v>domain_key</v></c><c r="B1" s="1" s="1" t="str"><v>pattern_key</v></c><c r="C1" s="1" s="1" t="str"><v>score_shape</v></c><c r="D1" s="1" s="1" t="str"><v>closing_summary</v></c><c r="E1" s="1" s="1" t="str"><v>core_gift</v></c><c r="F1" s="1" s="1" t="str"><v>core_trap</v></c><c r="G1" s="1" s="1" t="str"><v>development_edge</v></c><c r="H1" s="1" s="1" t="str"><v>memorable_line</v></c><c r="I1" s="1" s="1" t="str"><v>status</v></c><c r="J1" s="1" s="1" t="str"><v>lookup_key</v></c><c r="K1" s="1" s="1" t="str"><v>rank_1_signal_key</v></c><c r="L1" s="1" s="1" t="str"><v>rank_2_signal_key</v></c><c r="M1" s="1" s="1" t="str"><v>rank_3_signal_key</v></c><c r="N1" s="1" s="1" t="str"><v>rank_4_signal_key</v></c></row></sheetData><autoFilter ref="A1:N1"/><ignoredErrors><ignoredError numberStoredAsText="1" sqref="A1:N1"/></ignoredErrors></worksheet>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:N1"/>
+  <cols>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="19.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="20.83203125" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" customWidth="1"/>
+    <col min="10" max="10" width="14.83203125" customWidth="1"/>
+    <col min="11" max="11" width="21.83203125" customWidth="1"/>
+    <col min="12" max="12" width="21.83203125" customWidth="1"/>
+    <col min="13" max="13" width="21.83203125" customWidth="1"/>
+    <col min="14" max="14" width="21.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>domain_key</v>
+      </c>
+      <c r="B1" t="str">
+        <v>pattern_key</v>
+      </c>
+      <c r="C1" t="str">
+        <v>score_shape</v>
+      </c>
+      <c r="D1" t="str">
+        <v>closing_summary</v>
+      </c>
+      <c r="E1" t="str">
+        <v>core_gift</v>
+      </c>
+      <c r="F1" t="str">
+        <v>core_trap</v>
+      </c>
+      <c r="G1" t="str">
+        <v>development_edge</v>
+      </c>
+      <c r="H1" t="str">
+        <v>memorable_line</v>
+      </c>
+      <c r="I1" t="str">
+        <v>status</v>
+      </c>
+      <c r="J1" t="str">
+        <v>lookup_key</v>
+      </c>
+      <c r="K1" t="str">
+        <v>rank_1_signal_key</v>
+      </c>
+      <c r="L1" t="str">
+        <v>rank_2_signal_key</v>
+      </c>
+      <c r="M1" t="str">
+        <v>rank_3_signal_key</v>
+      </c>
+      <c r="N1" t="str">
+        <v>rank_4_signal_key</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:N1"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:N1"/>
+  </ignoredErrors>
+</worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="UTF-8" standalone="yes"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"><dimension ref="A1:Q1"/><cols><col min="1" max="1" width="20.83203125" customWidth="1"/><col min="2" max="2" width="18.83203125" customWidth="1"/><col min="3" max="3" width="14.83203125" customWidth="1"/><col min="4" max="4" width="14.83203125" customWidth="1"/><col min="5" max="5" width="21.83203125" customWidth="1"/><col min="6" max="6" width="21.83203125" customWidth="1"/><col min="7" max="7" width="21.83203125" customWidth="1"/><col min="8" max="8" width="21.83203125" customWidth="1"/><col min="9" max="9" width="32.83203125" customWidth="1"/><col min="10" max="10" width="32.83203125" customWidth="1"/><col min="11" max="11" width="32.83203125" customWidth="1"/><col min="12" max="12" width="32.83203125" customWidth="1"/><col min="13" max="13" width="24.83203125" customWidth="1"/><col min="14" max="14" width="24.83203125" customWidth="1"/><col min="15" max="15" width="29.83203125" customWidth="1"/><col min="16" max="16" width="14.83203125" customWidth="1"/><col min="17" max="17" width="14.83203125" customWidth="1"/></cols><sheetData><row r="1"><c r="A1" s="1" s="1" t="str"><v>preview_case_key</v></c><c r="B1" s="1" s="1" t="str"><v>assessment_key</v></c><c r="C1" s="1" s="1" t="str"><v>version</v></c><c r="D1" s="1" s="1" t="str"><v>domain_key</v></c><c r="E1" s="1" s="1" t="str"><v>rank_1_signal_key</v></c><c r="F1" s="1" s="1" t="str"><v>rank_2_signal_key</v></c><c r="G1" s="1" s="1" t="str"><v>rank_3_signal_key</v></c><c r="H1" s="1" s="1" t="str"><v>rank_4_signal_key</v></c><c r="I1" s="1" s="1" t="str"><v>normalized_rank_1_percentage</v></c><c r="J1" s="1" s="1" t="str"><v>normalized_rank_2_percentage</v></c><c r="K1" s="1" s="1" t="str"><v>normalized_rank_3_percentage</v></c><c r="L1" s="1" s="1" t="str"><v>normalized_rank_4_percentage</v></c><c r="M1" s="1" s="1" t="str"><v>expected_score_shape</v></c><c r="N1" s="1" s="1" t="str"><v>expected_pattern_key</v></c><c r="O1" s="1" s="1" t="str"><v>expected_payload_sections</v></c><c r="P1" s="1" s="1" t="str"><v>status</v></c><c r="Q1" s="1" s="1" t="str"><v>lookup_key</v></c></row></sheetData><autoFilter ref="A1:Q1"/><ignoredErrors><ignoredError numberStoredAsText="1" sqref="A1:Q1"/></ignoredErrors></worksheet>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Q1"/>
+  <cols>
+    <col min="1" max="1" width="20.83203125" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="21.83203125" customWidth="1"/>
+    <col min="6" max="6" width="21.83203125" customWidth="1"/>
+    <col min="7" max="7" width="21.83203125" customWidth="1"/>
+    <col min="8" max="8" width="21.83203125" customWidth="1"/>
+    <col min="9" max="9" width="32.83203125" customWidth="1"/>
+    <col min="10" max="10" width="32.83203125" customWidth="1"/>
+    <col min="11" max="11" width="32.83203125" customWidth="1"/>
+    <col min="12" max="12" width="32.83203125" customWidth="1"/>
+    <col min="13" max="13" width="24.83203125" customWidth="1"/>
+    <col min="14" max="14" width="24.83203125" customWidth="1"/>
+    <col min="15" max="15" width="29.83203125" customWidth="1"/>
+    <col min="16" max="16" width="14.83203125" customWidth="1"/>
+    <col min="17" max="17" width="14.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>preview_case_key</v>
+      </c>
+      <c r="B1" t="str">
+        <v>assessment_key</v>
+      </c>
+      <c r="C1" t="str">
+        <v>version</v>
+      </c>
+      <c r="D1" t="str">
+        <v>domain_key</v>
+      </c>
+      <c r="E1" t="str">
+        <v>rank_1_signal_key</v>
+      </c>
+      <c r="F1" t="str">
+        <v>rank_2_signal_key</v>
+      </c>
+      <c r="G1" t="str">
+        <v>rank_3_signal_key</v>
+      </c>
+      <c r="H1" t="str">
+        <v>rank_4_signal_key</v>
+      </c>
+      <c r="I1" t="str">
+        <v>normalized_rank_1_percentage</v>
+      </c>
+      <c r="J1" t="str">
+        <v>normalized_rank_2_percentage</v>
+      </c>
+      <c r="K1" t="str">
+        <v>normalized_rank_3_percentage</v>
+      </c>
+      <c r="L1" t="str">
+        <v>normalized_rank_4_percentage</v>
+      </c>
+      <c r="M1" t="str">
+        <v>expected_score_shape</v>
+      </c>
+      <c r="N1" t="str">
+        <v>expected_pattern_key</v>
+      </c>
+      <c r="O1" t="str">
+        <v>expected_payload_sections</v>
+      </c>
+      <c r="P1" t="str">
+        <v>status</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>lookup_key</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Q1"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q1"/>
+  </ignoredErrors>
+</worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="UTF-8" standalone="yes"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"><dimension ref="A1:K2"/><cols><col min="1" max="1" width="22.83203125" customWidth="1"/><col min="2" max="2" width="18.83203125" customWidth="1"/><col min="3" max="3" width="14.83203125" customWidth="1"/><col min="4" max="4" width="22.83203125" customWidth="1"/><col min="5" max="5" width="15.83203125" customWidth="1"/><col min="6" max="6" width="32.83203125" customWidth="1"/><col min="7" max="7" width="36.83203125" customWidth="1"/><col min="8" max="8" width="21.83203125" customWidth="1"/><col min="9" max="9" width="20.83203125" customWidth="1"/><col min="10" max="10" width="14.83203125" customWidth="1"/><col min="11" max="11" width="14.83203125" customWidth="1"/></cols><sheetData><row r="1"><c r="A1" s="1" s="1" t="str"><v>import_summary_key</v></c><c r="B1" s="1" s="1" t="str"><v>assessment_key</v></c><c r="C1" s="1" s="1" t="str"><v>version</v></c><c r="D1" s="1" s="1" t="str"><v>package_identifier</v></c><c r="E1" s="1" s="1" t="str"><v>source_name</v></c><c r="F1" s="1" s="1" t="str"><v>runtime_definition_row_count</v></c><c r="G1" s="1" s="1" t="str"><v>runtime_result_content_row_count</v></c><c r="H1" s="1" s="1" t="str"><v>preview_row_count</v></c><c r="I1" s="1" s="1" t="str"><v>validation_notes</v></c><c r="J1" s="1" s="1" t="str"><v>status</v></c><c r="K1" s="1" s="1" t="str"><v>lookup_key</v></c></row><row r="2"><c r="A2" t="str"><v>{{assessment_key}}::{{version}}</v></c><c r="B2" t="str"><v>{{assessment_key}}</v></c><c r="C2" t="str"><v>{{version}}</v></c><c r="D2" t="str"><v>{{package_identifier}}</v></c><c r="E2" t="str"><v>sonartra_report_first_fully_authored_import_TEMPLATE.xlsx</v></c><c r="F2" t="str"><v>{{runtime_definition_row_count}}</v></c><c r="G2" t="str"><v>{{runtime_result_content_row_count}}</v></c><c r="H2" t="str"><v>{{preview_row_count}}</v></c><c r="I2" t="str"><v>{{validation_notes}}</v></c><c r="J2" t="str"><v>draft</v></c><c r="K2" t="str"><v>import_summary::{{assessment_key}}::{{version}}</v></c></row></sheetData><autoFilter ref="A1:K2"/><ignoredErrors><ignoredError numberStoredAsText="1" sqref="A1:K2"/></ignoredErrors></worksheet>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K2"/>
+  <cols>
+    <col min="1" max="1" width="22.83203125" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="22.83203125" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" customWidth="1"/>
+    <col min="6" max="6" width="32.83203125" customWidth="1"/>
+    <col min="7" max="7" width="36.83203125" customWidth="1"/>
+    <col min="8" max="8" width="21.83203125" customWidth="1"/>
+    <col min="9" max="9" width="20.83203125" customWidth="1"/>
+    <col min="10" max="10" width="14.83203125" customWidth="1"/>
+    <col min="11" max="11" width="14.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>import_summary_key</v>
+      </c>
+      <c r="B1" t="str">
+        <v>assessment_key</v>
+      </c>
+      <c r="C1" t="str">
+        <v>version</v>
+      </c>
+      <c r="D1" t="str">
+        <v>package_identifier</v>
+      </c>
+      <c r="E1" t="str">
+        <v>source_name</v>
+      </c>
+      <c r="F1" t="str">
+        <v>runtime_definition_row_count</v>
+      </c>
+      <c r="G1" t="str">
+        <v>runtime_result_content_row_count</v>
+      </c>
+      <c r="H1" t="str">
+        <v>preview_row_count</v>
+      </c>
+      <c r="I1" t="str">
+        <v>validation_notes</v>
+      </c>
+      <c r="J1" t="str">
+        <v>status</v>
+      </c>
+      <c r="K1" t="str">
+        <v>lookup_key</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>{{assessment_key}}::{{version}}</v>
+      </c>
+      <c r="B2" t="str">
+        <v>{{assessment_key}}</v>
+      </c>
+      <c r="C2" t="str">
+        <v>{{version}}</v>
+      </c>
+      <c r="D2" t="str">
+        <v>{{package_identifier}}</v>
+      </c>
+      <c r="E2" t="str">
+        <v>sonartra_report_first_fully_authored_import_TEMPLATE.xlsx</v>
+      </c>
+      <c r="F2" t="str">
+        <v>{{runtime_definition_row_count}}</v>
+      </c>
+      <c r="G2" t="str">
+        <v>{{runtime_result_content_row_count}}</v>
+      </c>
+      <c r="H2" t="str">
+        <v>{{preview_row_count}}</v>
+      </c>
+      <c r="I2" t="str">
+        <v>{{validation_notes}}</v>
+      </c>
+      <c r="J2" t="str">
+        <v>draft</v>
+      </c>
+      <c r="K2" t="str">
+        <v>import_summary::{{assessment_key}}::{{version}}</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K2"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:K2"/>
+  </ignoredErrors>
+</worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="UTF-8" standalone="yes"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"><dimension ref="A1:I1"/><cols><col min="1" max="1" width="23.83203125" customWidth="1"/><col min="2" max="2" width="15.83203125" customWidth="1"/><col min="3" max="3" width="14.83203125" customWidth="1"/><col min="4" max="4" width="14.83203125" customWidth="1"/><col min="5" max="5" width="18.83203125" customWidth="1"/><col min="6" max="6" width="23.83203125" customWidth="1"/><col min="7" max="7" width="14.83203125" customWidth="1"/><col min="8" max="8" width="14.83203125" customWidth="1"/><col min="9" max="9" width="14.83203125" customWidth="1"/></cols><sheetData><row r="1"><c r="A1" s="1" s="1" t="str"><v>validation_rule_key</v></c><c r="B1" s="1" s="1" t="str"><v>section_key</v></c><c r="C1" s="1" s="1" t="str"><v>field_key</v></c><c r="D1" s="1" s="1" t="str"><v>rule_type</v></c><c r="E1" s="1" s="1" t="str"><v>expected_value</v></c><c r="F1" s="1" s="1" t="str"><v>validation_guidance</v></c><c r="G1" s="1" s="1" t="str"><v>severity</v></c><c r="H1" s="1" s="1" t="str"><v>status</v></c><c r="I1" s="1" s="1" t="str"><v>lookup_key</v></c></row></sheetData><autoFilter ref="A1:I1"/><ignoredErrors><ignoredError numberStoredAsText="1" sqref="A1:I1"/></ignoredErrors></worksheet>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I1"/>
+  <cols>
+    <col min="1" max="1" width="23.83203125" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" customWidth="1"/>
+    <col min="6" max="6" width="23.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>validation_rule_key</v>
+      </c>
+      <c r="B1" t="str">
+        <v>section_key</v>
+      </c>
+      <c r="C1" t="str">
+        <v>field_key</v>
+      </c>
+      <c r="D1" t="str">
+        <v>rule_type</v>
+      </c>
+      <c r="E1" t="str">
+        <v>expected_value</v>
+      </c>
+      <c r="F1" t="str">
+        <v>validation_guidance</v>
+      </c>
+      <c r="G1" t="str">
+        <v>severity</v>
+      </c>
+      <c r="H1" t="str">
+        <v>status</v>
+      </c>
+      <c r="I1" t="str">
+        <v>lookup_key</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I1"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I1"/>
+  </ignoredErrors>
+</worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="UTF-8" standalone="yes"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"><dimension ref="A1:F5"/><cols><col min="1" max="1" width="16.83203125" customWidth="1"/><col min="2" max="2" width="14.83203125" customWidth="1"/><col min="3" max="3" width="16.83203125" customWidth="1"/><col min="4" max="4" width="16.83203125" customWidth="1"/><col min="5" max="5" width="15.83203125" customWidth="1"/><col min="6" max="6" width="14.83203125" customWidth="1"/></cols><sheetData><row r="1"><c r="A1" s="1" s="1" t="str"><v>lookup_group</v></c><c r="B1" s="1" s="1" t="str"><v>lookup_key</v></c><c r="C1" s="1" s="1" t="str"><v>lookup_label</v></c><c r="D1" s="1" s="1" t="str"><v>lookup_value</v></c><c r="E1" s="1" s="1" t="str"><v>description</v></c><c r="F1" s="1" s="1" t="str"><v>status</v></c></row><row r="2"><c r="A2" t="str"><v>status</v></c><c r="B2" t="str"><v>active</v></c><c r="C2" t="str"><v>Active</v></c><c r="D2" t="str"><v>active</v></c><c r="E2" t="str"><v>Import-ready row.</v></c><c r="F2" t="str"><v>active</v></c></row><row r="3"><c r="A3" t="str"><v>boolean</v></c><c r="B3" t="str"><v>true</v></c><c r="C3" t="str"><v>TRUE</v></c><c r="D3" t="str"><v>TRUE</v></c><c r="E3" t="str"><v>Boolean true marker.</v></c><c r="F3" t="str"><v>active</v></c></row><row r="4"><c r="A4" t="str"><v>report_contract</v></c><c r="B4" t="str"><v>report_first_canonical_payload_v1</v></c><c r="C4" t="str"><v>Report-first canonical payload v1</v></c><c r="D4" t="str"><v>report_first_canonical_payload_v1</v></c><c r="E4" t="str"><v>Current report-first template contract.</v></c><c r="F4" t="str"><v>active</v></c></row><row r="5"><c r="A5" t="str"><v>score_shape_policy</v></c><c r="B5" t="str"><v>pattern_level_score_shape_neutral</v></c><c r="C5" t="str"><v>Pattern-level neutral</v></c><c r="D5" t="str"><v>pattern_level_score_shape_neutral</v></c><c r="E5" t="str"><v>One authored report per ranked pattern.</v></c><c r="F5" t="str"><v>active</v></c></row></sheetData><autoFilter ref="A1:F5"/><ignoredErrors><ignoredError numberStoredAsText="1" sqref="A1:F5"/></ignoredErrors></worksheet>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F5"/>
+  <cols>
+    <col min="1" max="1" width="16.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" customWidth="1"/>
+    <col min="4" max="4" width="16.83203125" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>lookup_group</v>
+      </c>
+      <c r="B1" t="str">
+        <v>lookup_key</v>
+      </c>
+      <c r="C1" t="str">
+        <v>lookup_label</v>
+      </c>
+      <c r="D1" t="str">
+        <v>lookup_value</v>
+      </c>
+      <c r="E1" t="str">
+        <v>description</v>
+      </c>
+      <c r="F1" t="str">
+        <v>status</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>status</v>
+      </c>
+      <c r="B2" t="str">
+        <v>active</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D2" t="str">
+        <v>active</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Import-ready row.</v>
+      </c>
+      <c r="F2" t="str">
+        <v>active</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>boolean</v>
+      </c>
+      <c r="B3" t="str">
+        <v>true</v>
+      </c>
+      <c r="C3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="D3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Boolean true marker.</v>
+      </c>
+      <c r="F3" t="str">
+        <v>active</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>report_contract</v>
+      </c>
+      <c r="B4" t="str">
+        <v>report_first_canonical_payload_v1</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Report-first canonical payload v1</v>
+      </c>
+      <c r="D4" t="str">
+        <v>report_first_canonical_payload_v1</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Current report-first template contract.</v>
+      </c>
+      <c r="F4" t="str">
+        <v>active</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>score_shape_policy</v>
+      </c>
+      <c r="B5" t="str">
+        <v>pattern_level_score_shape_neutral</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Pattern-level neutral</v>
+      </c>
+      <c r="D5" t="str">
+        <v>pattern_level_score_shape_neutral</v>
+      </c>
+      <c r="E5" t="str">
+        <v>One authored report per ranked pattern.</v>
+      </c>
+      <c r="F5" t="str">
+        <v>active</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
+  </ignoredErrors>
+</worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="UTF-8" standalone="yes"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"><dimension ref="A1:H5"/><cols><col min="1" max="1" width="14.83203125" customWidth="1"/><col min="2" max="2" width="14.83203125" customWidth="1"/><col min="3" max="3" width="16.83203125" customWidth="1"/><col min="4" max="4" width="22.83203125" customWidth="1"/><col min="5" max="5" width="16.83203125" customWidth="1"/><col min="6" max="6" width="14.83203125" customWidth="1"/><col min="7" max="7" width="14.83203125" customWidth="1"/><col min="8" max="8" width="14.83203125" customWidth="1"/></cols><sheetData><row r="1"><c r="A1" s="1" s="1" t="str"><v>domain_key</v></c><c r="B1" s="1" s="1" t="str"><v>signal_key</v></c><c r="C1" s="1" s="1" t="str"><v>signal_label</v></c><c r="D1" s="1" s="1" t="str"><v>signal_description</v></c><c r="E1" s="1" s="1" t="str"><v>signal_order</v></c><c r="F1" s="1" s="1" t="str"><v>scored</v></c><c r="G1" s="1" s="1" t="str"><v>status</v></c><c r="H1" s="1" s="1" t="str"><v>lookup_key</v></c></row><row r="2"><c r="A2" t="str"><v>{{domain_key}}</v></c><c r="B2" t="str"><v>signal_a</v></c><c r="C2" t="str"><v>{{signal_a_label}}</v></c><c r="D2" t="str"><v>{{signal_a_description}}</v></c><c r="E2"><v>1</v></c><c r="F2" t="str"><v>TRUE</v></c><c r="G2" t="str"><v>active</v></c><c r="H2" t="str"><v>signal::signal_a</v></c></row><row r="3"><c r="A3" t="str"><v>{{domain_key}}</v></c><c r="B3" t="str"><v>signal_b</v></c><c r="C3" t="str"><v>{{signal_b_label}}</v></c><c r="D3" t="str"><v>{{signal_b_description}}</v></c><c r="E3"><v>2</v></c><c r="F3" t="str"><v>TRUE</v></c><c r="G3" t="str"><v>active</v></c><c r="H3" t="str"><v>signal::signal_b</v></c></row><row r="4"><c r="A4" t="str"><v>{{domain_key}}</v></c><c r="B4" t="str"><v>signal_c</v></c><c r="C4" t="str"><v>{{signal_c_label}}</v></c><c r="D4" t="str"><v>{{signal_c_description}}</v></c><c r="E4"><v>3</v></c><c r="F4" t="str"><v>TRUE</v></c><c r="G4" t="str"><v>active</v></c><c r="H4" t="str"><v>signal::signal_c</v></c></row><row r="5"><c r="A5" t="str"><v>{{domain_key}}</v></c><c r="B5" t="str"><v>signal_d</v></c><c r="C5" t="str"><v>{{signal_d_label}}</v></c><c r="D5" t="str"><v>{{signal_d_description}}</v></c><c r="E5"><v>4</v></c><c r="F5" t="str"><v>TRUE</v></c><c r="G5" t="str"><v>active</v></c><c r="H5" t="str"><v>signal::signal_d</v></c></row></sheetData><autoFilter ref="A1:H5"/><ignoredErrors><ignoredError numberStoredAsText="1" sqref="A1:H5"/></ignoredErrors></worksheet>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H5"/>
+  <cols>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" customWidth="1"/>
+    <col min="4" max="4" width="22.83203125" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>domain_key</v>
+      </c>
+      <c r="B1" t="str">
+        <v>signal_key</v>
+      </c>
+      <c r="C1" t="str">
+        <v>signal_label</v>
+      </c>
+      <c r="D1" t="str">
+        <v>signal_description</v>
+      </c>
+      <c r="E1" t="str">
+        <v>signal_order</v>
+      </c>
+      <c r="F1" t="str">
+        <v>scored</v>
+      </c>
+      <c r="G1" t="str">
+        <v>status</v>
+      </c>
+      <c r="H1" t="str">
+        <v>lookup_key</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="B2" t="str">
+        <v>signal_a</v>
+      </c>
+      <c r="C2" t="str">
+        <v>{{signal_a_label}}</v>
+      </c>
+      <c r="D2" t="str">
+        <v>{{signal_a_description}}</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G2" t="str">
+        <v>active</v>
+      </c>
+      <c r="H2" t="str">
+        <v>signal::signal_a</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="B3" t="str">
+        <v>signal_b</v>
+      </c>
+      <c r="C3" t="str">
+        <v>{{signal_b_label}}</v>
+      </c>
+      <c r="D3" t="str">
+        <v>{{signal_b_description}}</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G3" t="str">
+        <v>active</v>
+      </c>
+      <c r="H3" t="str">
+        <v>signal::signal_b</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="B4" t="str">
+        <v>signal_c</v>
+      </c>
+      <c r="C4" t="str">
+        <v>{{signal_c_label}}</v>
+      </c>
+      <c r="D4" t="str">
+        <v>{{signal_c_description}}</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G4" t="str">
+        <v>active</v>
+      </c>
+      <c r="H4" t="str">
+        <v>signal::signal_c</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="B5" t="str">
+        <v>signal_d</v>
+      </c>
+      <c r="C5" t="str">
+        <v>{{signal_d_label}}</v>
+      </c>
+      <c r="D5" t="str">
+        <v>{{signal_d_description}}</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G5" t="str">
+        <v>active</v>
+      </c>
+      <c r="H5" t="str">
+        <v>signal::signal_d</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H5"/>
+  </ignoredErrors>
+</worksheet>
 </file>
 
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="UTF-8" standalone="yes"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"><dimension ref="A1:U25"/><cols><col min="1" max="1" width="18.83203125" customWidth="1"/><col min="2" max="2" width="22.83203125" customWidth="1"/><col min="3" max="3" width="15.83203125" customWidth="1"/><col min="4" max="4" width="19.83203125" customWidth="1"/><col min="5" max="5" width="14.83203125" customWidth="1"/><col min="6" max="6" width="15.83203125" customWidth="1"/><col min="7" max="7" width="14.83203125" customWidth="1"/><col min="8" max="8" width="19.83203125" customWidth="1"/><col min="9" max="9" width="22.83203125" customWidth="1"/><col min="10" max="10" width="15.83203125" customWidth="1"/><col min="11" max="11" width="26.83203125" customWidth="1"/><col min="12" max="12" width="24.83203125" customWidth="1"/><col min="13" max="13" width="23.83203125" customWidth="1"/><col min="14" max="14" width="16.83203125" customWidth="1"/><col min="15" max="15" width="24.83203125" customWidth="1"/><col min="16" max="16" width="14.83203125" customWidth="1"/><col min="17" max="17" width="19.83203125" customWidth="1"/><col min="18" max="18" width="15.83203125" customWidth="1"/><col min="19" max="19" width="20.83203125" customWidth="1"/><col min="20" max="20" width="23.83203125" customWidth="1"/><col min="21" max="21" width="14.83203125" customWidth="1"/></cols><sheetData><row r="1"><c r="A1" s="1" s="1" t="str"><v>assessment_key</v></c><c r="B1" s="1" s="1" t="str"><v>assessment_version</v></c><c r="C1" s="1" s="1" t="str"><v>package_key</v></c><c r="D1" s="1" s="1" t="str"><v>package_version</v></c><c r="E1" s="1" s="1" t="str"><v>domain_key</v></c><c r="F1" s="1" s="1" t="str"><v>pattern_key</v></c><c r="G1" s="1" s="1" t="str"><v>report_key</v></c><c r="H1" s="1" s="1" t="str"><v>report_contract</v></c><c r="I1" s="1" s="1" t="str"><v>score_shape_policy</v></c><c r="J1" s="1" s="1" t="str"><v>score_shape</v></c><c r="K1" s="1" s="1" t="str"><v>supported_score_shapes</v></c><c r="L1" s="1" s="1" t="str"><v>source_markdown_path</v></c><c r="M1" s="1" s="1" t="str"><v>source_content_hash</v></c><c r="N1" s="1" s="1" t="str"><v>content_hash</v></c><c r="O1" s="1" s="1" t="str"><v>report_template_json</v></c><c r="P1" s="1" s="1" t="str"><v>status</v></c><c r="Q1" s="1" s="1" t="str"><v>manifest_status</v></c><c r="R1" s="1" s="1" t="str"><v>publishable</v></c><c r="S1" s="1" s="1" t="str"><v>ready_for_import</v></c><c r="T1" s="1" s="1" t="str"><v>generation_metadata</v></c><c r="U1" s="1" s="1" t="str"><v>lookup_key</v></c></row><row r="2"><c r="A2" t="str"><v>{{assessment_key}}</v></c><c r="B2" t="str"><v>{{package_version}}</v></c><c r="C2" t="str"><v>{{assessment_key}}-report-first</v></c><c r="D2" t="str"><v>{{package_version}}</v></c><c r="E2" t="str"><v>{{domain_key}}</v></c><c r="F2" t="str"><v>signal_a_signal_b_signal_c_signal_d</v></c><c r="G2" t="str"><v>signal_a_signal_b_signal_c_signal_d</v></c><c r="H2" t="str"><v>report_first_canonical_payload_v1</v></c><c r="I2" t="str"><v>pattern_level_score_shape_neutral</v></c><c r="J2" t="str"><v></v></c><c r="K2" t="str"><v>[]</v></c><c r="L2" t="str"><v>content/authoring/{{assessment_key}}/report-first/canonical-reports/signal_a_signal_b_signal_c_signal_d.md</v></c><c r="M2" t="str"><v>{{source_content_hash}}</v></c><c r="N2" t="str"><v>{{content_hash}}</v></c><c r="O2" t="str"><v>{&quot;metadata&quot;:{&quot;contractName&quot;:&quot;report_first_canonical_payload_v1&quot;,&quot;reportModel&quot;:&quot;report_first_canonical&quot;},&quot;reportKey&quot;:&quot;signal_a_signal_b_signal_c_signal_d&quot;,&quot;patternKey&quot;:&quot;signal_a_signal_b_signal_c_signal_d&quot;,&quot;domainKey&quot;:&quot;{{domain_key}}&quot;,&quot;report&quot;:{&quot;reportKey&quot;:&quot;signal_a_signal_b_signal_c_signal_d&quot;,&quot;patternKey&quot;:&quot;signal_a_signal_b_signal_c_signal_d&quot;,&quot;reportTitle&quot;:&quot;{{assessment_title}} report&quot;,&quot;hero&quot;:{&quot;title&quot;:&quot;{{fully_authored_report_title}}&quot;,&quot;resultStatement&quot;:&quot;{{fully_authored_result_statement}}&quot;},&quot;opening&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{editorial_introduction}}&quot;}],&quot;patternSummary&quot;:{&quot;title&quot;:&quot;Pattern at a glance&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{pattern_summary}}&quot;}]},&quot;keyInsight&quot;:{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{key_insight}}&quot;},&quot;chapters&quot;:[{&quot;chapterKey&quot;:&quot;chapter_1&quot;,&quot;chapterNumber&quot;:1,&quot;title&quot;:&quot;{{chapter_1_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_1_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_2&quot;,&quot;chapterNumber&quot;:2,&quot;title&quot;:&quot;{{chapter_2_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_2_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_3&quot;,&quot;chapterNumber&quot;:3,&quot;title&quot;:&quot;{{chapter_3_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_3_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_4&quot;,&quot;chapterNumber&quot;:4,&quot;title&quot;:&quot;{{chapter_4_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_4_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_5&quot;,&quot;chapterNumber&quot;:5,&quot;title&quot;:&quot;{{chapter_5_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_5_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_6&quot;,&quot;chapterNumber&quot;:6,&quot;title&quot;:&quot;{{chapter_6_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_6_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_7&quot;,&quot;chapterNumber&quot;:7,&quot;title&quot;:&quot;{{chapter_7_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_7_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_8&quot;,&quot;chapterNumber&quot;:8,&quot;title&quot;:&quot;{{chapter_8_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_8_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_9&quot;,&quot;chapterNumber&quot;:9,&quot;title&quot;:&quot;{{chapter_9_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_9_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_10&quot;,&quot;chapterNumber&quot;:10,&quot;title&quot;:&quot;{{chapter_10_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_10_body}}&quot;}],&quot;readerFacing&quot;:true}],&quot;closing&quot;:{&quot;synthesis&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{closing_synthesis}}&quot;}],&quot;finalLine&quot;:&quot;{{final_line}}&quot;},&quot;pdf&quot;:{&quot;title&quot;:&quot;Save this report&quot;,&quot;body&quot;:&quot;{{reference_note}}&quot;}},&quot;evidenceTemplate&quot;:{&quot;title&quot;:&quot;Evidence behind your result&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{evidence_note}}&quot;}]}}</v></c><c r="P2" t="str"><v>active</v></c><c r="Q2" t="str"><v>ready_for_import</v></c><c r="R2" t="str"><v>TRUE</v></c><c r="S2" t="str"><v>TRUE</v></c><c r="T2" t="str"><v>{&quot;generated_from&quot;:&quot;fully_authored_report_first_template&quot;,&quot;deterministic&quot;:true}</v></c><c r="U2" t="str"><v>report_first::signal_a_signal_b_signal_c_signal_d</v></c></row><row r="3"><c r="A3" t="str"><v>{{assessment_key}}</v></c><c r="B3" t="str"><v>{{package_version}}</v></c><c r="C3" t="str"><v>{{assessment_key}}-report-first</v></c><c r="D3" t="str"><v>{{package_version}}</v></c><c r="E3" t="str"><v>{{domain_key}}</v></c><c r="F3" t="str"><v>signal_a_signal_b_signal_d_signal_c</v></c><c r="G3" t="str"><v>signal_a_signal_b_signal_d_signal_c</v></c><c r="H3" t="str"><v>report_first_canonical_payload_v1</v></c><c r="I3" t="str"><v>pattern_level_score_shape_neutral</v></c><c r="J3" t="str"><v></v></c><c r="K3" t="str"><v>[]</v></c><c r="L3" t="str"><v>content/authoring/{{assessment_key}}/report-first/canonical-reports/signal_a_signal_b_signal_d_signal_c.md</v></c><c r="M3" t="str"><v>{{source_content_hash}}</v></c><c r="N3" t="str"><v>{{content_hash}}</v></c><c r="O3" t="str"><v>{&quot;metadata&quot;:{&quot;contractName&quot;:&quot;report_first_canonical_payload_v1&quot;,&quot;reportModel&quot;:&quot;report_first_canonical&quot;},&quot;reportKey&quot;:&quot;signal_a_signal_b_signal_d_signal_c&quot;,&quot;patternKey&quot;:&quot;signal_a_signal_b_signal_d_signal_c&quot;,&quot;domainKey&quot;:&quot;{{domain_key}}&quot;,&quot;report&quot;:{&quot;reportKey&quot;:&quot;signal_a_signal_b_signal_d_signal_c&quot;,&quot;patternKey&quot;:&quot;signal_a_signal_b_signal_d_signal_c&quot;,&quot;reportTitle&quot;:&quot;{{assessment_title}} report&quot;,&quot;hero&quot;:{&quot;title&quot;:&quot;{{fully_authored_report_title}}&quot;,&quot;resultStatement&quot;:&quot;{{fully_authored_result_statement}}&quot;},&quot;opening&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{editorial_introduction}}&quot;}],&quot;patternSummary&quot;:{&quot;title&quot;:&quot;Pattern at a glance&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{pattern_summary}}&quot;}]},&quot;keyInsight&quot;:{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{key_insight}}&quot;},&quot;chapters&quot;:[{&quot;chapterKey&quot;:&quot;chapter_1&quot;,&quot;chapterNumber&quot;:1,&quot;title&quot;:&quot;{{chapter_1_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_1_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_2&quot;,&quot;chapterNumber&quot;:2,&quot;title&quot;:&quot;{{chapter_2_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_2_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_3&quot;,&quot;chapterNumber&quot;:3,&quot;title&quot;:&quot;{{chapter_3_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_3_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_4&quot;,&quot;chapterNumber&quot;:4,&quot;title&quot;:&quot;{{chapter_4_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_4_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_5&quot;,&quot;chapterNumber&quot;:5,&quot;title&quot;:&quot;{{chapter_5_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_5_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_6&quot;,&quot;chapterNumber&quot;:6,&quot;title&quot;:&quot;{{chapter_6_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_6_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_7&quot;,&quot;chapterNumber&quot;:7,&quot;title&quot;:&quot;{{chapter_7_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_7_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_8&quot;,&quot;chapterNumber&quot;:8,&quot;title&quot;:&quot;{{chapter_8_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_8_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_9&quot;,&quot;chapterNumber&quot;:9,&quot;title&quot;:&quot;{{chapter_9_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_9_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_10&quot;,&quot;chapterNumber&quot;:10,&quot;title&quot;:&quot;{{chapter_10_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_10_body}}&quot;}],&quot;readerFacing&quot;:true}],&quot;closing&quot;:{&quot;synthesis&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{closing_synthesis}}&quot;}],&quot;finalLine&quot;:&quot;{{final_line}}&quot;},&quot;pdf&quot;:{&quot;title&quot;:&quot;Save this report&quot;,&quot;body&quot;:&quot;{{reference_note}}&quot;}},&quot;evidenceTemplate&quot;:{&quot;title&quot;:&quot;Evidence behind your result&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{evidence_note}}&quot;}]}}</v></c><c r="P3" t="str"><v>active</v></c><c r="Q3" t="str"><v>ready_for_import</v></c><c r="R3" t="str"><v>TRUE</v></c><c r="S3" t="str"><v>TRUE</v></c><c r="T3" t="str"><v>{&quot;generated_from&quot;:&quot;fully_authored_report_first_template&quot;,&quot;deterministic&quot;:true}</v></c><c r="U3" t="str"><v>report_first::signal_a_signal_b_signal_d_signal_c</v></c></row><row r="4"><c r="A4" t="str"><v>{{assessment_key}}</v></c><c r="B4" t="str"><v>{{package_version}}</v></c><c r="C4" t="str"><v>{{assessment_key}}-report-first</v></c><c r="D4" t="str"><v>{{package_version}}</v></c><c r="E4" t="str"><v>{{domain_key}}</v></c><c r="F4" t="str"><v>signal_a_signal_c_signal_b_signal_d</v></c><c r="G4" t="str"><v>signal_a_signal_c_signal_b_signal_d</v></c><c r="H4" t="str"><v>report_first_canonical_payload_v1</v></c><c r="I4" t="str"><v>pattern_level_score_shape_neutral</v></c><c r="J4" t="str"><v></v></c><c r="K4" t="str"><v>[]</v></c><c r="L4" t="str"><v>content/authoring/{{assessment_key}}/report-first/canonical-reports/signal_a_signal_c_signal_b_signal_d.md</v></c><c r="M4" t="str"><v>{{source_content_hash}}</v></c><c r="N4" t="str"><v>{{content_hash}}</v></c><c r="O4" t="str"><v>{&quot;metadata&quot;:{&quot;contractName&quot;:&quot;report_first_canonical_payload_v1&quot;,&quot;reportModel&quot;:&quot;report_first_canonical&quot;},&quot;reportKey&quot;:&quot;signal_a_signal_c_signal_b_signal_d&quot;,&quot;patternKey&quot;:&quot;signal_a_signal_c_signal_b_signal_d&quot;,&quot;domainKey&quot;:&quot;{{domain_key}}&quot;,&quot;report&quot;:{&quot;reportKey&quot;:&quot;signal_a_signal_c_signal_b_signal_d&quot;,&quot;patternKey&quot;:&quot;signal_a_signal_c_signal_b_signal_d&quot;,&quot;reportTitle&quot;:&quot;{{assessment_title}} report&quot;,&quot;hero&quot;:{&quot;title&quot;:&quot;{{fully_authored_report_title}}&quot;,&quot;resultStatement&quot;:&quot;{{fully_authored_result_statement}}&quot;},&quot;opening&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{editorial_introduction}}&quot;}],&quot;patternSummary&quot;:{&quot;title&quot;:&quot;Pattern at a glance&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{pattern_summary}}&quot;}]},&quot;keyInsight&quot;:{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{key_insight}}&quot;},&quot;chapters&quot;:[{&quot;chapterKey&quot;:&quot;chapter_1&quot;,&quot;chapterNumber&quot;:1,&quot;title&quot;:&quot;{{chapter_1_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_1_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_2&quot;,&quot;chapterNumber&quot;:2,&quot;title&quot;:&quot;{{chapter_2_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_2_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_3&quot;,&quot;chapterNumber&quot;:3,&quot;title&quot;:&quot;{{chapter_3_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_3_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_4&quot;,&quot;chapterNumber&quot;:4,&quot;title&quot;:&quot;{{chapter_4_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_4_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_5&quot;,&quot;chapterNumber&quot;:5,&quot;title&quot;:&quot;{{chapter_5_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_5_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_6&quot;,&quot;chapterNumber&quot;:6,&quot;title&quot;:&quot;{{chapter_6_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_6_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_7&quot;,&quot;chapterNumber&quot;:7,&quot;title&quot;:&quot;{{chapter_7_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_7_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_8&quot;,&quot;chapterNumber&quot;:8,&quot;title&quot;:&quot;{{chapter_8_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_8_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_9&quot;,&quot;chapterNumber&quot;:9,&quot;title&quot;:&quot;{{chapter_9_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_9_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_10&quot;,&quot;chapterNumber&quot;:10,&quot;title&quot;:&quot;{{chapter_10_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_10_body}}&quot;}],&quot;readerFacing&quot;:true}],&quot;closing&quot;:{&quot;synthesis&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{closing_synthesis}}&quot;}],&quot;finalLine&quot;:&quot;{{final_line}}&quot;},&quot;pdf&quot;:{&quot;title&quot;:&quot;Save this report&quot;,&quot;body&quot;:&quot;{{reference_note}}&quot;}},&quot;evidenceTemplate&quot;:{&quot;title&quot;:&quot;Evidence behind your result&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{evidence_note}}&quot;}]}}</v></c><c r="P4" t="str"><v>active</v></c><c r="Q4" t="str"><v>ready_for_import</v></c><c r="R4" t="str"><v>TRUE</v></c><c r="S4" t="str"><v>TRUE</v></c><c r="T4" t="str"><v>{&quot;generated_from&quot;:&quot;fully_authored_report_first_template&quot;,&quot;deterministic&quot;:true}</v></c><c r="U4" t="str"><v>report_first::signal_a_signal_c_signal_b_signal_d</v></c></row><row r="5"><c r="A5" t="str"><v>{{assessment_key}}</v></c><c r="B5" t="str"><v>{{package_version}}</v></c><c r="C5" t="str"><v>{{assessment_key}}-report-first</v></c><c r="D5" t="str"><v>{{package_version}}</v></c><c r="E5" t="str"><v>{{domain_key}}</v></c><c r="F5" t="str"><v>signal_a_signal_c_signal_d_signal_b</v></c><c r="G5" t="str"><v>signal_a_signal_c_signal_d_signal_b</v></c><c r="H5" t="str"><v>report_first_canonical_payload_v1</v></c><c r="I5" t="str"><v>pattern_level_score_shape_neutral</v></c><c r="J5" t="str"><v></v></c><c r="K5" t="str"><v>[]</v></c><c r="L5" t="str"><v>content/authoring/{{assessment_key}}/report-first/canonical-reports/signal_a_signal_c_signal_d_signal_b.md</v></c><c r="M5" t="str"><v>{{source_content_hash}}</v></c><c r="N5" t="str"><v>{{content_hash}}</v></c><c r="O5" t="str"><v>{&quot;metadata&quot;:{&quot;contractName&quot;:&quot;report_first_canonical_payload_v1&quot;,&quot;reportModel&quot;:&quot;report_first_canonical&quot;},&quot;reportKey&quot;:&quot;signal_a_signal_c_signal_d_signal_b&quot;,&quot;patternKey&quot;:&quot;signal_a_signal_c_signal_d_signal_b&quot;,&quot;domainKey&quot;:&quot;{{domain_key}}&quot;,&quot;report&quot;:{&quot;reportKey&quot;:&quot;signal_a_signal_c_signal_d_signal_b&quot;,&quot;patternKey&quot;:&quot;signal_a_signal_c_signal_d_signal_b&quot;,&quot;reportTitle&quot;:&quot;{{assessment_title}} report&quot;,&quot;hero&quot;:{&quot;title&quot;:&quot;{{fully_authored_report_title}}&quot;,&quot;resultStatement&quot;:&quot;{{fully_authored_result_statement}}&quot;},&quot;opening&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{editorial_introduction}}&quot;}],&quot;patternSummary&quot;:{&quot;title&quot;:&quot;Pattern at a glance&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{pattern_summary}}&quot;}]},&quot;keyInsight&quot;:{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{key_insight}}&quot;},&quot;chapters&quot;:[{&quot;chapterKey&quot;:&quot;chapter_1&quot;,&quot;chapterNumber&quot;:1,&quot;title&quot;:&quot;{{chapter_1_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_1_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_2&quot;,&quot;chapterNumber&quot;:2,&quot;title&quot;:&quot;{{chapter_2_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_2_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_3&quot;,&quot;chapterNumber&quot;:3,&quot;title&quot;:&quot;{{chapter_3_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_3_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_4&quot;,&quot;chapterNumber&quot;:4,&quot;title&quot;:&quot;{{chapter_4_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_4_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_5&quot;,&quot;chapterNumber&quot;:5,&quot;title&quot;:&quot;{{chapter_5_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_5_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_6&quot;,&quot;chapterNumber&quot;:6,&quot;title&quot;:&quot;{{chapter_6_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_6_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_7&quot;,&quot;chapterNumber&quot;:7,&quot;title&quot;:&quot;{{chapter_7_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_7_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_8&quot;,&quot;chapterNumber&quot;:8,&quot;title&quot;:&quot;{{chapter_8_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_8_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_9&quot;,&quot;chapterNumber&quot;:9,&quot;title&quot;:&quot;{{chapter_9_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_9_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_10&quot;,&quot;chapterNumber&quot;:10,&quot;title&quot;:&quot;{{chapter_10_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_10_body}}&quot;}],&quot;readerFacing&quot;:true}],&quot;closing&quot;:{&quot;synthesis&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{closing_synthesis}}&quot;}],&quot;finalLine&quot;:&quot;{{final_line}}&quot;},&quot;pdf&quot;:{&quot;title&quot;:&quot;Save this report&quot;,&quot;body&quot;:&quot;{{reference_note}}&quot;}},&quot;evidenceTemplate&quot;:{&quot;title&quot;:&quot;Evidence behind your result&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{evidence_note}}&quot;}]}}</v></c><c r="P5" t="str"><v>active</v></c><c r="Q5" t="str"><v>ready_for_import</v></c><c r="R5" t="str"><v>TRUE</v></c><c r="S5" t="str"><v>TRUE</v></c><c r="T5" t="str"><v>{&quot;generated_from&quot;:&quot;fully_authored_report_first_template&quot;,&quot;deterministic&quot;:true}</v></c><c r="U5" t="str"><v>report_first::signal_a_signal_c_signal_d_signal_b</v></c></row><row r="6"><c r="A6" t="str"><v>{{assessment_key}}</v></c><c r="B6" t="str"><v>{{package_version}}</v></c><c r="C6" t="str"><v>{{assessment_key}}-report-first</v></c><c r="D6" t="str"><v>{{package_version}}</v></c><c r="E6" t="str"><v>{{domain_key}}</v></c><c r="F6" t="str"><v>signal_a_signal_d_signal_b_signal_c</v></c><c r="G6" t="str"><v>signal_a_signal_d_signal_b_signal_c</v></c><c r="H6" t="str"><v>report_first_canonical_payload_v1</v></c><c r="I6" t="str"><v>pattern_level_score_shape_neutral</v></c><c r="J6" t="str"><v></v></c><c r="K6" t="str"><v>[]</v></c><c r="L6" t="str"><v>content/authoring/{{assessment_key}}/report-first/canonical-reports/signal_a_signal_d_signal_b_signal_c.md</v></c><c r="M6" t="str"><v>{{source_content_hash}}</v></c><c r="N6" t="str"><v>{{content_hash}}</v></c><c r="O6" t="str"><v>{&quot;metadata&quot;:{&quot;contractName&quot;:&quot;report_first_canonical_payload_v1&quot;,&quot;reportModel&quot;:&quot;report_first_canonical&quot;},&quot;reportKey&quot;:&quot;signal_a_signal_d_signal_b_signal_c&quot;,&quot;patternKey&quot;:&quot;signal_a_signal_d_signal_b_signal_c&quot;,&quot;domainKey&quot;:&quot;{{domain_key}}&quot;,&quot;report&quot;:{&quot;reportKey&quot;:&quot;signal_a_signal_d_signal_b_signal_c&quot;,&quot;patternKey&quot;:&quot;signal_a_signal_d_signal_b_signal_c&quot;,&quot;reportTitle&quot;:&quot;{{assessment_title}} report&quot;,&quot;hero&quot;:{&quot;title&quot;:&quot;{{fully_authored_report_title}}&quot;,&quot;resultStatement&quot;:&quot;{{fully_authored_result_statement}}&quot;},&quot;opening&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{editorial_introduction}}&quot;}],&quot;patternSummary&quot;:{&quot;title&quot;:&quot;Pattern at a glance&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{pattern_summary}}&quot;}]},&quot;keyInsight&quot;:{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{key_insight}}&quot;},&quot;chapters&quot;:[{&quot;chapterKey&quot;:&quot;chapter_1&quot;,&quot;chapterNumber&quot;:1,&quot;title&quot;:&quot;{{chapter_1_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_1_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_2&quot;,&quot;chapterNumber&quot;:2,&quot;title&quot;:&quot;{{chapter_2_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_2_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_3&quot;,&quot;chapterNumber&quot;:3,&quot;title&quot;:&quot;{{chapter_3_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_3_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_4&quot;,&quot;chapterNumber&quot;:4,&quot;title&quot;:&quot;{{chapter_4_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_4_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_5&quot;,&quot;chapterNumber&quot;:5,&quot;title&quot;:&quot;{{chapter_5_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_5_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_6&quot;,&quot;chapterNumber&quot;:6,&quot;title&quot;:&quot;{{chapter_6_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_6_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_7&quot;,&quot;chapterNumber&quot;:7,&quot;title&quot;:&quot;{{chapter_7_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_7_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_8&quot;,&quot;chapterNumber&quot;:8,&quot;title&quot;:&quot;{{chapter_8_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_8_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_9&quot;,&quot;chapterNumber&quot;:9,&quot;title&quot;:&quot;{{chapter_9_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_9_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_10&quot;,&quot;chapterNumber&quot;:10,&quot;title&quot;:&quot;{{chapter_10_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_10_body}}&quot;}],&quot;readerFacing&quot;:true}],&quot;closing&quot;:{&quot;synthesis&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{closing_synthesis}}&quot;}],&quot;finalLine&quot;:&quot;{{final_line}}&quot;},&quot;pdf&quot;:{&quot;title&quot;:&quot;Save this report&quot;,&quot;body&quot;:&quot;{{reference_note}}&quot;}},&quot;evidenceTemplate&quot;:{&quot;title&quot;:&quot;Evidence behind your result&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{evidence_note}}&quot;}]}}</v></c><c r="P6" t="str"><v>active</v></c><c r="Q6" t="str"><v>ready_for_import</v></c><c r="R6" t="str"><v>TRUE</v></c><c r="S6" t="str"><v>TRUE</v></c><c r="T6" t="str"><v>{&quot;generated_from&quot;:&quot;fully_authored_report_first_template&quot;,&quot;deterministic&quot;:true}</v></c><c r="U6" t="str"><v>report_first::signal_a_signal_d_signal_b_signal_c</v></c></row><row r="7"><c r="A7" t="str"><v>{{assessment_key}}</v></c><c r="B7" t="str"><v>{{package_version}}</v></c><c r="C7" t="str"><v>{{assessment_key}}-report-first</v></c><c r="D7" t="str"><v>{{package_version}}</v></c><c r="E7" t="str"><v>{{domain_key}}</v></c><c r="F7" t="str"><v>signal_a_signal_d_signal_c_signal_b</v></c><c r="G7" t="str"><v>signal_a_signal_d_signal_c_signal_b</v></c><c r="H7" t="str"><v>report_first_canonical_payload_v1</v></c><c r="I7" t="str"><v>pattern_level_score_shape_neutral</v></c><c r="J7" t="str"><v></v></c><c r="K7" t="str"><v>[]</v></c><c r="L7" t="str"><v>content/authoring/{{assessment_key}}/report-first/canonical-reports/signal_a_signal_d_signal_c_signal_b.md</v></c><c r="M7" t="str"><v>{{source_content_hash}}</v></c><c r="N7" t="str"><v>{{content_hash}}</v></c><c r="O7" t="str"><v>{&quot;metadata&quot;:{&quot;contractName&quot;:&quot;report_first_canonical_payload_v1&quot;,&quot;reportModel&quot;:&quot;report_first_canonical&quot;},&quot;reportKey&quot;:&quot;signal_a_signal_d_signal_c_signal_b&quot;,&quot;patternKey&quot;:&quot;signal_a_signal_d_signal_c_signal_b&quot;,&quot;domainKey&quot;:&quot;{{domain_key}}&quot;,&quot;report&quot;:{&quot;reportKey&quot;:&quot;signal_a_signal_d_signal_c_signal_b&quot;,&quot;patternKey&quot;:&quot;signal_a_signal_d_signal_c_signal_b&quot;,&quot;reportTitle&quot;:&quot;{{assessment_title}} report&quot;,&quot;hero&quot;:{&quot;title&quot;:&quot;{{fully_authored_report_title}}&quot;,&quot;resultStatement&quot;:&quot;{{fully_authored_result_statement}}&quot;},&quot;opening&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{editorial_introduction}}&quot;}],&quot;patternSummary&quot;:{&quot;title&quot;:&quot;Pattern at a glance&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{pattern_summary}}&quot;}]},&quot;keyInsight&quot;:{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{key_insight}}&quot;},&quot;chapters&quot;:[{&quot;chapterKey&quot;:&quot;chapter_1&quot;,&quot;chapterNumber&quot;:1,&quot;title&quot;:&quot;{{chapter_1_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_1_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_2&quot;,&quot;chapterNumber&quot;:2,&quot;title&quot;:&quot;{{chapter_2_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_2_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_3&quot;,&quot;chapterNumber&quot;:3,&quot;title&quot;:&quot;{{chapter_3_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_3_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_4&quot;,&quot;chapterNumber&quot;:4,&quot;title&quot;:&quot;{{chapter_4_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_4_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_5&quot;,&quot;chapterNumber&quot;:5,&quot;title&quot;:&quot;{{chapter_5_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_5_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_6&quot;,&quot;chapterNumber&quot;:6,&quot;title&quot;:&quot;{{chapter_6_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_6_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_7&quot;,&quot;chapterNumber&quot;:7,&quot;title&quot;:&quot;{{chapter_7_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_7_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_8&quot;,&quot;chapterNumber&quot;:8,&quot;title&quot;:&quot;{{chapter_8_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_8_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_9&quot;,&quot;chapterNumber&quot;:9,&quot;title&quot;:&quot;{{chapter_9_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_9_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_10&quot;,&quot;chapterNumber&quot;:10,&quot;title&quot;:&quot;{{chapter_10_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_10_body}}&quot;}],&quot;readerFacing&quot;:true}],&quot;closing&quot;:{&quot;synthesis&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{closing_synthesis}}&quot;}],&quot;finalLine&quot;:&quot;{{final_line}}&quot;},&quot;pdf&quot;:{&quot;title&quot;:&quot;Save this report&quot;,&quot;body&quot;:&quot;{{reference_note}}&quot;}},&quot;evidenceTemplate&quot;:{&quot;title&quot;:&quot;Evidence behind your result&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{evidence_note}}&quot;}]}}</v></c><c r="P7" t="str"><v>active</v></c><c r="Q7" t="str"><v>ready_for_import</v></c><c r="R7" t="str"><v>TRUE</v></c><c r="S7" t="str"><v>TRUE</v></c><c r="T7" t="str"><v>{&quot;generated_from&quot;:&quot;fully_authored_report_first_template&quot;,&quot;deterministic&quot;:true}</v></c><c r="U7" t="str"><v>report_first::signal_a_signal_d_signal_c_signal_b</v></c></row><row r="8"><c r="A8" t="str"><v>{{assessment_key}}</v></c><c r="B8" t="str"><v>{{package_version}}</v></c><c r="C8" t="str"><v>{{assessment_key}}-report-first</v></c><c r="D8" t="str"><v>{{package_version}}</v></c><c r="E8" t="str"><v>{{domain_key}}</v></c><c r="F8" t="str"><v>signal_b_signal_a_signal_c_signal_d</v></c><c r="G8" t="str"><v>signal_b_signal_a_signal_c_signal_d</v></c><c r="H8" t="str"><v>report_first_canonical_payload_v1</v></c><c r="I8" t="str"><v>pattern_level_score_shape_neutral</v></c><c r="J8" t="str"><v></v></c><c r="K8" t="str"><v>[]</v></c><c r="L8" t="str"><v>content/authoring/{{assessment_key}}/report-first/canonical-reports/signal_b_signal_a_signal_c_signal_d.md</v></c><c r="M8" t="str"><v>{{source_content_hash}}</v></c><c r="N8" t="str"><v>{{content_hash}}</v></c><c r="O8" t="str"><v>{&quot;metadata&quot;:{&quot;contractName&quot;:&quot;report_first_canonical_payload_v1&quot;,&quot;reportModel&quot;:&quot;report_first_canonical&quot;},&quot;reportKey&quot;:&quot;signal_b_signal_a_signal_c_signal_d&quot;,&quot;patternKey&quot;:&quot;signal_b_signal_a_signal_c_signal_d&quot;,&quot;domainKey&quot;:&quot;{{domain_key}}&quot;,&quot;report&quot;:{&quot;reportKey&quot;:&quot;signal_b_signal_a_signal_c_signal_d&quot;,&quot;patternKey&quot;:&quot;signal_b_signal_a_signal_c_signal_d&quot;,&quot;reportTitle&quot;:&quot;{{assessment_title}} report&quot;,&quot;hero&quot;:{&quot;title&quot;:&quot;{{fully_authored_report_title}}&quot;,&quot;resultStatement&quot;:&quot;{{fully_authored_result_statement}}&quot;},&quot;opening&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{editorial_introduction}}&quot;}],&quot;patternSummary&quot;:{&quot;title&quot;:&quot;Pattern at a glance&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{pattern_summary}}&quot;}]},&quot;keyInsight&quot;:{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{key_insight}}&quot;},&quot;chapters&quot;:[{&quot;chapterKey&quot;:&quot;chapter_1&quot;,&quot;chapterNumber&quot;:1,&quot;title&quot;:&quot;{{chapter_1_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_1_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_2&quot;,&quot;chapterNumber&quot;:2,&quot;title&quot;:&quot;{{chapter_2_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_2_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_3&quot;,&quot;chapterNumber&quot;:3,&quot;title&quot;:&quot;{{chapter_3_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_3_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_4&quot;,&quot;chapterNumber&quot;:4,&quot;title&quot;:&quot;{{chapter_4_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_4_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_5&quot;,&quot;chapterNumber&quot;:5,&quot;title&quot;:&quot;{{chapter_5_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_5_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_6&quot;,&quot;chapterNumber&quot;:6,&quot;title&quot;:&quot;{{chapter_6_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_6_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_7&quot;,&quot;chapterNumber&quot;:7,&quot;title&quot;:&quot;{{chapter_7_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_7_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_8&quot;,&quot;chapterNumber&quot;:8,&quot;title&quot;:&quot;{{chapter_8_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_8_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_9&quot;,&quot;chapterNumber&quot;:9,&quot;title&quot;:&quot;{{chapter_9_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_9_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_10&quot;,&quot;chapterNumber&quot;:10,&quot;title&quot;:&quot;{{chapter_10_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_10_body}}&quot;}],&quot;readerFacing&quot;:true}],&quot;closing&quot;:{&quot;synthesis&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{closing_synthesis}}&quot;}],&quot;finalLine&quot;:&quot;{{final_line}}&quot;},&quot;pdf&quot;:{&quot;title&quot;:&quot;Save this report&quot;,&quot;body&quot;:&quot;{{reference_note}}&quot;}},&quot;evidenceTemplate&quot;:{&quot;title&quot;:&quot;Evidence behind your result&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{evidence_note}}&quot;}]}}</v></c><c r="P8" t="str"><v>active</v></c><c r="Q8" t="str"><v>ready_for_import</v></c><c r="R8" t="str"><v>TRUE</v></c><c r="S8" t="str"><v>TRUE</v></c><c r="T8" t="str"><v>{&quot;generated_from&quot;:&quot;fully_authored_report_first_template&quot;,&quot;deterministic&quot;:true}</v></c><c r="U8" t="str"><v>report_first::signal_b_signal_a_signal_c_signal_d</v></c></row><row r="9"><c r="A9" t="str"><v>{{assessment_key}}</v></c><c r="B9" t="str"><v>{{package_version}}</v></c><c r="C9" t="str"><v>{{assessment_key}}-report-first</v></c><c r="D9" t="str"><v>{{package_version}}</v></c><c r="E9" t="str"><v>{{domain_key}}</v></c><c r="F9" t="str"><v>signal_b_signal_a_signal_d_signal_c</v></c><c r="G9" t="str"><v>signal_b_signal_a_signal_d_signal_c</v></c><c r="H9" t="str"><v>report_first_canonical_payload_v1</v></c><c r="I9" t="str"><v>pattern_level_score_shape_neutral</v></c><c r="J9" t="str"><v></v></c><c r="K9" t="str"><v>[]</v></c><c r="L9" t="str"><v>content/authoring/{{assessment_key}}/report-first/canonical-reports/signal_b_signal_a_signal_d_signal_c.md</v></c><c r="M9" t="str"><v>{{source_content_hash}}</v></c><c r="N9" t="str"><v>{{content_hash}}</v></c><c r="O9" t="str"><v>{&quot;metadata&quot;:{&quot;contractName&quot;:&quot;report_first_canonical_payload_v1&quot;,&quot;reportModel&quot;:&quot;report_first_canonical&quot;},&quot;reportKey&quot;:&quot;signal_b_signal_a_signal_d_signal_c&quot;,&quot;patternKey&quot;:&quot;signal_b_signal_a_signal_d_signal_c&quot;,&quot;domainKey&quot;:&quot;{{domain_key}}&quot;,&quot;report&quot;:{&quot;reportKey&quot;:&quot;signal_b_signal_a_signal_d_signal_c&quot;,&quot;patternKey&quot;:&quot;signal_b_signal_a_signal_d_signal_c&quot;,&quot;reportTitle&quot;:&quot;{{assessment_title}} report&quot;,&quot;hero&quot;:{&quot;title&quot;:&quot;{{fully_authored_report_title}}&quot;,&quot;resultStatement&quot;:&quot;{{fully_authored_result_statement}}&quot;},&quot;opening&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{editorial_introduction}}&quot;}],&quot;patternSummary&quot;:{&quot;title&quot;:&quot;Pattern at a glance&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{pattern_summary}}&quot;}]},&quot;keyInsight&quot;:{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{key_insight}}&quot;},&quot;chapters&quot;:[{&quot;chapterKey&quot;:&quot;chapter_1&quot;,&quot;chapterNumber&quot;:1,&quot;title&quot;:&quot;{{chapter_1_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_1_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_2&quot;,&quot;chapterNumber&quot;:2,&quot;title&quot;:&quot;{{chapter_2_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_2_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_3&quot;,&quot;chapterNumber&quot;:3,&quot;title&quot;:&quot;{{chapter_3_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_3_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_4&quot;,&quot;chapterNumber&quot;:4,&quot;title&quot;:&quot;{{chapter_4_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_4_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_5&quot;,&quot;chapterNumber&quot;:5,&quot;title&quot;:&quot;{{chapter_5_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_5_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_6&quot;,&quot;chapterNumber&quot;:6,&quot;title&quot;:&quot;{{chapter_6_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_6_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_7&quot;,&quot;chapterNumber&quot;:7,&quot;title&quot;:&quot;{{chapter_7_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_7_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_8&quot;,&quot;chapterNumber&quot;:8,&quot;title&quot;:&quot;{{chapter_8_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_8_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_9&quot;,&quot;chapterNumber&quot;:9,&quot;title&quot;:&quot;{{chapter_9_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_9_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_10&quot;,&quot;chapterNumber&quot;:10,&quot;title&quot;:&quot;{{chapter_10_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_10_body}}&quot;}],&quot;readerFacing&quot;:true}],&quot;closing&quot;:{&quot;synthesis&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{closing_synthesis}}&quot;}],&quot;finalLine&quot;:&quot;{{final_line}}&quot;},&quot;pdf&quot;:{&quot;title&quot;:&quot;Save this report&quot;,&quot;body&quot;:&quot;{{reference_note}}&quot;}},&quot;evidenceTemplate&quot;:{&quot;title&quot;:&quot;Evidence behind your result&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{evidence_note}}&quot;}]}}</v></c><c r="P9" t="str"><v>active</v></c><c r="Q9" t="str"><v>ready_for_import</v></c><c r="R9" t="str"><v>TRUE</v></c><c r="S9" t="str"><v>TRUE</v></c><c r="T9" t="str"><v>{&quot;generated_from&quot;:&quot;fully_authored_report_first_template&quot;,&quot;deterministic&quot;:true}</v></c><c r="U9" t="str"><v>report_first::signal_b_signal_a_signal_d_signal_c</v></c></row><row r="10"><c r="A10" t="str"><v>{{assessment_key}}</v></c><c r="B10" t="str"><v>{{package_version}}</v></c><c r="C10" t="str"><v>{{assessment_key}}-report-first</v></c><c r="D10" t="str"><v>{{package_version}}</v></c><c r="E10" t="str"><v>{{domain_key}}</v></c><c r="F10" t="str"><v>signal_b_signal_c_signal_a_signal_d</v></c><c r="G10" t="str"><v>signal_b_signal_c_signal_a_signal_d</v></c><c r="H10" t="str"><v>report_first_canonical_payload_v1</v></c><c r="I10" t="str"><v>pattern_level_score_shape_neutral</v></c><c r="J10" t="str"><v></v></c><c r="K10" t="str"><v>[]</v></c><c r="L10" t="str"><v>content/authoring/{{assessment_key}}/report-first/canonical-reports/signal_b_signal_c_signal_a_signal_d.md</v></c><c r="M10" t="str"><v>{{source_content_hash}}</v></c><c r="N10" t="str"><v>{{content_hash}}</v></c><c r="O10" t="str"><v>{&quot;metadata&quot;:{&quot;contractName&quot;:&quot;report_first_canonical_payload_v1&quot;,&quot;reportModel&quot;:&quot;report_first_canonical&quot;},&quot;reportKey&quot;:&quot;signal_b_signal_c_signal_a_signal_d&quot;,&quot;patternKey&quot;:&quot;signal_b_signal_c_signal_a_signal_d&quot;,&quot;domainKey&quot;:&quot;{{domain_key}}&quot;,&quot;report&quot;:{&quot;reportKey&quot;:&quot;signal_b_signal_c_signal_a_signal_d&quot;,&quot;patternKey&quot;:&quot;signal_b_signal_c_signal_a_signal_d&quot;,&quot;reportTitle&quot;:&quot;{{assessment_title}} report&quot;,&quot;hero&quot;:{&quot;title&quot;:&quot;{{fully_authored_report_title}}&quot;,&quot;resultStatement&quot;:&quot;{{fully_authored_result_statement}}&quot;},&quot;opening&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{editorial_introduction}}&quot;}],&quot;patternSummary&quot;:{&quot;title&quot;:&quot;Pattern at a glance&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{pattern_summary}}&quot;}]},&quot;keyInsight&quot;:{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{key_insight}}&quot;},&quot;chapters&quot;:[{&quot;chapterKey&quot;:&quot;chapter_1&quot;,&quot;chapterNumber&quot;:1,&quot;title&quot;:&quot;{{chapter_1_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_1_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_2&quot;,&quot;chapterNumber&quot;:2,&quot;title&quot;:&quot;{{chapter_2_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_2_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_3&quot;,&quot;chapterNumber&quot;:3,&quot;title&quot;:&quot;{{chapter_3_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_3_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_4&quot;,&quot;chapterNumber&quot;:4,&quot;title&quot;:&quot;{{chapter_4_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_4_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_5&quot;,&quot;chapterNumber&quot;:5,&quot;title&quot;:&quot;{{chapter_5_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_5_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_6&quot;,&quot;chapterNumber&quot;:6,&quot;title&quot;:&quot;{{chapter_6_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_6_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_7&quot;,&quot;chapterNumber&quot;:7,&quot;title&quot;:&quot;{{chapter_7_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_7_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_8&quot;,&quot;chapterNumber&quot;:8,&quot;title&quot;:&quot;{{chapter_8_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_8_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_9&quot;,&quot;chapterNumber&quot;:9,&quot;title&quot;:&quot;{{chapter_9_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_9_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_10&quot;,&quot;chapterNumber&quot;:10,&quot;title&quot;:&quot;{{chapter_10_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_10_body}}&quot;}],&quot;readerFacing&quot;:true}],&quot;closing&quot;:{&quot;synthesis&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{closing_synthesis}}&quot;}],&quot;finalLine&quot;:&quot;{{final_line}}&quot;},&quot;pdf&quot;:{&quot;title&quot;:&quot;Save this report&quot;,&quot;body&quot;:&quot;{{reference_note}}&quot;}},&quot;evidenceTemplate&quot;:{&quot;title&quot;:&quot;Evidence behind your result&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{evidence_note}}&quot;}]}}</v></c><c r="P10" t="str"><v>active</v></c><c r="Q10" t="str"><v>ready_for_import</v></c><c r="R10" t="str"><v>TRUE</v></c><c r="S10" t="str"><v>TRUE</v></c><c r="T10" t="str"><v>{&quot;generated_from&quot;:&quot;fully_authored_report_first_template&quot;,&quot;deterministic&quot;:true}</v></c><c r="U10" t="str"><v>report_first::signal_b_signal_c_signal_a_signal_d</v></c></row><row r="11"><c r="A11" t="str"><v>{{assessment_key}}</v></c><c r="B11" t="str"><v>{{package_version}}</v></c><c r="C11" t="str"><v>{{assessment_key}}-report-first</v></c><c r="D11" t="str"><v>{{package_version}}</v></c><c r="E11" t="str"><v>{{domain_key}}</v></c><c r="F11" t="str"><v>signal_b_signal_c_signal_d_signal_a</v></c><c r="G11" t="str"><v>signal_b_signal_c_signal_d_signal_a</v></c><c r="H11" t="str"><v>report_first_canonical_payload_v1</v></c><c r="I11" t="str"><v>pattern_level_score_shape_neutral</v></c><c r="J11" t="str"><v></v></c><c r="K11" t="str"><v>[]</v></c><c r="L11" t="str"><v>content/authoring/{{assessment_key}}/report-first/canonical-reports/signal_b_signal_c_signal_d_signal_a.md</v></c><c r="M11" t="str"><v>{{source_content_hash}}</v></c><c r="N11" t="str"><v>{{content_hash}}</v></c><c r="O11" t="str"><v>{&quot;metadata&quot;:{&quot;contractName&quot;:&quot;report_first_canonical_payload_v1&quot;,&quot;reportModel&quot;:&quot;report_first_canonical&quot;},&quot;reportKey&quot;:&quot;signal_b_signal_c_signal_d_signal_a&quot;,&quot;patternKey&quot;:&quot;signal_b_signal_c_signal_d_signal_a&quot;,&quot;domainKey&quot;:&quot;{{domain_key}}&quot;,&quot;report&quot;:{&quot;reportKey&quot;:&quot;signal_b_signal_c_signal_d_signal_a&quot;,&quot;patternKey&quot;:&quot;signal_b_signal_c_signal_d_signal_a&quot;,&quot;reportTitle&quot;:&quot;{{assessment_title}} report&quot;,&quot;hero&quot;:{&quot;title&quot;:&quot;{{fully_authored_report_title}}&quot;,&quot;resultStatement&quot;:&quot;{{fully_authored_result_statement}}&quot;},&quot;opening&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{editorial_introduction}}&quot;}],&quot;patternSummary&quot;:{&quot;title&quot;:&quot;Pattern at a glance&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{pattern_summary}}&quot;}]},&quot;keyInsight&quot;:{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{key_insight}}&quot;},&quot;chapters&quot;:[{&quot;chapterKey&quot;:&quot;chapter_1&quot;,&quot;chapterNumber&quot;:1,&quot;title&quot;:&quot;{{chapter_1_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_1_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_2&quot;,&quot;chapterNumber&quot;:2,&quot;title&quot;:&quot;{{chapter_2_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_2_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_3&quot;,&quot;chapterNumber&quot;:3,&quot;title&quot;:&quot;{{chapter_3_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_3_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_4&quot;,&quot;chapterNumber&quot;:4,&quot;title&quot;:&quot;{{chapter_4_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_4_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_5&quot;,&quot;chapterNumber&quot;:5,&quot;title&quot;:&quot;{{chapter_5_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_5_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_6&quot;,&quot;chapterNumber&quot;:6,&quot;title&quot;:&quot;{{chapter_6_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_6_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_7&quot;,&quot;chapterNumber&quot;:7,&quot;title&quot;:&quot;{{chapter_7_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_7_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_8&quot;,&quot;chapterNumber&quot;:8,&quot;title&quot;:&quot;{{chapter_8_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_8_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_9&quot;,&quot;chapterNumber&quot;:9,&quot;title&quot;:&quot;{{chapter_9_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_9_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_10&quot;,&quot;chapterNumber&quot;:10,&quot;title&quot;:&quot;{{chapter_10_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_10_body}}&quot;}],&quot;readerFacing&quot;:true}],&quot;closing&quot;:{&quot;synthesis&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{closing_synthesis}}&quot;}],&quot;finalLine&quot;:&quot;{{final_line}}&quot;},&quot;pdf&quot;:{&quot;title&quot;:&quot;Save this report&quot;,&quot;body&quot;:&quot;{{reference_note}}&quot;}},&quot;evidenceTemplate&quot;:{&quot;title&quot;:&quot;Evidence behind your result&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{evidence_note}}&quot;}]}}</v></c><c r="P11" t="str"><v>active</v></c><c r="Q11" t="str"><v>ready_for_import</v></c><c r="R11" t="str"><v>TRUE</v></c><c r="S11" t="str"><v>TRUE</v></c><c r="T11" t="str"><v>{&quot;generated_from&quot;:&quot;fully_authored_report_first_template&quot;,&quot;deterministic&quot;:true}</v></c><c r="U11" t="str"><v>report_first::signal_b_signal_c_signal_d_signal_a</v></c></row><row r="12"><c r="A12" t="str"><v>{{assessment_key}}</v></c><c r="B12" t="str"><v>{{package_version}}</v></c><c r="C12" t="str"><v>{{assessment_key}}-report-first</v></c><c r="D12" t="str"><v>{{package_version}}</v></c><c r="E12" t="str"><v>{{domain_key}}</v></c><c r="F12" t="str"><v>signal_b_signal_d_signal_a_signal_c</v></c><c r="G12" t="str"><v>signal_b_signal_d_signal_a_signal_c</v></c><c r="H12" t="str"><v>report_first_canonical_payload_v1</v></c><c r="I12" t="str"><v>pattern_level_score_shape_neutral</v></c><c r="J12" t="str"><v></v></c><c r="K12" t="str"><v>[]</v></c><c r="L12" t="str"><v>content/authoring/{{assessment_key}}/report-first/canonical-reports/signal_b_signal_d_signal_a_signal_c.md</v></c><c r="M12" t="str"><v>{{source_content_hash}}</v></c><c r="N12" t="str"><v>{{content_hash}}</v></c><c r="O12" t="str"><v>{&quot;metadata&quot;:{&quot;contractName&quot;:&quot;report_first_canonical_payload_v1&quot;,&quot;reportModel&quot;:&quot;report_first_canonical&quot;},&quot;reportKey&quot;:&quot;signal_b_signal_d_signal_a_signal_c&quot;,&quot;patternKey&quot;:&quot;signal_b_signal_d_signal_a_signal_c&quot;,&quot;domainKey&quot;:&quot;{{domain_key}}&quot;,&quot;report&quot;:{&quot;reportKey&quot;:&quot;signal_b_signal_d_signal_a_signal_c&quot;,&quot;patternKey&quot;:&quot;signal_b_signal_d_signal_a_signal_c&quot;,&quot;reportTitle&quot;:&quot;{{assessment_title}} report&quot;,&quot;hero&quot;:{&quot;title&quot;:&quot;{{fully_authored_report_title}}&quot;,&quot;resultStatement&quot;:&quot;{{fully_authored_result_statement}}&quot;},&quot;opening&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{editorial_introduction}}&quot;}],&quot;patternSummary&quot;:{&quot;title&quot;:&quot;Pattern at a glance&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{pattern_summary}}&quot;}]},&quot;keyInsight&quot;:{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{key_insight}}&quot;},&quot;chapters&quot;:[{&quot;chapterKey&quot;:&quot;chapter_1&quot;,&quot;chapterNumber&quot;:1,&quot;title&quot;:&quot;{{chapter_1_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_1_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_2&quot;,&quot;chapterNumber&quot;:2,&quot;title&quot;:&quot;{{chapter_2_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_2_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_3&quot;,&quot;chapterNumber&quot;:3,&quot;title&quot;:&quot;{{chapter_3_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_3_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_4&quot;,&quot;chapterNumber&quot;:4,&quot;title&quot;:&quot;{{chapter_4_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_4_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_5&quot;,&quot;chapterNumber&quot;:5,&quot;title&quot;:&quot;{{chapter_5_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_5_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_6&quot;,&quot;chapterNumber&quot;:6,&quot;title&quot;:&quot;{{chapter_6_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_6_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_7&quot;,&quot;chapterNumber&quot;:7,&quot;title&quot;:&quot;{{chapter_7_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_7_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_8&quot;,&quot;chapterNumber&quot;:8,&quot;title&quot;:&quot;{{chapter_8_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_8_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_9&quot;,&quot;chapterNumber&quot;:9,&quot;title&quot;:&quot;{{chapter_9_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_9_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_10&quot;,&quot;chapterNumber&quot;:10,&quot;title&quot;:&quot;{{chapter_10_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_10_body}}&quot;}],&quot;readerFacing&quot;:true}],&quot;closing&quot;:{&quot;synthesis&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{closing_synthesis}}&quot;}],&quot;finalLine&quot;:&quot;{{final_line}}&quot;},&quot;pdf&quot;:{&quot;title&quot;:&quot;Save this report&quot;,&quot;body&quot;:&quot;{{reference_note}}&quot;}},&quot;evidenceTemplate&quot;:{&quot;title&quot;:&quot;Evidence behind your result&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{evidence_note}}&quot;}]}}</v></c><c r="P12" t="str"><v>active</v></c><c r="Q12" t="str"><v>ready_for_import</v></c><c r="R12" t="str"><v>TRUE</v></c><c r="S12" t="str"><v>TRUE</v></c><c r="T12" t="str"><v>{&quot;generated_from&quot;:&quot;fully_authored_report_first_template&quot;,&quot;deterministic&quot;:true}</v></c><c r="U12" t="str"><v>report_first::signal_b_signal_d_signal_a_signal_c</v></c></row><row r="13"><c r="A13" t="str"><v>{{assessment_key}}</v></c><c r="B13" t="str"><v>{{package_version}}</v></c><c r="C13" t="str"><v>{{assessment_key}}-report-first</v></c><c r="D13" t="str"><v>{{package_version}}</v></c><c r="E13" t="str"><v>{{domain_key}}</v></c><c r="F13" t="str"><v>signal_b_signal_d_signal_c_signal_a</v></c><c r="G13" t="str"><v>signal_b_signal_d_signal_c_signal_a</v></c><c r="H13" t="str"><v>report_first_canonical_payload_v1</v></c><c r="I13" t="str"><v>pattern_level_score_shape_neutral</v></c><c r="J13" t="str"><v></v></c><c r="K13" t="str"><v>[]</v></c><c r="L13" t="str"><v>content/authoring/{{assessment_key}}/report-first/canonical-reports/signal_b_signal_d_signal_c_signal_a.md</v></c><c r="M13" t="str"><v>{{source_content_hash}}</v></c><c r="N13" t="str"><v>{{content_hash}}</v></c><c r="O13" t="str"><v>{&quot;metadata&quot;:{&quot;contractName&quot;:&quot;report_first_canonical_payload_v1&quot;,&quot;reportModel&quot;:&quot;report_first_canonical&quot;},&quot;reportKey&quot;:&quot;signal_b_signal_d_signal_c_signal_a&quot;,&quot;patternKey&quot;:&quot;signal_b_signal_d_signal_c_signal_a&quot;,&quot;domainKey&quot;:&quot;{{domain_key}}&quot;,&quot;report&quot;:{&quot;reportKey&quot;:&quot;signal_b_signal_d_signal_c_signal_a&quot;,&quot;patternKey&quot;:&quot;signal_b_signal_d_signal_c_signal_a&quot;,&quot;reportTitle&quot;:&quot;{{assessment_title}} report&quot;,&quot;hero&quot;:{&quot;title&quot;:&quot;{{fully_authored_report_title}}&quot;,&quot;resultStatement&quot;:&quot;{{fully_authored_result_statement}}&quot;},&quot;opening&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{editorial_introduction}}&quot;}],&quot;patternSummary&quot;:{&quot;title&quot;:&quot;Pattern at a glance&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{pattern_summary}}&quot;}]},&quot;keyInsight&quot;:{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{key_insight}}&quot;},&quot;chapters&quot;:[{&quot;chapterKey&quot;:&quot;chapter_1&quot;,&quot;chapterNumber&quot;:1,&quot;title&quot;:&quot;{{chapter_1_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_1_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_2&quot;,&quot;chapterNumber&quot;:2,&quot;title&quot;:&quot;{{chapter_2_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_2_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_3&quot;,&quot;chapterNumber&quot;:3,&quot;title&quot;:&quot;{{chapter_3_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_3_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_4&quot;,&quot;chapterNumber&quot;:4,&quot;title&quot;:&quot;{{chapter_4_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_4_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_5&quot;,&quot;chapterNumber&quot;:5,&quot;title&quot;:&quot;{{chapter_5_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_5_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_6&quot;,&quot;chapterNumber&quot;:6,&quot;title&quot;:&quot;{{chapter_6_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_6_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_7&quot;,&quot;chapterNumber&quot;:7,&quot;title&quot;:&quot;{{chapter_7_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_7_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_8&quot;,&quot;chapterNumber&quot;:8,&quot;title&quot;:&quot;{{chapter_8_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_8_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_9&quot;,&quot;chapterNumber&quot;:9,&quot;title&quot;:&quot;{{chapter_9_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_9_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_10&quot;,&quot;chapterNumber&quot;:10,&quot;title&quot;:&quot;{{chapter_10_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_10_body}}&quot;}],&quot;readerFacing&quot;:true}],&quot;closing&quot;:{&quot;synthesis&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{closing_synthesis}}&quot;}],&quot;finalLine&quot;:&quot;{{final_line}}&quot;},&quot;pdf&quot;:{&quot;title&quot;:&quot;Save this report&quot;,&quot;body&quot;:&quot;{{reference_note}}&quot;}},&quot;evidenceTemplate&quot;:{&quot;title&quot;:&quot;Evidence behind your result&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{evidence_note}}&quot;}]}}</v></c><c r="P13" t="str"><v>active</v></c><c r="Q13" t="str"><v>ready_for_import</v></c><c r="R13" t="str"><v>TRUE</v></c><c r="S13" t="str"><v>TRUE</v></c><c r="T13" t="str"><v>{&quot;generated_from&quot;:&quot;fully_authored_report_first_template&quot;,&quot;deterministic&quot;:true}</v></c><c r="U13" t="str"><v>report_first::signal_b_signal_d_signal_c_signal_a</v></c></row><row r="14"><c r="A14" t="str"><v>{{assessment_key}}</v></c><c r="B14" t="str"><v>{{package_version}}</v></c><c r="C14" t="str"><v>{{assessment_key}}-report-first</v></c><c r="D14" t="str"><v>{{package_version}}</v></c><c r="E14" t="str"><v>{{domain_key}}</v></c><c r="F14" t="str"><v>signal_c_signal_a_signal_b_signal_d</v></c><c r="G14" t="str"><v>signal_c_signal_a_signal_b_signal_d</v></c><c r="H14" t="str"><v>report_first_canonical_payload_v1</v></c><c r="I14" t="str"><v>pattern_level_score_shape_neutral</v></c><c r="J14" t="str"><v></v></c><c r="K14" t="str"><v>[]</v></c><c r="L14" t="str"><v>content/authoring/{{assessment_key}}/report-first/canonical-reports/signal_c_signal_a_signal_b_signal_d.md</v></c><c r="M14" t="str"><v>{{source_content_hash}}</v></c><c r="N14" t="str"><v>{{content_hash}}</v></c><c r="O14" t="str"><v>{&quot;metadata&quot;:{&quot;contractName&quot;:&quot;report_first_canonical_payload_v1&quot;,&quot;reportModel&quot;:&quot;report_first_canonical&quot;},&quot;reportKey&quot;:&quot;signal_c_signal_a_signal_b_signal_d&quot;,&quot;patternKey&quot;:&quot;signal_c_signal_a_signal_b_signal_d&quot;,&quot;domainKey&quot;:&quot;{{domain_key}}&quot;,&quot;report&quot;:{&quot;reportKey&quot;:&quot;signal_c_signal_a_signal_b_signal_d&quot;,&quot;patternKey&quot;:&quot;signal_c_signal_a_signal_b_signal_d&quot;,&quot;reportTitle&quot;:&quot;{{assessment_title}} report&quot;,&quot;hero&quot;:{&quot;title&quot;:&quot;{{fully_authored_report_title}}&quot;,&quot;resultStatement&quot;:&quot;{{fully_authored_result_statement}}&quot;},&quot;opening&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{editorial_introduction}}&quot;}],&quot;patternSummary&quot;:{&quot;title&quot;:&quot;Pattern at a glance&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{pattern_summary}}&quot;}]},&quot;keyInsight&quot;:{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{key_insight}}&quot;},&quot;chapters&quot;:[{&quot;chapterKey&quot;:&quot;chapter_1&quot;,&quot;chapterNumber&quot;:1,&quot;title&quot;:&quot;{{chapter_1_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_1_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_2&quot;,&quot;chapterNumber&quot;:2,&quot;title&quot;:&quot;{{chapter_2_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_2_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_3&quot;,&quot;chapterNumber&quot;:3,&quot;title&quot;:&quot;{{chapter_3_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_3_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_4&quot;,&quot;chapterNumber&quot;:4,&quot;title&quot;:&quot;{{chapter_4_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_4_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_5&quot;,&quot;chapterNumber&quot;:5,&quot;title&quot;:&quot;{{chapter_5_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_5_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_6&quot;,&quot;chapterNumber&quot;:6,&quot;title&quot;:&quot;{{chapter_6_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_6_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_7&quot;,&quot;chapterNumber&quot;:7,&quot;title&quot;:&quot;{{chapter_7_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_7_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_8&quot;,&quot;chapterNumber&quot;:8,&quot;title&quot;:&quot;{{chapter_8_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_8_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_9&quot;,&quot;chapterNumber&quot;:9,&quot;title&quot;:&quot;{{chapter_9_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_9_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_10&quot;,&quot;chapterNumber&quot;:10,&quot;title&quot;:&quot;{{chapter_10_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_10_body}}&quot;}],&quot;readerFacing&quot;:true}],&quot;closing&quot;:{&quot;synthesis&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{closing_synthesis}}&quot;}],&quot;finalLine&quot;:&quot;{{final_line}}&quot;},&quot;pdf&quot;:{&quot;title&quot;:&quot;Save this report&quot;,&quot;body&quot;:&quot;{{reference_note}}&quot;}},&quot;evidenceTemplate&quot;:{&quot;title&quot;:&quot;Evidence behind your result&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{evidence_note}}&quot;}]}}</v></c><c r="P14" t="str"><v>active</v></c><c r="Q14" t="str"><v>ready_for_import</v></c><c r="R14" t="str"><v>TRUE</v></c><c r="S14" t="str"><v>TRUE</v></c><c r="T14" t="str"><v>{&quot;generated_from&quot;:&quot;fully_authored_report_first_template&quot;,&quot;deterministic&quot;:true}</v></c><c r="U14" t="str"><v>report_first::signal_c_signal_a_signal_b_signal_d</v></c></row><row r="15"><c r="A15" t="str"><v>{{assessment_key}}</v></c><c r="B15" t="str"><v>{{package_version}}</v></c><c r="C15" t="str"><v>{{assessment_key}}-report-first</v></c><c r="D15" t="str"><v>{{package_version}}</v></c><c r="E15" t="str"><v>{{domain_key}}</v></c><c r="F15" t="str"><v>signal_c_signal_a_signal_d_signal_b</v></c><c r="G15" t="str"><v>signal_c_signal_a_signal_d_signal_b</v></c><c r="H15" t="str"><v>report_first_canonical_payload_v1</v></c><c r="I15" t="str"><v>pattern_level_score_shape_neutral</v></c><c r="J15" t="str"><v></v></c><c r="K15" t="str"><v>[]</v></c><c r="L15" t="str"><v>content/authoring/{{assessment_key}}/report-first/canonical-reports/signal_c_signal_a_signal_d_signal_b.md</v></c><c r="M15" t="str"><v>{{source_content_hash}}</v></c><c r="N15" t="str"><v>{{content_hash}}</v></c><c r="O15" t="str"><v>{&quot;metadata&quot;:{&quot;contractName&quot;:&quot;report_first_canonical_payload_v1&quot;,&quot;reportModel&quot;:&quot;report_first_canonical&quot;},&quot;reportKey&quot;:&quot;signal_c_signal_a_signal_d_signal_b&quot;,&quot;patternKey&quot;:&quot;signal_c_signal_a_signal_d_signal_b&quot;,&quot;domainKey&quot;:&quot;{{domain_key}}&quot;,&quot;report&quot;:{&quot;reportKey&quot;:&quot;signal_c_signal_a_signal_d_signal_b&quot;,&quot;patternKey&quot;:&quot;signal_c_signal_a_signal_d_signal_b&quot;,&quot;reportTitle&quot;:&quot;{{assessment_title}} report&quot;,&quot;hero&quot;:{&quot;title&quot;:&quot;{{fully_authored_report_title}}&quot;,&quot;resultStatement&quot;:&quot;{{fully_authored_result_statement}}&quot;},&quot;opening&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{editorial_introduction}}&quot;}],&quot;patternSummary&quot;:{&quot;title&quot;:&quot;Pattern at a glance&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{pattern_summary}}&quot;}]},&quot;keyInsight&quot;:{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{key_insight}}&quot;},&quot;chapters&quot;:[{&quot;chapterKey&quot;:&quot;chapter_1&quot;,&quot;chapterNumber&quot;:1,&quot;title&quot;:&quot;{{chapter_1_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_1_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_2&quot;,&quot;chapterNumber&quot;:2,&quot;title&quot;:&quot;{{chapter_2_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_2_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_3&quot;,&quot;chapterNumber&quot;:3,&quot;title&quot;:&quot;{{chapter_3_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_3_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_4&quot;,&quot;chapterNumber&quot;:4,&quot;title&quot;:&quot;{{chapter_4_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_4_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_5&quot;,&quot;chapterNumber&quot;:5,&quot;title&quot;:&quot;{{chapter_5_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_5_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_6&quot;,&quot;chapterNumber&quot;:6,&quot;title&quot;:&quot;{{chapter_6_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_6_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_7&quot;,&quot;chapterNumber&quot;:7,&quot;title&quot;:&quot;{{chapter_7_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_7_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_8&quot;,&quot;chapterNumber&quot;:8,&quot;title&quot;:&quot;{{chapter_8_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_8_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_9&quot;,&quot;chapterNumber&quot;:9,&quot;title&quot;:&quot;{{chapter_9_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_9_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_10&quot;,&quot;chapterNumber&quot;:10,&quot;title&quot;:&quot;{{chapter_10_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_10_body}}&quot;}],&quot;readerFacing&quot;:true}],&quot;closing&quot;:{&quot;synthesis&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{closing_synthesis}}&quot;}],&quot;finalLine&quot;:&quot;{{final_line}}&quot;},&quot;pdf&quot;:{&quot;title&quot;:&quot;Save this report&quot;,&quot;body&quot;:&quot;{{reference_note}}&quot;}},&quot;evidenceTemplate&quot;:{&quot;title&quot;:&quot;Evidence behind your result&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{evidence_note}}&quot;}]}}</v></c><c r="P15" t="str"><v>active</v></c><c r="Q15" t="str"><v>ready_for_import</v></c><c r="R15" t="str"><v>TRUE</v></c><c r="S15" t="str"><v>TRUE</v></c><c r="T15" t="str"><v>{&quot;generated_from&quot;:&quot;fully_authored_report_first_template&quot;,&quot;deterministic&quot;:true}</v></c><c r="U15" t="str"><v>report_first::signal_c_signal_a_signal_d_signal_b</v></c></row><row r="16"><c r="A16" t="str"><v>{{assessment_key}}</v></c><c r="B16" t="str"><v>{{package_version}}</v></c><c r="C16" t="str"><v>{{assessment_key}}-report-first</v></c><c r="D16" t="str"><v>{{package_version}}</v></c><c r="E16" t="str"><v>{{domain_key}}</v></c><c r="F16" t="str"><v>signal_c_signal_b_signal_a_signal_d</v></c><c r="G16" t="str"><v>signal_c_signal_b_signal_a_signal_d</v></c><c r="H16" t="str"><v>report_first_canonical_payload_v1</v></c><c r="I16" t="str"><v>pattern_level_score_shape_neutral</v></c><c r="J16" t="str"><v></v></c><c r="K16" t="str"><v>[]</v></c><c r="L16" t="str"><v>content/authoring/{{assessment_key}}/report-first/canonical-reports/signal_c_signal_b_signal_a_signal_d.md</v></c><c r="M16" t="str"><v>{{source_content_hash}}</v></c><c r="N16" t="str"><v>{{content_hash}}</v></c><c r="O16" t="str"><v>{&quot;metadata&quot;:{&quot;contractName&quot;:&quot;report_first_canonical_payload_v1&quot;,&quot;reportModel&quot;:&quot;report_first_canonical&quot;},&quot;reportKey&quot;:&quot;signal_c_signal_b_signal_a_signal_d&quot;,&quot;patternKey&quot;:&quot;signal_c_signal_b_signal_a_signal_d&quot;,&quot;domainKey&quot;:&quot;{{domain_key}}&quot;,&quot;report&quot;:{&quot;reportKey&quot;:&quot;signal_c_signal_b_signal_a_signal_d&quot;,&quot;patternKey&quot;:&quot;signal_c_signal_b_signal_a_signal_d&quot;,&quot;reportTitle&quot;:&quot;{{assessment_title}} report&quot;,&quot;hero&quot;:{&quot;title&quot;:&quot;{{fully_authored_report_title}}&quot;,&quot;resultStatement&quot;:&quot;{{fully_authored_result_statement}}&quot;},&quot;opening&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{editorial_introduction}}&quot;}],&quot;patternSummary&quot;:{&quot;title&quot;:&quot;Pattern at a glance&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{pattern_summary}}&quot;}]},&quot;keyInsight&quot;:{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{key_insight}}&quot;},&quot;chapters&quot;:[{&quot;chapterKey&quot;:&quot;chapter_1&quot;,&quot;chapterNumber&quot;:1,&quot;title&quot;:&quot;{{chapter_1_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_1_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_2&quot;,&quot;chapterNumber&quot;:2,&quot;title&quot;:&quot;{{chapter_2_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_2_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_3&quot;,&quot;chapterNumber&quot;:3,&quot;title&quot;:&quot;{{chapter_3_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_3_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_4&quot;,&quot;chapterNumber&quot;:4,&quot;title&quot;:&quot;{{chapter_4_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_4_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_5&quot;,&quot;chapterNumber&quot;:5,&quot;title&quot;:&quot;{{chapter_5_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_5_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_6&quot;,&quot;chapterNumber&quot;:6,&quot;title&quot;:&quot;{{chapter_6_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_6_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_7&quot;,&quot;chapterNumber&quot;:7,&quot;title&quot;:&quot;{{chapter_7_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_7_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_8&quot;,&quot;chapterNumber&quot;:8,&quot;title&quot;:&quot;{{chapter_8_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_8_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_9&quot;,&quot;chapterNumber&quot;:9,&quot;title&quot;:&quot;{{chapter_9_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_9_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_10&quot;,&quot;chapterNumber&quot;:10,&quot;title&quot;:&quot;{{chapter_10_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_10_body}}&quot;}],&quot;readerFacing&quot;:true}],&quot;closing&quot;:{&quot;synthesis&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{closing_synthesis}}&quot;}],&quot;finalLine&quot;:&quot;{{final_line}}&quot;},&quot;pdf&quot;:{&quot;title&quot;:&quot;Save this report&quot;,&quot;body&quot;:&quot;{{reference_note}}&quot;}},&quot;evidenceTemplate&quot;:{&quot;title&quot;:&quot;Evidence behind your result&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{evidence_note}}&quot;}]}}</v></c><c r="P16" t="str"><v>active</v></c><c r="Q16" t="str"><v>ready_for_import</v></c><c r="R16" t="str"><v>TRUE</v></c><c r="S16" t="str"><v>TRUE</v></c><c r="T16" t="str"><v>{&quot;generated_from&quot;:&quot;fully_authored_report_first_template&quot;,&quot;deterministic&quot;:true}</v></c><c r="U16" t="str"><v>report_first::signal_c_signal_b_signal_a_signal_d</v></c></row><row r="17"><c r="A17" t="str"><v>{{assessment_key}}</v></c><c r="B17" t="str"><v>{{package_version}}</v></c><c r="C17" t="str"><v>{{assessment_key}}-report-first</v></c><c r="D17" t="str"><v>{{package_version}}</v></c><c r="E17" t="str"><v>{{domain_key}}</v></c><c r="F17" t="str"><v>signal_c_signal_b_signal_d_signal_a</v></c><c r="G17" t="str"><v>signal_c_signal_b_signal_d_signal_a</v></c><c r="H17" t="str"><v>report_first_canonical_payload_v1</v></c><c r="I17" t="str"><v>pattern_level_score_shape_neutral</v></c><c r="J17" t="str"><v></v></c><c r="K17" t="str"><v>[]</v></c><c r="L17" t="str"><v>content/authoring/{{assessment_key}}/report-first/canonical-reports/signal_c_signal_b_signal_d_signal_a.md</v></c><c r="M17" t="str"><v>{{source_content_hash}}</v></c><c r="N17" t="str"><v>{{content_hash}}</v></c><c r="O17" t="str"><v>{&quot;metadata&quot;:{&quot;contractName&quot;:&quot;report_first_canonical_payload_v1&quot;,&quot;reportModel&quot;:&quot;report_first_canonical&quot;},&quot;reportKey&quot;:&quot;signal_c_signal_b_signal_d_signal_a&quot;,&quot;patternKey&quot;:&quot;signal_c_signal_b_signal_d_signal_a&quot;,&quot;domainKey&quot;:&quot;{{domain_key}}&quot;,&quot;report&quot;:{&quot;reportKey&quot;:&quot;signal_c_signal_b_signal_d_signal_a&quot;,&quot;patternKey&quot;:&quot;signal_c_signal_b_signal_d_signal_a&quot;,&quot;reportTitle&quot;:&quot;{{assessment_title}} report&quot;,&quot;hero&quot;:{&quot;title&quot;:&quot;{{fully_authored_report_title}}&quot;,&quot;resultStatement&quot;:&quot;{{fully_authored_result_statement}}&quot;},&quot;opening&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{editorial_introduction}}&quot;}],&quot;patternSummary&quot;:{&quot;title&quot;:&quot;Pattern at a glance&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{pattern_summary}}&quot;}]},&quot;keyInsight&quot;:{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{key_insight}}&quot;},&quot;chapters&quot;:[{&quot;chapterKey&quot;:&quot;chapter_1&quot;,&quot;chapterNumber&quot;:1,&quot;title&quot;:&quot;{{chapter_1_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_1_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_2&quot;,&quot;chapterNumber&quot;:2,&quot;title&quot;:&quot;{{chapter_2_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_2_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_3&quot;,&quot;chapterNumber&quot;:3,&quot;title&quot;:&quot;{{chapter_3_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_3_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_4&quot;,&quot;chapterNumber&quot;:4,&quot;title&quot;:&quot;{{chapter_4_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_4_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_5&quot;,&quot;chapterNumber&quot;:5,&quot;title&quot;:&quot;{{chapter_5_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_5_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_6&quot;,&quot;chapterNumber&quot;:6,&quot;title&quot;:&quot;{{chapter_6_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_6_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_7&quot;,&quot;chapterNumber&quot;:7,&quot;title&quot;:&quot;{{chapter_7_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_7_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_8&quot;,&quot;chapterNumber&quot;:8,&quot;title&quot;:&quot;{{chapter_8_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_8_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_9&quot;,&quot;chapterNumber&quot;:9,&quot;title&quot;:&quot;{{chapter_9_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_9_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_10&quot;,&quot;chapterNumber&quot;:10,&quot;title&quot;:&quot;{{chapter_10_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_10_body}}&quot;}],&quot;readerFacing&quot;:true}],&quot;closing&quot;:{&quot;synthesis&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{closing_synthesis}}&quot;}],&quot;finalLine&quot;:&quot;{{final_line}}&quot;},&quot;pdf&quot;:{&quot;title&quot;:&quot;Save this report&quot;,&quot;body&quot;:&quot;{{reference_note}}&quot;}},&quot;evidenceTemplate&quot;:{&quot;title&quot;:&quot;Evidence behind your result&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{evidence_note}}&quot;}]}}</v></c><c r="P17" t="str"><v>active</v></c><c r="Q17" t="str"><v>ready_for_import</v></c><c r="R17" t="str"><v>TRUE</v></c><c r="S17" t="str"><v>TRUE</v></c><c r="T17" t="str"><v>{&quot;generated_from&quot;:&quot;fully_authored_report_first_template&quot;,&quot;deterministic&quot;:true}</v></c><c r="U17" t="str"><v>report_first::signal_c_signal_b_signal_d_signal_a</v></c></row><row r="18"><c r="A18" t="str"><v>{{assessment_key}}</v></c><c r="B18" t="str"><v>{{package_version}}</v></c><c r="C18" t="str"><v>{{assessment_key}}-report-first</v></c><c r="D18" t="str"><v>{{package_version}}</v></c><c r="E18" t="str"><v>{{domain_key}}</v></c><c r="F18" t="str"><v>signal_c_signal_d_signal_a_signal_b</v></c><c r="G18" t="str"><v>signal_c_signal_d_signal_a_signal_b</v></c><c r="H18" t="str"><v>report_first_canonical_payload_v1</v></c><c r="I18" t="str"><v>pattern_level_score_shape_neutral</v></c><c r="J18" t="str"><v></v></c><c r="K18" t="str"><v>[]</v></c><c r="L18" t="str"><v>content/authoring/{{assessment_key}}/report-first/canonical-reports/signal_c_signal_d_signal_a_signal_b.md</v></c><c r="M18" t="str"><v>{{source_content_hash}}</v></c><c r="N18" t="str"><v>{{content_hash}}</v></c><c r="O18" t="str"><v>{&quot;metadata&quot;:{&quot;contractName&quot;:&quot;report_first_canonical_payload_v1&quot;,&quot;reportModel&quot;:&quot;report_first_canonical&quot;},&quot;reportKey&quot;:&quot;signal_c_signal_d_signal_a_signal_b&quot;,&quot;patternKey&quot;:&quot;signal_c_signal_d_signal_a_signal_b&quot;,&quot;domainKey&quot;:&quot;{{domain_key}}&quot;,&quot;report&quot;:{&quot;reportKey&quot;:&quot;signal_c_signal_d_signal_a_signal_b&quot;,&quot;patternKey&quot;:&quot;signal_c_signal_d_signal_a_signal_b&quot;,&quot;reportTitle&quot;:&quot;{{assessment_title}} report&quot;,&quot;hero&quot;:{&quot;title&quot;:&quot;{{fully_authored_report_title}}&quot;,&quot;resultStatement&quot;:&quot;{{fully_authored_result_statement}}&quot;},&quot;opening&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{editorial_introduction}}&quot;}],&quot;patternSummary&quot;:{&quot;title&quot;:&quot;Pattern at a glance&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{pattern_summary}}&quot;}]},&quot;keyInsight&quot;:{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{key_insight}}&quot;},&quot;chapters&quot;:[{&quot;chapterKey&quot;:&quot;chapter_1&quot;,&quot;chapterNumber&quot;:1,&quot;title&quot;:&quot;{{chapter_1_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_1_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_2&quot;,&quot;chapterNumber&quot;:2,&quot;title&quot;:&quot;{{chapter_2_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_2_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_3&quot;,&quot;chapterNumber&quot;:3,&quot;title&quot;:&quot;{{chapter_3_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_3_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_4&quot;,&quot;chapterNumber&quot;:4,&quot;title&quot;:&quot;{{chapter_4_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_4_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_5&quot;,&quot;chapterNumber&quot;:5,&quot;title&quot;:&quot;{{chapter_5_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_5_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_6&quot;,&quot;chapterNumber&quot;:6,&quot;title&quot;:&quot;{{chapter_6_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_6_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_7&quot;,&quot;chapterNumber&quot;:7,&quot;title&quot;:&quot;{{chapter_7_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_7_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_8&quot;,&quot;chapterNumber&quot;:8,&quot;title&quot;:&quot;{{chapter_8_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_8_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_9&quot;,&quot;chapterNumber&quot;:9,&quot;title&quot;:&quot;{{chapter_9_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_9_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_10&quot;,&quot;chapterNumber&quot;:10,&quot;title&quot;:&quot;{{chapter_10_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_10_body}}&quot;}],&quot;readerFacing&quot;:true}],&quot;closing&quot;:{&quot;synthesis&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{closing_synthesis}}&quot;}],&quot;finalLine&quot;:&quot;{{final_line}}&quot;},&quot;pdf&quot;:{&quot;title&quot;:&quot;Save this report&quot;,&quot;body&quot;:&quot;{{reference_note}}&quot;}},&quot;evidenceTemplate&quot;:{&quot;title&quot;:&quot;Evidence behind your result&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{evidence_note}}&quot;}]}}</v></c><c r="P18" t="str"><v>active</v></c><c r="Q18" t="str"><v>ready_for_import</v></c><c r="R18" t="str"><v>TRUE</v></c><c r="S18" t="str"><v>TRUE</v></c><c r="T18" t="str"><v>{&quot;generated_from&quot;:&quot;fully_authored_report_first_template&quot;,&quot;deterministic&quot;:true}</v></c><c r="U18" t="str"><v>report_first::signal_c_signal_d_signal_a_signal_b</v></c></row><row r="19"><c r="A19" t="str"><v>{{assessment_key}}</v></c><c r="B19" t="str"><v>{{package_version}}</v></c><c r="C19" t="str"><v>{{assessment_key}}-report-first</v></c><c r="D19" t="str"><v>{{package_version}}</v></c><c r="E19" t="str"><v>{{domain_key}}</v></c><c r="F19" t="str"><v>signal_c_signal_d_signal_b_signal_a</v></c><c r="G19" t="str"><v>signal_c_signal_d_signal_b_signal_a</v></c><c r="H19" t="str"><v>report_first_canonical_payload_v1</v></c><c r="I19" t="str"><v>pattern_level_score_shape_neutral</v></c><c r="J19" t="str"><v></v></c><c r="K19" t="str"><v>[]</v></c><c r="L19" t="str"><v>content/authoring/{{assessment_key}}/report-first/canonical-reports/signal_c_signal_d_signal_b_signal_a.md</v></c><c r="M19" t="str"><v>{{source_content_hash}}</v></c><c r="N19" t="str"><v>{{content_hash}}</v></c><c r="O19" t="str"><v>{&quot;metadata&quot;:{&quot;contractName&quot;:&quot;report_first_canonical_payload_v1&quot;,&quot;reportModel&quot;:&quot;report_first_canonical&quot;},&quot;reportKey&quot;:&quot;signal_c_signal_d_signal_b_signal_a&quot;,&quot;patternKey&quot;:&quot;signal_c_signal_d_signal_b_signal_a&quot;,&quot;domainKey&quot;:&quot;{{domain_key}}&quot;,&quot;report&quot;:{&quot;reportKey&quot;:&quot;signal_c_signal_d_signal_b_signal_a&quot;,&quot;patternKey&quot;:&quot;signal_c_signal_d_signal_b_signal_a&quot;,&quot;reportTitle&quot;:&quot;{{assessment_title}} report&quot;,&quot;hero&quot;:{&quot;title&quot;:&quot;{{fully_authored_report_title}}&quot;,&quot;resultStatement&quot;:&quot;{{fully_authored_result_statement}}&quot;},&quot;opening&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{editorial_introduction}}&quot;}],&quot;patternSummary&quot;:{&quot;title&quot;:&quot;Pattern at a glance&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{pattern_summary}}&quot;}]},&quot;keyInsight&quot;:{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{key_insight}}&quot;},&quot;chapters&quot;:[{&quot;chapterKey&quot;:&quot;chapter_1&quot;,&quot;chapterNumber&quot;:1,&quot;title&quot;:&quot;{{chapter_1_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_1_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_2&quot;,&quot;chapterNumber&quot;:2,&quot;title&quot;:&quot;{{chapter_2_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_2_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_3&quot;,&quot;chapterNumber&quot;:3,&quot;title&quot;:&quot;{{chapter_3_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_3_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_4&quot;,&quot;chapterNumber&quot;:4,&quot;title&quot;:&quot;{{chapter_4_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_4_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_5&quot;,&quot;chapterNumber&quot;:5,&quot;title&quot;:&quot;{{chapter_5_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_5_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_6&quot;,&quot;chapterNumber&quot;:6,&quot;title&quot;:&quot;{{chapter_6_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_6_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_7&quot;,&quot;chapterNumber&quot;:7,&quot;title&quot;:&quot;{{chapter_7_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_7_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_8&quot;,&quot;chapterNumber&quot;:8,&quot;title&quot;:&quot;{{chapter_8_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_8_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_9&quot;,&quot;chapterNumber&quot;:9,&quot;title&quot;:&quot;{{chapter_9_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_9_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_10&quot;,&quot;chapterNumber&quot;:10,&quot;title&quot;:&quot;{{chapter_10_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_10_body}}&quot;}],&quot;readerFacing&quot;:true}],&quot;closing&quot;:{&quot;synthesis&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{closing_synthesis}}&quot;}],&quot;finalLine&quot;:&quot;{{final_line}}&quot;},&quot;pdf&quot;:{&quot;title&quot;:&quot;Save this report&quot;,&quot;body&quot;:&quot;{{reference_note}}&quot;}},&quot;evidenceTemplate&quot;:{&quot;title&quot;:&quot;Evidence behind your result&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{evidence_note}}&quot;}]}}</v></c><c r="P19" t="str"><v>active</v></c><c r="Q19" t="str"><v>ready_for_import</v></c><c r="R19" t="str"><v>TRUE</v></c><c r="S19" t="str"><v>TRUE</v></c><c r="T19" t="str"><v>{&quot;generated_from&quot;:&quot;fully_authored_report_first_template&quot;,&quot;deterministic&quot;:true}</v></c><c r="U19" t="str"><v>report_first::signal_c_signal_d_signal_b_signal_a</v></c></row><row r="20"><c r="A20" t="str"><v>{{assessment_key}}</v></c><c r="B20" t="str"><v>{{package_version}}</v></c><c r="C20" t="str"><v>{{assessment_key}}-report-first</v></c><c r="D20" t="str"><v>{{package_version}}</v></c><c r="E20" t="str"><v>{{domain_key}}</v></c><c r="F20" t="str"><v>signal_d_signal_a_signal_b_signal_c</v></c><c r="G20" t="str"><v>signal_d_signal_a_signal_b_signal_c</v></c><c r="H20" t="str"><v>report_first_canonical_payload_v1</v></c><c r="I20" t="str"><v>pattern_level_score_shape_neutral</v></c><c r="J20" t="str"><v></v></c><c r="K20" t="str"><v>[]</v></c><c r="L20" t="str"><v>content/authoring/{{assessment_key}}/report-first/canonical-reports/signal_d_signal_a_signal_b_signal_c.md</v></c><c r="M20" t="str"><v>{{source_content_hash}}</v></c><c r="N20" t="str"><v>{{content_hash}}</v></c><c r="O20" t="str"><v>{&quot;metadata&quot;:{&quot;contractName&quot;:&quot;report_first_canonical_payload_v1&quot;,&quot;reportModel&quot;:&quot;report_first_canonical&quot;},&quot;reportKey&quot;:&quot;signal_d_signal_a_signal_b_signal_c&quot;,&quot;patternKey&quot;:&quot;signal_d_signal_a_signal_b_signal_c&quot;,&quot;domainKey&quot;:&quot;{{domain_key}}&quot;,&quot;report&quot;:{&quot;reportKey&quot;:&quot;signal_d_signal_a_signal_b_signal_c&quot;,&quot;patternKey&quot;:&quot;signal_d_signal_a_signal_b_signal_c&quot;,&quot;reportTitle&quot;:&quot;{{assessment_title}} report&quot;,&quot;hero&quot;:{&quot;title&quot;:&quot;{{fully_authored_report_title}}&quot;,&quot;resultStatement&quot;:&quot;{{fully_authored_result_statement}}&quot;},&quot;opening&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{editorial_introduction}}&quot;}],&quot;patternSummary&quot;:{&quot;title&quot;:&quot;Pattern at a glance&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{pattern_summary}}&quot;}]},&quot;keyInsight&quot;:{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{key_insight}}&quot;},&quot;chapters&quot;:[{&quot;chapterKey&quot;:&quot;chapter_1&quot;,&quot;chapterNumber&quot;:1,&quot;title&quot;:&quot;{{chapter_1_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_1_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_2&quot;,&quot;chapterNumber&quot;:2,&quot;title&quot;:&quot;{{chapter_2_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_2_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_3&quot;,&quot;chapterNumber&quot;:3,&quot;title&quot;:&quot;{{chapter_3_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_3_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_4&quot;,&quot;chapterNumber&quot;:4,&quot;title&quot;:&quot;{{chapter_4_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_4_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_5&quot;,&quot;chapterNumber&quot;:5,&quot;title&quot;:&quot;{{chapter_5_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_5_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_6&quot;,&quot;chapterNumber&quot;:6,&quot;title&quot;:&quot;{{chapter_6_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_6_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_7&quot;,&quot;chapterNumber&quot;:7,&quot;title&quot;:&quot;{{chapter_7_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_7_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_8&quot;,&quot;chapterNumber&quot;:8,&quot;title&quot;:&quot;{{chapter_8_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_8_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_9&quot;,&quot;chapterNumber&quot;:9,&quot;title&quot;:&quot;{{chapter_9_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_9_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_10&quot;,&quot;chapterNumber&quot;:10,&quot;title&quot;:&quot;{{chapter_10_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_10_body}}&quot;}],&quot;readerFacing&quot;:true}],&quot;closing&quot;:{&quot;synthesis&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{closing_synthesis}}&quot;}],&quot;finalLine&quot;:&quot;{{final_line}}&quot;},&quot;pdf&quot;:{&quot;title&quot;:&quot;Save this report&quot;,&quot;body&quot;:&quot;{{reference_note}}&quot;}},&quot;evidenceTemplate&quot;:{&quot;title&quot;:&quot;Evidence behind your result&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{evidence_note}}&quot;}]}}</v></c><c r="P20" t="str"><v>active</v></c><c r="Q20" t="str"><v>ready_for_import</v></c><c r="R20" t="str"><v>TRUE</v></c><c r="S20" t="str"><v>TRUE</v></c><c r="T20" t="str"><v>{&quot;generated_from&quot;:&quot;fully_authored_report_first_template&quot;,&quot;deterministic&quot;:true}</v></c><c r="U20" t="str"><v>report_first::signal_d_signal_a_signal_b_signal_c</v></c></row><row r="21"><c r="A21" t="str"><v>{{assessment_key}}</v></c><c r="B21" t="str"><v>{{package_version}}</v></c><c r="C21" t="str"><v>{{assessment_key}}-report-first</v></c><c r="D21" t="str"><v>{{package_version}}</v></c><c r="E21" t="str"><v>{{domain_key}}</v></c><c r="F21" t="str"><v>signal_d_signal_a_signal_c_signal_b</v></c><c r="G21" t="str"><v>signal_d_signal_a_signal_c_signal_b</v></c><c r="H21" t="str"><v>report_first_canonical_payload_v1</v></c><c r="I21" t="str"><v>pattern_level_score_shape_neutral</v></c><c r="J21" t="str"><v></v></c><c r="K21" t="str"><v>[]</v></c><c r="L21" t="str"><v>content/authoring/{{assessment_key}}/report-first/canonical-reports/signal_d_signal_a_signal_c_signal_b.md</v></c><c r="M21" t="str"><v>{{source_content_hash}}</v></c><c r="N21" t="str"><v>{{content_hash}}</v></c><c r="O21" t="str"><v>{&quot;metadata&quot;:{&quot;contractName&quot;:&quot;report_first_canonical_payload_v1&quot;,&quot;reportModel&quot;:&quot;report_first_canonical&quot;},&quot;reportKey&quot;:&quot;signal_d_signal_a_signal_c_signal_b&quot;,&quot;patternKey&quot;:&quot;signal_d_signal_a_signal_c_signal_b&quot;,&quot;domainKey&quot;:&quot;{{domain_key}}&quot;,&quot;report&quot;:{&quot;reportKey&quot;:&quot;signal_d_signal_a_signal_c_signal_b&quot;,&quot;patternKey&quot;:&quot;signal_d_signal_a_signal_c_signal_b&quot;,&quot;reportTitle&quot;:&quot;{{assessment_title}} report&quot;,&quot;hero&quot;:{&quot;title&quot;:&quot;{{fully_authored_report_title}}&quot;,&quot;resultStatement&quot;:&quot;{{fully_authored_result_statement}}&quot;},&quot;opening&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{editorial_introduction}}&quot;}],&quot;patternSummary&quot;:{&quot;title&quot;:&quot;Pattern at a glance&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{pattern_summary}}&quot;}]},&quot;keyInsight&quot;:{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{key_insight}}&quot;},&quot;chapters&quot;:[{&quot;chapterKey&quot;:&quot;chapter_1&quot;,&quot;chapterNumber&quot;:1,&quot;title&quot;:&quot;{{chapter_1_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_1_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_2&quot;,&quot;chapterNumber&quot;:2,&quot;title&quot;:&quot;{{chapter_2_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_2_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_3&quot;,&quot;chapterNumber&quot;:3,&quot;title&quot;:&quot;{{chapter_3_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_3_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_4&quot;,&quot;chapterNumber&quot;:4,&quot;title&quot;:&quot;{{chapter_4_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_4_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_5&quot;,&quot;chapterNumber&quot;:5,&quot;title&quot;:&quot;{{chapter_5_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_5_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_6&quot;,&quot;chapterNumber&quot;:6,&quot;title&quot;:&quot;{{chapter_6_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_6_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_7&quot;,&quot;chapterNumber&quot;:7,&quot;title&quot;:&quot;{{chapter_7_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_7_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_8&quot;,&quot;chapterNumber&quot;:8,&quot;title&quot;:&quot;{{chapter_8_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_8_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_9&quot;,&quot;chapterNumber&quot;:9,&quot;title&quot;:&quot;{{chapter_9_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_9_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_10&quot;,&quot;chapterNumber&quot;:10,&quot;title&quot;:&quot;{{chapter_10_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_10_body}}&quot;}],&quot;readerFacing&quot;:true}],&quot;closing&quot;:{&quot;synthesis&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{closing_synthesis}}&quot;}],&quot;finalLine&quot;:&quot;{{final_line}}&quot;},&quot;pdf&quot;:{&quot;title&quot;:&quot;Save this report&quot;,&quot;body&quot;:&quot;{{reference_note}}&quot;}},&quot;evidenceTemplate&quot;:{&quot;title&quot;:&quot;Evidence behind your result&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{evidence_note}}&quot;}]}}</v></c><c r="P21" t="str"><v>active</v></c><c r="Q21" t="str"><v>ready_for_import</v></c><c r="R21" t="str"><v>TRUE</v></c><c r="S21" t="str"><v>TRUE</v></c><c r="T21" t="str"><v>{&quot;generated_from&quot;:&quot;fully_authored_report_first_template&quot;,&quot;deterministic&quot;:true}</v></c><c r="U21" t="str"><v>report_first::signal_d_signal_a_signal_c_signal_b</v></c></row><row r="22"><c r="A22" t="str"><v>{{assessment_key}}</v></c><c r="B22" t="str"><v>{{package_version}}</v></c><c r="C22" t="str"><v>{{assessment_key}}-report-first</v></c><c r="D22" t="str"><v>{{package_version}}</v></c><c r="E22" t="str"><v>{{domain_key}}</v></c><c r="F22" t="str"><v>signal_d_signal_b_signal_a_signal_c</v></c><c r="G22" t="str"><v>signal_d_signal_b_signal_a_signal_c</v></c><c r="H22" t="str"><v>report_first_canonical_payload_v1</v></c><c r="I22" t="str"><v>pattern_level_score_shape_neutral</v></c><c r="J22" t="str"><v></v></c><c r="K22" t="str"><v>[]</v></c><c r="L22" t="str"><v>content/authoring/{{assessment_key}}/report-first/canonical-reports/signal_d_signal_b_signal_a_signal_c.md</v></c><c r="M22" t="str"><v>{{source_content_hash}}</v></c><c r="N22" t="str"><v>{{content_hash}}</v></c><c r="O22" t="str"><v>{&quot;metadata&quot;:{&quot;contractName&quot;:&quot;report_first_canonical_payload_v1&quot;,&quot;reportModel&quot;:&quot;report_first_canonical&quot;},&quot;reportKey&quot;:&quot;signal_d_signal_b_signal_a_signal_c&quot;,&quot;patternKey&quot;:&quot;signal_d_signal_b_signal_a_signal_c&quot;,&quot;domainKey&quot;:&quot;{{domain_key}}&quot;,&quot;report&quot;:{&quot;reportKey&quot;:&quot;signal_d_signal_b_signal_a_signal_c&quot;,&quot;patternKey&quot;:&quot;signal_d_signal_b_signal_a_signal_c&quot;,&quot;reportTitle&quot;:&quot;{{assessment_title}} report&quot;,&quot;hero&quot;:{&quot;title&quot;:&quot;{{fully_authored_report_title}}&quot;,&quot;resultStatement&quot;:&quot;{{fully_authored_result_statement}}&quot;},&quot;opening&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{editorial_introduction}}&quot;}],&quot;patternSummary&quot;:{&quot;title&quot;:&quot;Pattern at a glance&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{pattern_summary}}&quot;}]},&quot;keyInsight&quot;:{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{key_insight}}&quot;},&quot;chapters&quot;:[{&quot;chapterKey&quot;:&quot;chapter_1&quot;,&quot;chapterNumber&quot;:1,&quot;title&quot;:&quot;{{chapter_1_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_1_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_2&quot;,&quot;chapterNumber&quot;:2,&quot;title&quot;:&quot;{{chapter_2_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_2_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_3&quot;,&quot;chapterNumber&quot;:3,&quot;title&quot;:&quot;{{chapter_3_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_3_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_4&quot;,&quot;chapterNumber&quot;:4,&quot;title&quot;:&quot;{{chapter_4_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_4_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_5&quot;,&quot;chapterNumber&quot;:5,&quot;title&quot;:&quot;{{chapter_5_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_5_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_6&quot;,&quot;chapterNumber&quot;:6,&quot;title&quot;:&quot;{{chapter_6_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_6_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_7&quot;,&quot;chapterNumber&quot;:7,&quot;title&quot;:&quot;{{chapter_7_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_7_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_8&quot;,&quot;chapterNumber&quot;:8,&quot;title&quot;:&quot;{{chapter_8_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_8_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_9&quot;,&quot;chapterNumber&quot;:9,&quot;title&quot;:&quot;{{chapter_9_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_9_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_10&quot;,&quot;chapterNumber&quot;:10,&quot;title&quot;:&quot;{{chapter_10_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_10_body}}&quot;}],&quot;readerFacing&quot;:true}],&quot;closing&quot;:{&quot;synthesis&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{closing_synthesis}}&quot;}],&quot;finalLine&quot;:&quot;{{final_line}}&quot;},&quot;pdf&quot;:{&quot;title&quot;:&quot;Save this report&quot;,&quot;body&quot;:&quot;{{reference_note}}&quot;}},&quot;evidenceTemplate&quot;:{&quot;title&quot;:&quot;Evidence behind your result&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{evidence_note}}&quot;}]}}</v></c><c r="P22" t="str"><v>active</v></c><c r="Q22" t="str"><v>ready_for_import</v></c><c r="R22" t="str"><v>TRUE</v></c><c r="S22" t="str"><v>TRUE</v></c><c r="T22" t="str"><v>{&quot;generated_from&quot;:&quot;fully_authored_report_first_template&quot;,&quot;deterministic&quot;:true}</v></c><c r="U22" t="str"><v>report_first::signal_d_signal_b_signal_a_signal_c</v></c></row><row r="23"><c r="A23" t="str"><v>{{assessment_key}}</v></c><c r="B23" t="str"><v>{{package_version}}</v></c><c r="C23" t="str"><v>{{assessment_key}}-report-first</v></c><c r="D23" t="str"><v>{{package_version}}</v></c><c r="E23" t="str"><v>{{domain_key}}</v></c><c r="F23" t="str"><v>signal_d_signal_b_signal_c_signal_a</v></c><c r="G23" t="str"><v>signal_d_signal_b_signal_c_signal_a</v></c><c r="H23" t="str"><v>report_first_canonical_payload_v1</v></c><c r="I23" t="str"><v>pattern_level_score_shape_neutral</v></c><c r="J23" t="str"><v></v></c><c r="K23" t="str"><v>[]</v></c><c r="L23" t="str"><v>content/authoring/{{assessment_key}}/report-first/canonical-reports/signal_d_signal_b_signal_c_signal_a.md</v></c><c r="M23" t="str"><v>{{source_content_hash}}</v></c><c r="N23" t="str"><v>{{content_hash}}</v></c><c r="O23" t="str"><v>{&quot;metadata&quot;:{&quot;contractName&quot;:&quot;report_first_canonical_payload_v1&quot;,&quot;reportModel&quot;:&quot;report_first_canonical&quot;},&quot;reportKey&quot;:&quot;signal_d_signal_b_signal_c_signal_a&quot;,&quot;patternKey&quot;:&quot;signal_d_signal_b_signal_c_signal_a&quot;,&quot;domainKey&quot;:&quot;{{domain_key}}&quot;,&quot;report&quot;:{&quot;reportKey&quot;:&quot;signal_d_signal_b_signal_c_signal_a&quot;,&quot;patternKey&quot;:&quot;signal_d_signal_b_signal_c_signal_a&quot;,&quot;reportTitle&quot;:&quot;{{assessment_title}} report&quot;,&quot;hero&quot;:{&quot;title&quot;:&quot;{{fully_authored_report_title}}&quot;,&quot;resultStatement&quot;:&quot;{{fully_authored_result_statement}}&quot;},&quot;opening&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{editorial_introduction}}&quot;}],&quot;patternSummary&quot;:{&quot;title&quot;:&quot;Pattern at a glance&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{pattern_summary}}&quot;}]},&quot;keyInsight&quot;:{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{key_insight}}&quot;},&quot;chapters&quot;:[{&quot;chapterKey&quot;:&quot;chapter_1&quot;,&quot;chapterNumber&quot;:1,&quot;title&quot;:&quot;{{chapter_1_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_1_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_2&quot;,&quot;chapterNumber&quot;:2,&quot;title&quot;:&quot;{{chapter_2_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_2_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_3&quot;,&quot;chapterNumber&quot;:3,&quot;title&quot;:&quot;{{chapter_3_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_3_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_4&quot;,&quot;chapterNumber&quot;:4,&quot;title&quot;:&quot;{{chapter_4_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_4_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_5&quot;,&quot;chapterNumber&quot;:5,&quot;title&quot;:&quot;{{chapter_5_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_5_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_6&quot;,&quot;chapterNumber&quot;:6,&quot;title&quot;:&quot;{{chapter_6_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_6_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_7&quot;,&quot;chapterNumber&quot;:7,&quot;title&quot;:&quot;{{chapter_7_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_7_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_8&quot;,&quot;chapterNumber&quot;:8,&quot;title&quot;:&quot;{{chapter_8_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_8_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_9&quot;,&quot;chapterNumber&quot;:9,&quot;title&quot;:&quot;{{chapter_9_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_9_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_10&quot;,&quot;chapterNumber&quot;:10,&quot;title&quot;:&quot;{{chapter_10_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_10_body}}&quot;}],&quot;readerFacing&quot;:true}],&quot;closing&quot;:{&quot;synthesis&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{closing_synthesis}}&quot;}],&quot;finalLine&quot;:&quot;{{final_line}}&quot;},&quot;pdf&quot;:{&quot;title&quot;:&quot;Save this report&quot;,&quot;body&quot;:&quot;{{reference_note}}&quot;}},&quot;evidenceTemplate&quot;:{&quot;title&quot;:&quot;Evidence behind your result&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{evidence_note}}&quot;}]}}</v></c><c r="P23" t="str"><v>active</v></c><c r="Q23" t="str"><v>ready_for_import</v></c><c r="R23" t="str"><v>TRUE</v></c><c r="S23" t="str"><v>TRUE</v></c><c r="T23" t="str"><v>{&quot;generated_from&quot;:&quot;fully_authored_report_first_template&quot;,&quot;deterministic&quot;:true}</v></c><c r="U23" t="str"><v>report_first::signal_d_signal_b_signal_c_signal_a</v></c></row><row r="24"><c r="A24" t="str"><v>{{assessment_key}}</v></c><c r="B24" t="str"><v>{{package_version}}</v></c><c r="C24" t="str"><v>{{assessment_key}}-report-first</v></c><c r="D24" t="str"><v>{{package_version}}</v></c><c r="E24" t="str"><v>{{domain_key}}</v></c><c r="F24" t="str"><v>signal_d_signal_c_signal_a_signal_b</v></c><c r="G24" t="str"><v>signal_d_signal_c_signal_a_signal_b</v></c><c r="H24" t="str"><v>report_first_canonical_payload_v1</v></c><c r="I24" t="str"><v>pattern_level_score_shape_neutral</v></c><c r="J24" t="str"><v></v></c><c r="K24" t="str"><v>[]</v></c><c r="L24" t="str"><v>content/authoring/{{assessment_key}}/report-first/canonical-reports/signal_d_signal_c_signal_a_signal_b.md</v></c><c r="M24" t="str"><v>{{source_content_hash}}</v></c><c r="N24" t="str"><v>{{content_hash}}</v></c><c r="O24" t="str"><v>{&quot;metadata&quot;:{&quot;contractName&quot;:&quot;report_first_canonical_payload_v1&quot;,&quot;reportModel&quot;:&quot;report_first_canonical&quot;},&quot;reportKey&quot;:&quot;signal_d_signal_c_signal_a_signal_b&quot;,&quot;patternKey&quot;:&quot;signal_d_signal_c_signal_a_signal_b&quot;,&quot;domainKey&quot;:&quot;{{domain_key}}&quot;,&quot;report&quot;:{&quot;reportKey&quot;:&quot;signal_d_signal_c_signal_a_signal_b&quot;,&quot;patternKey&quot;:&quot;signal_d_signal_c_signal_a_signal_b&quot;,&quot;reportTitle&quot;:&quot;{{assessment_title}} report&quot;,&quot;hero&quot;:{&quot;title&quot;:&quot;{{fully_authored_report_title}}&quot;,&quot;resultStatement&quot;:&quot;{{fully_authored_result_statement}}&quot;},&quot;opening&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{editorial_introduction}}&quot;}],&quot;patternSummary&quot;:{&quot;title&quot;:&quot;Pattern at a glance&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{pattern_summary}}&quot;}]},&quot;keyInsight&quot;:{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{key_insight}}&quot;},&quot;chapters&quot;:[{&quot;chapterKey&quot;:&quot;chapter_1&quot;,&quot;chapterNumber&quot;:1,&quot;title&quot;:&quot;{{chapter_1_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_1_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_2&quot;,&quot;chapterNumber&quot;:2,&quot;title&quot;:&quot;{{chapter_2_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_2_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_3&quot;,&quot;chapterNumber&quot;:3,&quot;title&quot;:&quot;{{chapter_3_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_3_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_4&quot;,&quot;chapterNumber&quot;:4,&quot;title&quot;:&quot;{{chapter_4_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_4_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_5&quot;,&quot;chapterNumber&quot;:5,&quot;title&quot;:&quot;{{chapter_5_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_5_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_6&quot;,&quot;chapterNumber&quot;:6,&quot;title&quot;:&quot;{{chapter_6_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_6_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_7&quot;,&quot;chapterNumber&quot;:7,&quot;title&quot;:&quot;{{chapter_7_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_7_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_8&quot;,&quot;chapterNumber&quot;:8,&quot;title&quot;:&quot;{{chapter_8_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_8_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_9&quot;,&quot;chapterNumber&quot;:9,&quot;title&quot;:&quot;{{chapter_9_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_9_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_10&quot;,&quot;chapterNumber&quot;:10,&quot;title&quot;:&quot;{{chapter_10_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_10_body}}&quot;}],&quot;readerFacing&quot;:true}],&quot;closing&quot;:{&quot;synthesis&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{closing_synthesis}}&quot;}],&quot;finalLine&quot;:&quot;{{final_line}}&quot;},&quot;pdf&quot;:{&quot;title&quot;:&quot;Save this report&quot;,&quot;body&quot;:&quot;{{reference_note}}&quot;}},&quot;evidenceTemplate&quot;:{&quot;title&quot;:&quot;Evidence behind your result&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{evidence_note}}&quot;}]}}</v></c><c r="P24" t="str"><v>active</v></c><c r="Q24" t="str"><v>ready_for_import</v></c><c r="R24" t="str"><v>TRUE</v></c><c r="S24" t="str"><v>TRUE</v></c><c r="T24" t="str"><v>{&quot;generated_from&quot;:&quot;fully_authored_report_first_template&quot;,&quot;deterministic&quot;:true}</v></c><c r="U24" t="str"><v>report_first::signal_d_signal_c_signal_a_signal_b</v></c></row><row r="25"><c r="A25" t="str"><v>{{assessment_key}}</v></c><c r="B25" t="str"><v>{{package_version}}</v></c><c r="C25" t="str"><v>{{assessment_key}}-report-first</v></c><c r="D25" t="str"><v>{{package_version}}</v></c><c r="E25" t="str"><v>{{domain_key}}</v></c><c r="F25" t="str"><v>signal_d_signal_c_signal_b_signal_a</v></c><c r="G25" t="str"><v>signal_d_signal_c_signal_b_signal_a</v></c><c r="H25" t="str"><v>report_first_canonical_payload_v1</v></c><c r="I25" t="str"><v>pattern_level_score_shape_neutral</v></c><c r="J25" t="str"><v></v></c><c r="K25" t="str"><v>[]</v></c><c r="L25" t="str"><v>content/authoring/{{assessment_key}}/report-first/canonical-reports/signal_d_signal_c_signal_b_signal_a.md</v></c><c r="M25" t="str"><v>{{source_content_hash}}</v></c><c r="N25" t="str"><v>{{content_hash}}</v></c><c r="O25" t="str"><v>{&quot;metadata&quot;:{&quot;contractName&quot;:&quot;report_first_canonical_payload_v1&quot;,&quot;reportModel&quot;:&quot;report_first_canonical&quot;},&quot;reportKey&quot;:&quot;signal_d_signal_c_signal_b_signal_a&quot;,&quot;patternKey&quot;:&quot;signal_d_signal_c_signal_b_signal_a&quot;,&quot;domainKey&quot;:&quot;{{domain_key}}&quot;,&quot;report&quot;:{&quot;reportKey&quot;:&quot;signal_d_signal_c_signal_b_signal_a&quot;,&quot;patternKey&quot;:&quot;signal_d_signal_c_signal_b_signal_a&quot;,&quot;reportTitle&quot;:&quot;{{assessment_title}} report&quot;,&quot;hero&quot;:{&quot;title&quot;:&quot;{{fully_authored_report_title}}&quot;,&quot;resultStatement&quot;:&quot;{{fully_authored_result_statement}}&quot;},&quot;opening&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{editorial_introduction}}&quot;}],&quot;patternSummary&quot;:{&quot;title&quot;:&quot;Pattern at a glance&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{pattern_summary}}&quot;}]},&quot;keyInsight&quot;:{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{key_insight}}&quot;},&quot;chapters&quot;:[{&quot;chapterKey&quot;:&quot;chapter_1&quot;,&quot;chapterNumber&quot;:1,&quot;title&quot;:&quot;{{chapter_1_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_1_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_2&quot;,&quot;chapterNumber&quot;:2,&quot;title&quot;:&quot;{{chapter_2_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_2_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_3&quot;,&quot;chapterNumber&quot;:3,&quot;title&quot;:&quot;{{chapter_3_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_3_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_4&quot;,&quot;chapterNumber&quot;:4,&quot;title&quot;:&quot;{{chapter_4_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_4_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_5&quot;,&quot;chapterNumber&quot;:5,&quot;title&quot;:&quot;{{chapter_5_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_5_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_6&quot;,&quot;chapterNumber&quot;:6,&quot;title&quot;:&quot;{{chapter_6_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_6_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_7&quot;,&quot;chapterNumber&quot;:7,&quot;title&quot;:&quot;{{chapter_7_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_7_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_8&quot;,&quot;chapterNumber&quot;:8,&quot;title&quot;:&quot;{{chapter_8_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_8_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_9&quot;,&quot;chapterNumber&quot;:9,&quot;title&quot;:&quot;{{chapter_9_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_9_body}}&quot;}],&quot;readerFacing&quot;:true},{&quot;chapterKey&quot;:&quot;chapter_10&quot;,&quot;chapterNumber&quot;:10,&quot;title&quot;:&quot;{{chapter_10_title}}&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{chapter_10_body}}&quot;}],&quot;readerFacing&quot;:true}],&quot;closing&quot;:{&quot;synthesis&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{closing_synthesis}}&quot;}],&quot;finalLine&quot;:&quot;{{final_line}}&quot;},&quot;pdf&quot;:{&quot;title&quot;:&quot;Save this report&quot;,&quot;body&quot;:&quot;{{reference_note}}&quot;}},&quot;evidenceTemplate&quot;:{&quot;title&quot;:&quot;Evidence behind your result&quot;,&quot;blocks&quot;:[{&quot;type&quot;:&quot;paragraph&quot;,&quot;text&quot;:&quot;{{evidence_note}}&quot;}]}}</v></c><c r="P25" t="str"><v>active</v></c><c r="Q25" t="str"><v>ready_for_import</v></c><c r="R25" t="str"><v>TRUE</v></c><c r="S25" t="str"><v>TRUE</v></c><c r="T25" t="str"><v>{&quot;generated_from&quot;:&quot;fully_authored_report_first_template&quot;,&quot;deterministic&quot;:true}</v></c><c r="U25" t="str"><v>report_first::signal_d_signal_c_signal_b_signal_a</v></c></row></sheetData><autoFilter ref="A1:U25"/><ignoredErrors><ignoredError numberStoredAsText="1" sqref="A1:U25"/></ignoredErrors></worksheet>
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:U25"/>
+  <cols>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="19.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="15.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="19.83203125" customWidth="1"/>
+    <col min="9" max="9" width="22.83203125" customWidth="1"/>
+    <col min="10" max="10" width="15.83203125" customWidth="1"/>
+    <col min="11" max="11" width="26.83203125" customWidth="1"/>
+    <col min="12" max="12" width="24.83203125" customWidth="1"/>
+    <col min="13" max="13" width="23.83203125" customWidth="1"/>
+    <col min="14" max="14" width="16.83203125" customWidth="1"/>
+    <col min="15" max="15" width="24.83203125" customWidth="1"/>
+    <col min="16" max="16" width="14.83203125" customWidth="1"/>
+    <col min="17" max="17" width="19.83203125" customWidth="1"/>
+    <col min="18" max="18" width="15.83203125" customWidth="1"/>
+    <col min="19" max="19" width="20.83203125" customWidth="1"/>
+    <col min="20" max="20" width="23.83203125" customWidth="1"/>
+    <col min="21" max="21" width="14.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>assessment_key</v>
+      </c>
+      <c r="B1" t="str">
+        <v>assessment_version</v>
+      </c>
+      <c r="C1" t="str">
+        <v>package_key</v>
+      </c>
+      <c r="D1" t="str">
+        <v>package_version</v>
+      </c>
+      <c r="E1" t="str">
+        <v>domain_key</v>
+      </c>
+      <c r="F1" t="str">
+        <v>pattern_key</v>
+      </c>
+      <c r="G1" t="str">
+        <v>report_key</v>
+      </c>
+      <c r="H1" t="str">
+        <v>report_contract</v>
+      </c>
+      <c r="I1" t="str">
+        <v>score_shape_policy</v>
+      </c>
+      <c r="J1" t="str">
+        <v>score_shape</v>
+      </c>
+      <c r="K1" t="str">
+        <v>supported_score_shapes</v>
+      </c>
+      <c r="L1" t="str">
+        <v>source_markdown_path</v>
+      </c>
+      <c r="M1" t="str">
+        <v>source_content_hash</v>
+      </c>
+      <c r="N1" t="str">
+        <v>content_hash</v>
+      </c>
+      <c r="O1" t="str">
+        <v>report_template_json</v>
+      </c>
+      <c r="P1" t="str">
+        <v>status</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>manifest_status</v>
+      </c>
+      <c r="R1" t="str">
+        <v>publishable</v>
+      </c>
+      <c r="S1" t="str">
+        <v>ready_for_import</v>
+      </c>
+      <c r="T1" t="str">
+        <v>generation_metadata</v>
+      </c>
+      <c r="U1" t="str">
+        <v>lookup_key</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>{{assessment_key}}</v>
+      </c>
+      <c r="B2" t="str">
+        <v>{{package_version}}</v>
+      </c>
+      <c r="C2" t="str">
+        <v>{{assessment_key}}-report-first</v>
+      </c>
+      <c r="D2" t="str">
+        <v>{{package_version}}</v>
+      </c>
+      <c r="E2" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="F2" t="str">
+        <v>signal_a_signal_b_signal_c_signal_d</v>
+      </c>
+      <c r="G2" t="str">
+        <v>signal_a_signal_b_signal_c_signal_d</v>
+      </c>
+      <c r="H2" t="str">
+        <v>report_first_canonical_payload_v1</v>
+      </c>
+      <c r="I2" t="str">
+        <v>pattern_level_score_shape_neutral</v>
+      </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v>[]</v>
+      </c>
+      <c r="L2" t="str">
+        <v>content/authoring/{{assessment_key}}/report-first/canonical-reports/signal_a_signal_b_signal_c_signal_d.md</v>
+      </c>
+      <c r="M2" t="str">
+        <v>{{source_content_hash}}</v>
+      </c>
+      <c r="N2" t="str">
+        <v>{{content_hash}}</v>
+      </c>
+      <c r="O2" t="str">
+        <v>{"metadata":{"contractName":"report_first_canonical_payload_v1","reportModel":"report_first_canonical"},"reportKey":"signal_a_signal_b_signal_c_signal_d","patternKey":"signal_a_signal_b_signal_c_signal_d","domainKey":"{{domain_key}}","report":{"reportKey":"signal_a_signal_b_signal_c_signal_d","patternKey":"signal_a_signal_b_signal_c_signal_d","reportTitle":"{{assessment_title}} report","hero":{"title":"{{fully_authored_report_title}}","resultStatement":"{{fully_authored_result_statement}}"},"opening":[{"type":"paragraph","text":"{{editorial_introduction}}"}],"patternSummary":{"title":"Pattern at a glance","blocks":[{"type":"paragraph","text":"{{pattern_summary}}"}]},"keyInsight":{"type":"paragraph","text":"{{key_insight}}"},"chapters":[{"chapterKey":"chapter_1","chapterNumber":1,"title":"{{chapter_1_title}}","blocks":[{"type":"paragraph","text":"{{chapter_1_body}}"}],"readerFacing":true},{"chapterKey":"chapter_2","chapterNumber":2,"title":"{{chapter_2_title}}","blocks":[{"type":"paragraph","text":"{{chapter_2_body}}"}],"readerFacing":true},{"chapterKey":"chapter_3","chapterNumber":3,"title":"{{chapter_3_title}}","blocks":[{"type":"paragraph","text":"{{chapter_3_body}}"}],"readerFacing":true},{"chapterKey":"chapter_4","chapterNumber":4,"title":"{{chapter_4_title}}","blocks":[{"type":"paragraph","text":"{{chapter_4_body}}"}],"readerFacing":true},{"chapterKey":"chapter_5","chapterNumber":5,"title":"{{chapter_5_title}}","blocks":[{"type":"paragraph","text":"{{chapter_5_body}}"}],"readerFacing":true},{"chapterKey":"chapter_6","chapterNumber":6,"title":"{{chapter_6_title}}","blocks":[{"type":"paragraph","text":"{{chapter_6_body}}"}],"readerFacing":true},{"chapterKey":"chapter_7","chapterNumber":7,"title":"{{chapter_7_title}}","blocks":[{"type":"paragraph","text":"{{chapter_7_body}}"}],"readerFacing":true},{"chapterKey":"chapter_8","chapterNumber":8,"title":"{{chapter_8_title}}","blocks":[{"type":"paragraph","text":"{{chapter_8_body}}"}],"readerFacing":true},{"chapterKey":"chapter_9","chapterNumber":9,"title":"{{chapter_9_title}}","blocks":[{"type":"paragraph","text":"{{chapter_9_body}}"}],"readerFacing":true},{"chapterKey":"chapter_10","chapterNumber":10,"title":"{{chapter_10_title}}","blocks":[{"type":"paragraph","text":"{{chapter_10_body}}"}],"readerFacing":true}],"closing":{"synthesis":[{"type":"paragraph","text":"{{closing_synthesis}}"}],"finalLine":"{{final_line}}"},"pdf":{"title":"Save this report","body":"{{reference_note}}"}},"evidenceTemplate":{"title":"Evidence behind your result","blocks":[{"type":"paragraph","text":"{{evidence_note}}"}]}}</v>
+      </c>
+      <c r="P2" t="str">
+        <v>active</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>ready_for_import</v>
+      </c>
+      <c r="R2" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="S2" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="T2" t="str">
+        <v>{"generated_from":"fully_authored_report_first_template","deterministic":true}</v>
+      </c>
+      <c r="U2" t="str">
+        <v>report_first::signal_a_signal_b_signal_c_signal_d</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>{{assessment_key}}</v>
+      </c>
+      <c r="B3" t="str">
+        <v>{{package_version}}</v>
+      </c>
+      <c r="C3" t="str">
+        <v>{{assessment_key}}-report-first</v>
+      </c>
+      <c r="D3" t="str">
+        <v>{{package_version}}</v>
+      </c>
+      <c r="E3" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="F3" t="str">
+        <v>signal_a_signal_b_signal_d_signal_c</v>
+      </c>
+      <c r="G3" t="str">
+        <v>signal_a_signal_b_signal_d_signal_c</v>
+      </c>
+      <c r="H3" t="str">
+        <v>report_first_canonical_payload_v1</v>
+      </c>
+      <c r="I3" t="str">
+        <v>pattern_level_score_shape_neutral</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v>[]</v>
+      </c>
+      <c r="L3" t="str">
+        <v>content/authoring/{{assessment_key}}/report-first/canonical-reports/signal_a_signal_b_signal_d_signal_c.md</v>
+      </c>
+      <c r="M3" t="str">
+        <v>{{source_content_hash}}</v>
+      </c>
+      <c r="N3" t="str">
+        <v>{{content_hash}}</v>
+      </c>
+      <c r="O3" t="str">
+        <v>{"metadata":{"contractName":"report_first_canonical_payload_v1","reportModel":"report_first_canonical"},"reportKey":"signal_a_signal_b_signal_d_signal_c","patternKey":"signal_a_signal_b_signal_d_signal_c","domainKey":"{{domain_key}}","report":{"reportKey":"signal_a_signal_b_signal_d_signal_c","patternKey":"signal_a_signal_b_signal_d_signal_c","reportTitle":"{{assessment_title}} report","hero":{"title":"{{fully_authored_report_title}}","resultStatement":"{{fully_authored_result_statement}}"},"opening":[{"type":"paragraph","text":"{{editorial_introduction}}"}],"patternSummary":{"title":"Pattern at a glance","blocks":[{"type":"paragraph","text":"{{pattern_summary}}"}]},"keyInsight":{"type":"paragraph","text":"{{key_insight}}"},"chapters":[{"chapterKey":"chapter_1","chapterNumber":1,"title":"{{chapter_1_title}}","blocks":[{"type":"paragraph","text":"{{chapter_1_body}}"}],"readerFacing":true},{"chapterKey":"chapter_2","chapterNumber":2,"title":"{{chapter_2_title}}","blocks":[{"type":"paragraph","text":"{{chapter_2_body}}"}],"readerFacing":true},{"chapterKey":"chapter_3","chapterNumber":3,"title":"{{chapter_3_title}}","blocks":[{"type":"paragraph","text":"{{chapter_3_body}}"}],"readerFacing":true},{"chapterKey":"chapter_4","chapterNumber":4,"title":"{{chapter_4_title}}","blocks":[{"type":"paragraph","text":"{{chapter_4_body}}"}],"readerFacing":true},{"chapterKey":"chapter_5","chapterNumber":5,"title":"{{chapter_5_title}}","blocks":[{"type":"paragraph","text":"{{chapter_5_body}}"}],"readerFacing":true},{"chapterKey":"chapter_6","chapterNumber":6,"title":"{{chapter_6_title}}","blocks":[{"type":"paragraph","text":"{{chapter_6_body}}"}],"readerFacing":true},{"chapterKey":"chapter_7","chapterNumber":7,"title":"{{chapter_7_title}}","blocks":[{"type":"paragraph","text":"{{chapter_7_body}}"}],"readerFacing":true},{"chapterKey":"chapter_8","chapterNumber":8,"title":"{{chapter_8_title}}","blocks":[{"type":"paragraph","text":"{{chapter_8_body}}"}],"readerFacing":true},{"chapterKey":"chapter_9","chapterNumber":9,"title":"{{chapter_9_title}}","blocks":[{"type":"paragraph","text":"{{chapter_9_body}}"}],"readerFacing":true},{"chapterKey":"chapter_10","chapterNumber":10,"title":"{{chapter_10_title}}","blocks":[{"type":"paragraph","text":"{{chapter_10_body}}"}],"readerFacing":true}],"closing":{"synthesis":[{"type":"paragraph","text":"{{closing_synthesis}}"}],"finalLine":"{{final_line}}"},"pdf":{"title":"Save this report","body":"{{reference_note}}"}},"evidenceTemplate":{"title":"Evidence behind your result","blocks":[{"type":"paragraph","text":"{{evidence_note}}"}]}}</v>
+      </c>
+      <c r="P3" t="str">
+        <v>active</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>ready_for_import</v>
+      </c>
+      <c r="R3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="S3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="T3" t="str">
+        <v>{"generated_from":"fully_authored_report_first_template","deterministic":true}</v>
+      </c>
+      <c r="U3" t="str">
+        <v>report_first::signal_a_signal_b_signal_d_signal_c</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>{{assessment_key}}</v>
+      </c>
+      <c r="B4" t="str">
+        <v>{{package_version}}</v>
+      </c>
+      <c r="C4" t="str">
+        <v>{{assessment_key}}-report-first</v>
+      </c>
+      <c r="D4" t="str">
+        <v>{{package_version}}</v>
+      </c>
+      <c r="E4" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="F4" t="str">
+        <v>signal_a_signal_c_signal_b_signal_d</v>
+      </c>
+      <c r="G4" t="str">
+        <v>signal_a_signal_c_signal_b_signal_d</v>
+      </c>
+      <c r="H4" t="str">
+        <v>report_first_canonical_payload_v1</v>
+      </c>
+      <c r="I4" t="str">
+        <v>pattern_level_score_shape_neutral</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v>[]</v>
+      </c>
+      <c r="L4" t="str">
+        <v>content/authoring/{{assessment_key}}/report-first/canonical-reports/signal_a_signal_c_signal_b_signal_d.md</v>
+      </c>
+      <c r="M4" t="str">
+        <v>{{source_content_hash}}</v>
+      </c>
+      <c r="N4" t="str">
+        <v>{{content_hash}}</v>
+      </c>
+      <c r="O4" t="str">
+        <v>{"metadata":{"contractName":"report_first_canonical_payload_v1","reportModel":"report_first_canonical"},"reportKey":"signal_a_signal_c_signal_b_signal_d","patternKey":"signal_a_signal_c_signal_b_signal_d","domainKey":"{{domain_key}}","report":{"reportKey":"signal_a_signal_c_signal_b_signal_d","patternKey":"signal_a_signal_c_signal_b_signal_d","reportTitle":"{{assessment_title}} report","hero":{"title":"{{fully_authored_report_title}}","resultStatement":"{{fully_authored_result_statement}}"},"opening":[{"type":"paragraph","text":"{{editorial_introduction}}"}],"patternSummary":{"title":"Pattern at a glance","blocks":[{"type":"paragraph","text":"{{pattern_summary}}"}]},"keyInsight":{"type":"paragraph","text":"{{key_insight}}"},"chapters":[{"chapterKey":"chapter_1","chapterNumber":1,"title":"{{chapter_1_title}}","blocks":[{"type":"paragraph","text":"{{chapter_1_body}}"}],"readerFacing":true},{"chapterKey":"chapter_2","chapterNumber":2,"title":"{{chapter_2_title}}","blocks":[{"type":"paragraph","text":"{{chapter_2_body}}"}],"readerFacing":true},{"chapterKey":"chapter_3","chapterNumber":3,"title":"{{chapter_3_title}}","blocks":[{"type":"paragraph","text":"{{chapter_3_body}}"}],"readerFacing":true},{"chapterKey":"chapter_4","chapterNumber":4,"title":"{{chapter_4_title}}","blocks":[{"type":"paragraph","text":"{{chapter_4_body}}"}],"readerFacing":true},{"chapterKey":"chapter_5","chapterNumber":5,"title":"{{chapter_5_title}}","blocks":[{"type":"paragraph","text":"{{chapter_5_body}}"}],"readerFacing":true},{"chapterKey":"chapter_6","chapterNumber":6,"title":"{{chapter_6_title}}","blocks":[{"type":"paragraph","text":"{{chapter_6_body}}"}],"readerFacing":true},{"chapterKey":"chapter_7","chapterNumber":7,"title":"{{chapter_7_title}}","blocks":[{"type":"paragraph","text":"{{chapter_7_body}}"}],"readerFacing":true},{"chapterKey":"chapter_8","chapterNumber":8,"title":"{{chapter_8_title}}","blocks":[{"type":"paragraph","text":"{{chapter_8_body}}"}],"readerFacing":true},{"chapterKey":"chapter_9","chapterNumber":9,"title":"{{chapter_9_title}}","blocks":[{"type":"paragraph","text":"{{chapter_9_body}}"}],"readerFacing":true},{"chapterKey":"chapter_10","chapterNumber":10,"title":"{{chapter_10_title}}","blocks":[{"type":"paragraph","text":"{{chapter_10_body}}"}],"readerFacing":true}],"closing":{"synthesis":[{"type":"paragraph","text":"{{closing_synthesis}}"}],"finalLine":"{{final_line}}"},"pdf":{"title":"Save this report","body":"{{reference_note}}"}},"evidenceTemplate":{"title":"Evidence behind your result","blocks":[{"type":"paragraph","text":"{{evidence_note}}"}]}}</v>
+      </c>
+      <c r="P4" t="str">
+        <v>active</v>
+      </c>
+      <c r="Q4" t="str">
+        <v>ready_for_import</v>
+      </c>
+      <c r="R4" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="S4" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="T4" t="str">
+        <v>{"generated_from":"fully_authored_report_first_template","deterministic":true}</v>
+      </c>
+      <c r="U4" t="str">
+        <v>report_first::signal_a_signal_c_signal_b_signal_d</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>{{assessment_key}}</v>
+      </c>
+      <c r="B5" t="str">
+        <v>{{package_version}}</v>
+      </c>
+      <c r="C5" t="str">
+        <v>{{assessment_key}}-report-first</v>
+      </c>
+      <c r="D5" t="str">
+        <v>{{package_version}}</v>
+      </c>
+      <c r="E5" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="F5" t="str">
+        <v>signal_a_signal_c_signal_d_signal_b</v>
+      </c>
+      <c r="G5" t="str">
+        <v>signal_a_signal_c_signal_d_signal_b</v>
+      </c>
+      <c r="H5" t="str">
+        <v>report_first_canonical_payload_v1</v>
+      </c>
+      <c r="I5" t="str">
+        <v>pattern_level_score_shape_neutral</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v>[]</v>
+      </c>
+      <c r="L5" t="str">
+        <v>content/authoring/{{assessment_key}}/report-first/canonical-reports/signal_a_signal_c_signal_d_signal_b.md</v>
+      </c>
+      <c r="M5" t="str">
+        <v>{{source_content_hash}}</v>
+      </c>
+      <c r="N5" t="str">
+        <v>{{content_hash}}</v>
+      </c>
+      <c r="O5" t="str">
+        <v>{"metadata":{"contractName":"report_first_canonical_payload_v1","reportModel":"report_first_canonical"},"reportKey":"signal_a_signal_c_signal_d_signal_b","patternKey":"signal_a_signal_c_signal_d_signal_b","domainKey":"{{domain_key}}","report":{"reportKey":"signal_a_signal_c_signal_d_signal_b","patternKey":"signal_a_signal_c_signal_d_signal_b","reportTitle":"{{assessment_title}} report","hero":{"title":"{{fully_authored_report_title}}","resultStatement":"{{fully_authored_result_statement}}"},"opening":[{"type":"paragraph","text":"{{editorial_introduction}}"}],"patternSummary":{"title":"Pattern at a glance","blocks":[{"type":"paragraph","text":"{{pattern_summary}}"}]},"keyInsight":{"type":"paragraph","text":"{{key_insight}}"},"chapters":[{"chapterKey":"chapter_1","chapterNumber":1,"title":"{{chapter_1_title}}","blocks":[{"type":"paragraph","text":"{{chapter_1_body}}"}],"readerFacing":true},{"chapterKey":"chapter_2","chapterNumber":2,"title":"{{chapter_2_title}}","blocks":[{"type":"paragraph","text":"{{chapter_2_body}}"}],"readerFacing":true},{"chapterKey":"chapter_3","chapterNumber":3,"title":"{{chapter_3_title}}","blocks":[{"type":"paragraph","text":"{{chapter_3_body}}"}],"readerFacing":true},{"chapterKey":"chapter_4","chapterNumber":4,"title":"{{chapter_4_title}}","blocks":[{"type":"paragraph","text":"{{chapter_4_body}}"}],"readerFacing":true},{"chapterKey":"chapter_5","chapterNumber":5,"title":"{{chapter_5_title}}","blocks":[{"type":"paragraph","text":"{{chapter_5_body}}"}],"readerFacing":true},{"chapterKey":"chapter_6","chapterNumber":6,"title":"{{chapter_6_title}}","blocks":[{"type":"paragraph","text":"{{chapter_6_body}}"}],"readerFacing":true},{"chapterKey":"chapter_7","chapterNumber":7,"title":"{{chapter_7_title}}","blocks":[{"type":"paragraph","text":"{{chapter_7_body}}"}],"readerFacing":true},{"chapterKey":"chapter_8","chapterNumber":8,"title":"{{chapter_8_title}}","blocks":[{"type":"paragraph","text":"{{chapter_8_body}}"}],"readerFacing":true},{"chapterKey":"chapter_9","chapterNumber":9,"title":"{{chapter_9_title}}","blocks":[{"type":"paragraph","text":"{{chapter_9_body}}"}],"readerFacing":true},{"chapterKey":"chapter_10","chapterNumber":10,"title":"{{chapter_10_title}}","blocks":[{"type":"paragraph","text":"{{chapter_10_body}}"}],"readerFacing":true}],"closing":{"synthesis":[{"type":"paragraph","text":"{{closing_synthesis}}"}],"finalLine":"{{final_line}}"},"pdf":{"title":"Save this report","body":"{{reference_note}}"}},"evidenceTemplate":{"title":"Evidence behind your result","blocks":[{"type":"paragraph","text":"{{evidence_note}}"}]}}</v>
+      </c>
+      <c r="P5" t="str">
+        <v>active</v>
+      </c>
+      <c r="Q5" t="str">
+        <v>ready_for_import</v>
+      </c>
+      <c r="R5" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="S5" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="T5" t="str">
+        <v>{"generated_from":"fully_authored_report_first_template","deterministic":true}</v>
+      </c>
+      <c r="U5" t="str">
+        <v>report_first::signal_a_signal_c_signal_d_signal_b</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>{{assessment_key}}</v>
+      </c>
+      <c r="B6" t="str">
+        <v>{{package_version}}</v>
+      </c>
+      <c r="C6" t="str">
+        <v>{{assessment_key}}-report-first</v>
+      </c>
+      <c r="D6" t="str">
+        <v>{{package_version}}</v>
+      </c>
+      <c r="E6" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="F6" t="str">
+        <v>signal_a_signal_d_signal_b_signal_c</v>
+      </c>
+      <c r="G6" t="str">
+        <v>signal_a_signal_d_signal_b_signal_c</v>
+      </c>
+      <c r="H6" t="str">
+        <v>report_first_canonical_payload_v1</v>
+      </c>
+      <c r="I6" t="str">
+        <v>pattern_level_score_shape_neutral</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v>[]</v>
+      </c>
+      <c r="L6" t="str">
+        <v>content/authoring/{{assessment_key}}/report-first/canonical-reports/signal_a_signal_d_signal_b_signal_c.md</v>
+      </c>
+      <c r="M6" t="str">
+        <v>{{source_content_hash}}</v>
+      </c>
+      <c r="N6" t="str">
+        <v>{{content_hash}}</v>
+      </c>
+      <c r="O6" t="str">
+        <v>{"metadata":{"contractName":"report_first_canonical_payload_v1","reportModel":"report_first_canonical"},"reportKey":"signal_a_signal_d_signal_b_signal_c","patternKey":"signal_a_signal_d_signal_b_signal_c","domainKey":"{{domain_key}}","report":{"reportKey":"signal_a_signal_d_signal_b_signal_c","patternKey":"signal_a_signal_d_signal_b_signal_c","reportTitle":"{{assessment_title}} report","hero":{"title":"{{fully_authored_report_title}}","resultStatement":"{{fully_authored_result_statement}}"},"opening":[{"type":"paragraph","text":"{{editorial_introduction}}"}],"patternSummary":{"title":"Pattern at a glance","blocks":[{"type":"paragraph","text":"{{pattern_summary}}"}]},"keyInsight":{"type":"paragraph","text":"{{key_insight}}"},"chapters":[{"chapterKey":"chapter_1","chapterNumber":1,"title":"{{chapter_1_title}}","blocks":[{"type":"paragraph","text":"{{chapter_1_body}}"}],"readerFacing":true},{"chapterKey":"chapter_2","chapterNumber":2,"title":"{{chapter_2_title}}","blocks":[{"type":"paragraph","text":"{{chapter_2_body}}"}],"readerFacing":true},{"chapterKey":"chapter_3","chapterNumber":3,"title":"{{chapter_3_title}}","blocks":[{"type":"paragraph","text":"{{chapter_3_body}}"}],"readerFacing":true},{"chapterKey":"chapter_4","chapterNumber":4,"title":"{{chapter_4_title}}","blocks":[{"type":"paragraph","text":"{{chapter_4_body}}"}],"readerFacing":true},{"chapterKey":"chapter_5","chapterNumber":5,"title":"{{chapter_5_title}}","blocks":[{"type":"paragraph","text":"{{chapter_5_body}}"}],"readerFacing":true},{"chapterKey":"chapter_6","chapterNumber":6,"title":"{{chapter_6_title}}","blocks":[{"type":"paragraph","text":"{{chapter_6_body}}"}],"readerFacing":true},{"chapterKey":"chapter_7","chapterNumber":7,"title":"{{chapter_7_title}}","blocks":[{"type":"paragraph","text":"{{chapter_7_body}}"}],"readerFacing":true},{"chapterKey":"chapter_8","chapterNumber":8,"title":"{{chapter_8_title}}","blocks":[{"type":"paragraph","text":"{{chapter_8_body}}"}],"readerFacing":true},{"chapterKey":"chapter_9","chapterNumber":9,"title":"{{chapter_9_title}}","blocks":[{"type":"paragraph","text":"{{chapter_9_body}}"}],"readerFacing":true},{"chapterKey":"chapter_10","chapterNumber":10,"title":"{{chapter_10_title}}","blocks":[{"type":"paragraph","text":"{{chapter_10_body}}"}],"readerFacing":true}],"closing":{"synthesis":[{"type":"paragraph","text":"{{closing_synthesis}}"}],"finalLine":"{{final_line}}"},"pdf":{"title":"Save this report","body":"{{reference_note}}"}},"evidenceTemplate":{"title":"Evidence behind your result","blocks":[{"type":"paragraph","text":"{{evidence_note}}"}]}}</v>
+      </c>
+      <c r="P6" t="str">
+        <v>active</v>
+      </c>
+      <c r="Q6" t="str">
+        <v>ready_for_import</v>
+      </c>
+      <c r="R6" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="S6" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="T6" t="str">
+        <v>{"generated_from":"fully_authored_report_first_template","deterministic":true}</v>
+      </c>
+      <c r="U6" t="str">
+        <v>report_first::signal_a_signal_d_signal_b_signal_c</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>{{assessment_key}}</v>
+      </c>
+      <c r="B7" t="str">
+        <v>{{package_version}}</v>
+      </c>
+      <c r="C7" t="str">
+        <v>{{assessment_key}}-report-first</v>
+      </c>
+      <c r="D7" t="str">
+        <v>{{package_version}}</v>
+      </c>
+      <c r="E7" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="F7" t="str">
+        <v>signal_a_signal_d_signal_c_signal_b</v>
+      </c>
+      <c r="G7" t="str">
+        <v>signal_a_signal_d_signal_c_signal_b</v>
+      </c>
+      <c r="H7" t="str">
+        <v>report_first_canonical_payload_v1</v>
+      </c>
+      <c r="I7" t="str">
+        <v>pattern_level_score_shape_neutral</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v>[]</v>
+      </c>
+      <c r="L7" t="str">
+        <v>content/authoring/{{assessment_key}}/report-first/canonical-reports/signal_a_signal_d_signal_c_signal_b.md</v>
+      </c>
+      <c r="M7" t="str">
+        <v>{{source_content_hash}}</v>
+      </c>
+      <c r="N7" t="str">
+        <v>{{content_hash}}</v>
+      </c>
+      <c r="O7" t="str">
+        <v>{"metadata":{"contractName":"report_first_canonical_payload_v1","reportModel":"report_first_canonical"},"reportKey":"signal_a_signal_d_signal_c_signal_b","patternKey":"signal_a_signal_d_signal_c_signal_b","domainKey":"{{domain_key}}","report":{"reportKey":"signal_a_signal_d_signal_c_signal_b","patternKey":"signal_a_signal_d_signal_c_signal_b","reportTitle":"{{assessment_title}} report","hero":{"title":"{{fully_authored_report_title}}","resultStatement":"{{fully_authored_result_statement}}"},"opening":[{"type":"paragraph","text":"{{editorial_introduction}}"}],"patternSummary":{"title":"Pattern at a glance","blocks":[{"type":"paragraph","text":"{{pattern_summary}}"}]},"keyInsight":{"type":"paragraph","text":"{{key_insight}}"},"chapters":[{"chapterKey":"chapter_1","chapterNumber":1,"title":"{{chapter_1_title}}","blocks":[{"type":"paragraph","text":"{{chapter_1_body}}"}],"readerFacing":true},{"chapterKey":"chapter_2","chapterNumber":2,"title":"{{chapter_2_title}}","blocks":[{"type":"paragraph","text":"{{chapter_2_body}}"}],"readerFacing":true},{"chapterKey":"chapter_3","chapterNumber":3,"title":"{{chapter_3_title}}","blocks":[{"type":"paragraph","text":"{{chapter_3_body}}"}],"readerFacing":true},{"chapterKey":"chapter_4","chapterNumber":4,"title":"{{chapter_4_title}}","blocks":[{"type":"paragraph","text":"{{chapter_4_body}}"}],"readerFacing":true},{"chapterKey":"chapter_5","chapterNumber":5,"title":"{{chapter_5_title}}","blocks":[{"type":"paragraph","text":"{{chapter_5_body}}"}],"readerFacing":true},{"chapterKey":"chapter_6","chapterNumber":6,"title":"{{chapter_6_title}}","blocks":[{"type":"paragraph","text":"{{chapter_6_body}}"}],"readerFacing":true},{"chapterKey":"chapter_7","chapterNumber":7,"title":"{{chapter_7_title}}","blocks":[{"type":"paragraph","text":"{{chapter_7_body}}"}],"readerFacing":true},{"chapterKey":"chapter_8","chapterNumber":8,"title":"{{chapter_8_title}}","blocks":[{"type":"paragraph","text":"{{chapter_8_body}}"}],"readerFacing":true},{"chapterKey":"chapter_9","chapterNumber":9,"title":"{{chapter_9_title}}","blocks":[{"type":"paragraph","text":"{{chapter_9_body}}"}],"readerFacing":true},{"chapterKey":"chapter_10","chapterNumber":10,"title":"{{chapter_10_title}}","blocks":[{"type":"paragraph","text":"{{chapter_10_body}}"}],"readerFacing":true}],"closing":{"synthesis":[{"type":"paragraph","text":"{{closing_synthesis}}"}],"finalLine":"{{final_line}}"},"pdf":{"title":"Save this report","body":"{{reference_note}}"}},"evidenceTemplate":{"title":"Evidence behind your result","blocks":[{"type":"paragraph","text":"{{evidence_note}}"}]}}</v>
+      </c>
+      <c r="P7" t="str">
+        <v>active</v>
+      </c>
+      <c r="Q7" t="str">
+        <v>ready_for_import</v>
+      </c>
+      <c r="R7" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="S7" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="T7" t="str">
+        <v>{"generated_from":"fully_authored_report_first_template","deterministic":true}</v>
+      </c>
+      <c r="U7" t="str">
+        <v>report_first::signal_a_signal_d_signal_c_signal_b</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>{{assessment_key}}</v>
+      </c>
+      <c r="B8" t="str">
+        <v>{{package_version}}</v>
+      </c>
+      <c r="C8" t="str">
+        <v>{{assessment_key}}-report-first</v>
+      </c>
+      <c r="D8" t="str">
+        <v>{{package_version}}</v>
+      </c>
+      <c r="E8" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="F8" t="str">
+        <v>signal_b_signal_a_signal_c_signal_d</v>
+      </c>
+      <c r="G8" t="str">
+        <v>signal_b_signal_a_signal_c_signal_d</v>
+      </c>
+      <c r="H8" t="str">
+        <v>report_first_canonical_payload_v1</v>
+      </c>
+      <c r="I8" t="str">
+        <v>pattern_level_score_shape_neutral</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v>[]</v>
+      </c>
+      <c r="L8" t="str">
+        <v>content/authoring/{{assessment_key}}/report-first/canonical-reports/signal_b_signal_a_signal_c_signal_d.md</v>
+      </c>
+      <c r="M8" t="str">
+        <v>{{source_content_hash}}</v>
+      </c>
+      <c r="N8" t="str">
+        <v>{{content_hash}}</v>
+      </c>
+      <c r="O8" t="str">
+        <v>{"metadata":{"contractName":"report_first_canonical_payload_v1","reportModel":"report_first_canonical"},"reportKey":"signal_b_signal_a_signal_c_signal_d","patternKey":"signal_b_signal_a_signal_c_signal_d","domainKey":"{{domain_key}}","report":{"reportKey":"signal_b_signal_a_signal_c_signal_d","patternKey":"signal_b_signal_a_signal_c_signal_d","reportTitle":"{{assessment_title}} report","hero":{"title":"{{fully_authored_report_title}}","resultStatement":"{{fully_authored_result_statement}}"},"opening":[{"type":"paragraph","text":"{{editorial_introduction}}"}],"patternSummary":{"title":"Pattern at a glance","blocks":[{"type":"paragraph","text":"{{pattern_summary}}"}]},"keyInsight":{"type":"paragraph","text":"{{key_insight}}"},"chapters":[{"chapterKey":"chapter_1","chapterNumber":1,"title":"{{chapter_1_title}}","blocks":[{"type":"paragraph","text":"{{chapter_1_body}}"}],"readerFacing":true},{"chapterKey":"chapter_2","chapterNumber":2,"title":"{{chapter_2_title}}","blocks":[{"type":"paragraph","text":"{{chapter_2_body}}"}],"readerFacing":true},{"chapterKey":"chapter_3","chapterNumber":3,"title":"{{chapter_3_title}}","blocks":[{"type":"paragraph","text":"{{chapter_3_body}}"}],"readerFacing":true},{"chapterKey":"chapter_4","chapterNumber":4,"title":"{{chapter_4_title}}","blocks":[{"type":"paragraph","text":"{{chapter_4_body}}"}],"readerFacing":true},{"chapterKey":"chapter_5","chapterNumber":5,"title":"{{chapter_5_title}}","blocks":[{"type":"paragraph","text":"{{chapter_5_body}}"}],"readerFacing":true},{"chapterKey":"chapter_6","chapterNumber":6,"title":"{{chapter_6_title}}","blocks":[{"type":"paragraph","text":"{{chapter_6_body}}"}],"readerFacing":true},{"chapterKey":"chapter_7","chapterNumber":7,"title":"{{chapter_7_title}}","blocks":[{"type":"paragraph","text":"{{chapter_7_body}}"}],"readerFacing":true},{"chapterKey":"chapter_8","chapterNumber":8,"title":"{{chapter_8_title}}","blocks":[{"type":"paragraph","text":"{{chapter_8_body}}"}],"readerFacing":true},{"chapterKey":"chapter_9","chapterNumber":9,"title":"{{chapter_9_title}}","blocks":[{"type":"paragraph","text":"{{chapter_9_body}}"}],"readerFacing":true},{"chapterKey":"chapter_10","chapterNumber":10,"title":"{{chapter_10_title}}","blocks":[{"type":"paragraph","text":"{{chapter_10_body}}"}],"readerFacing":true}],"closing":{"synthesis":[{"type":"paragraph","text":"{{closing_synthesis}}"}],"finalLine":"{{final_line}}"},"pdf":{"title":"Save this report","body":"{{reference_note}}"}},"evidenceTemplate":{"title":"Evidence behind your result","blocks":[{"type":"paragraph","text":"{{evidence_note}}"}]}}</v>
+      </c>
+      <c r="P8" t="str">
+        <v>active</v>
+      </c>
+      <c r="Q8" t="str">
+        <v>ready_for_import</v>
+      </c>
+      <c r="R8" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="S8" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="T8" t="str">
+        <v>{"generated_from":"fully_authored_report_first_template","deterministic":true}</v>
+      </c>
+      <c r="U8" t="str">
+        <v>report_first::signal_b_signal_a_signal_c_signal_d</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>{{assessment_key}}</v>
+      </c>
+      <c r="B9" t="str">
+        <v>{{package_version}}</v>
+      </c>
+      <c r="C9" t="str">
+        <v>{{assessment_key}}-report-first</v>
+      </c>
+      <c r="D9" t="str">
+        <v>{{package_version}}</v>
+      </c>
+      <c r="E9" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="F9" t="str">
+        <v>signal_b_signal_a_signal_d_signal_c</v>
+      </c>
+      <c r="G9" t="str">
+        <v>signal_b_signal_a_signal_d_signal_c</v>
+      </c>
+      <c r="H9" t="str">
+        <v>report_first_canonical_payload_v1</v>
+      </c>
+      <c r="I9" t="str">
+        <v>pattern_level_score_shape_neutral</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v>[]</v>
+      </c>
+      <c r="L9" t="str">
+        <v>content/authoring/{{assessment_key}}/report-first/canonical-reports/signal_b_signal_a_signal_d_signal_c.md</v>
+      </c>
+      <c r="M9" t="str">
+        <v>{{source_content_hash}}</v>
+      </c>
+      <c r="N9" t="str">
+        <v>{{content_hash}}</v>
+      </c>
+      <c r="O9" t="str">
+        <v>{"metadata":{"contractName":"report_first_canonical_payload_v1","reportModel":"report_first_canonical"},"reportKey":"signal_b_signal_a_signal_d_signal_c","patternKey":"signal_b_signal_a_signal_d_signal_c","domainKey":"{{domain_key}}","report":{"reportKey":"signal_b_signal_a_signal_d_signal_c","patternKey":"signal_b_signal_a_signal_d_signal_c","reportTitle":"{{assessment_title}} report","hero":{"title":"{{fully_authored_report_title}}","resultStatement":"{{fully_authored_result_statement}}"},"opening":[{"type":"paragraph","text":"{{editorial_introduction}}"}],"patternSummary":{"title":"Pattern at a glance","blocks":[{"type":"paragraph","text":"{{pattern_summary}}"}]},"keyInsight":{"type":"paragraph","text":"{{key_insight}}"},"chapters":[{"chapterKey":"chapter_1","chapterNumber":1,"title":"{{chapter_1_title}}","blocks":[{"type":"paragraph","text":"{{chapter_1_body}}"}],"readerFacing":true},{"chapterKey":"chapter_2","chapterNumber":2,"title":"{{chapter_2_title}}","blocks":[{"type":"paragraph","text":"{{chapter_2_body}}"}],"readerFacing":true},{"chapterKey":"chapter_3","chapterNumber":3,"title":"{{chapter_3_title}}","blocks":[{"type":"paragraph","text":"{{chapter_3_body}}"}],"readerFacing":true},{"chapterKey":"chapter_4","chapterNumber":4,"title":"{{chapter_4_title}}","blocks":[{"type":"paragraph","text":"{{chapter_4_body}}"}],"readerFacing":true},{"chapterKey":"chapter_5","chapterNumber":5,"title":"{{chapter_5_title}}","blocks":[{"type":"paragraph","text":"{{chapter_5_body}}"}],"readerFacing":true},{"chapterKey":"chapter_6","chapterNumber":6,"title":"{{chapter_6_title}}","blocks":[{"type":"paragraph","text":"{{chapter_6_body}}"}],"readerFacing":true},{"chapterKey":"chapter_7","chapterNumber":7,"title":"{{chapter_7_title}}","blocks":[{"type":"paragraph","text":"{{chapter_7_body}}"}],"readerFacing":true},{"chapterKey":"chapter_8","chapterNumber":8,"title":"{{chapter_8_title}}","blocks":[{"type":"paragraph","text":"{{chapter_8_body}}"}],"readerFacing":true},{"chapterKey":"chapter_9","chapterNumber":9,"title":"{{chapter_9_title}}","blocks":[{"type":"paragraph","text":"{{chapter_9_body}}"}],"readerFacing":true},{"chapterKey":"chapter_10","chapterNumber":10,"title":"{{chapter_10_title}}","blocks":[{"type":"paragraph","text":"{{chapter_10_body}}"}],"readerFacing":true}],"closing":{"synthesis":[{"type":"paragraph","text":"{{closing_synthesis}}"}],"finalLine":"{{final_line}}"},"pdf":{"title":"Save this report","body":"{{reference_note}}"}},"evidenceTemplate":{"title":"Evidence behind your result","blocks":[{"type":"paragraph","text":"{{evidence_note}}"}]}}</v>
+      </c>
+      <c r="P9" t="str">
+        <v>active</v>
+      </c>
+      <c r="Q9" t="str">
+        <v>ready_for_import</v>
+      </c>
+      <c r="R9" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="S9" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="T9" t="str">
+        <v>{"generated_from":"fully_authored_report_first_template","deterministic":true}</v>
+      </c>
+      <c r="U9" t="str">
+        <v>report_first::signal_b_signal_a_signal_d_signal_c</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>{{assessment_key}}</v>
+      </c>
+      <c r="B10" t="str">
+        <v>{{package_version}}</v>
+      </c>
+      <c r="C10" t="str">
+        <v>{{assessment_key}}-report-first</v>
+      </c>
+      <c r="D10" t="str">
+        <v>{{package_version}}</v>
+      </c>
+      <c r="E10" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="F10" t="str">
+        <v>signal_b_signal_c_signal_a_signal_d</v>
+      </c>
+      <c r="G10" t="str">
+        <v>signal_b_signal_c_signal_a_signal_d</v>
+      </c>
+      <c r="H10" t="str">
+        <v>report_first_canonical_payload_v1</v>
+      </c>
+      <c r="I10" t="str">
+        <v>pattern_level_score_shape_neutral</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v>[]</v>
+      </c>
+      <c r="L10" t="str">
+        <v>content/authoring/{{assessment_key}}/report-first/canonical-reports/signal_b_signal_c_signal_a_signal_d.md</v>
+      </c>
+      <c r="M10" t="str">
+        <v>{{source_content_hash}}</v>
+      </c>
+      <c r="N10" t="str">
+        <v>{{content_hash}}</v>
+      </c>
+      <c r="O10" t="str">
+        <v>{"metadata":{"contractName":"report_first_canonical_payload_v1","reportModel":"report_first_canonical"},"reportKey":"signal_b_signal_c_signal_a_signal_d","patternKey":"signal_b_signal_c_signal_a_signal_d","domainKey":"{{domain_key}}","report":{"reportKey":"signal_b_signal_c_signal_a_signal_d","patternKey":"signal_b_signal_c_signal_a_signal_d","reportTitle":"{{assessment_title}} report","hero":{"title":"{{fully_authored_report_title}}","resultStatement":"{{fully_authored_result_statement}}"},"opening":[{"type":"paragraph","text":"{{editorial_introduction}}"}],"patternSummary":{"title":"Pattern at a glance","blocks":[{"type":"paragraph","text":"{{pattern_summary}}"}]},"keyInsight":{"type":"paragraph","text":"{{key_insight}}"},"chapters":[{"chapterKey":"chapter_1","chapterNumber":1,"title":"{{chapter_1_title}}","blocks":[{"type":"paragraph","text":"{{chapter_1_body}}"}],"readerFacing":true},{"chapterKey":"chapter_2","chapterNumber":2,"title":"{{chapter_2_title}}","blocks":[{"type":"paragraph","text":"{{chapter_2_body}}"}],"readerFacing":true},{"chapterKey":"chapter_3","chapterNumber":3,"title":"{{chapter_3_title}}","blocks":[{"type":"paragraph","text":"{{chapter_3_body}}"}],"readerFacing":true},{"chapterKey":"chapter_4","chapterNumber":4,"title":"{{chapter_4_title}}","blocks":[{"type":"paragraph","text":"{{chapter_4_body}}"}],"readerFacing":true},{"chapterKey":"chapter_5","chapterNumber":5,"title":"{{chapter_5_title}}","blocks":[{"type":"paragraph","text":"{{chapter_5_body}}"}],"readerFacing":true},{"chapterKey":"chapter_6","chapterNumber":6,"title":"{{chapter_6_title}}","blocks":[{"type":"paragraph","text":"{{chapter_6_body}}"}],"readerFacing":true},{"chapterKey":"chapter_7","chapterNumber":7,"title":"{{chapter_7_title}}","blocks":[{"type":"paragraph","text":"{{chapter_7_body}}"}],"readerFacing":true},{"chapterKey":"chapter_8","chapterNumber":8,"title":"{{chapter_8_title}}","blocks":[{"type":"paragraph","text":"{{chapter_8_body}}"}],"readerFacing":true},{"chapterKey":"chapter_9","chapterNumber":9,"title":"{{chapter_9_title}}","blocks":[{"type":"paragraph","text":"{{chapter_9_body}}"}],"readerFacing":true},{"chapterKey":"chapter_10","chapterNumber":10,"title":"{{chapter_10_title}}","blocks":[{"type":"paragraph","text":"{{chapter_10_body}}"}],"readerFacing":true}],"closing":{"synthesis":[{"type":"paragraph","text":"{{closing_synthesis}}"}],"finalLine":"{{final_line}}"},"pdf":{"title":"Save this report","body":"{{reference_note}}"}},"evidenceTemplate":{"title":"Evidence behind your result","blocks":[{"type":"paragraph","text":"{{evidence_note}}"}]}}</v>
+      </c>
+      <c r="P10" t="str">
+        <v>active</v>
+      </c>
+      <c r="Q10" t="str">
+        <v>ready_for_import</v>
+      </c>
+      <c r="R10" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="S10" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="T10" t="str">
+        <v>{"generated_from":"fully_authored_report_first_template","deterministic":true}</v>
+      </c>
+      <c r="U10" t="str">
+        <v>report_first::signal_b_signal_c_signal_a_signal_d</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>{{assessment_key}}</v>
+      </c>
+      <c r="B11" t="str">
+        <v>{{package_version}}</v>
+      </c>
+      <c r="C11" t="str">
+        <v>{{assessment_key}}-report-first</v>
+      </c>
+      <c r="D11" t="str">
+        <v>{{package_version}}</v>
+      </c>
+      <c r="E11" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="F11" t="str">
+        <v>signal_b_signal_c_signal_d_signal_a</v>
+      </c>
+      <c r="G11" t="str">
+        <v>signal_b_signal_c_signal_d_signal_a</v>
+      </c>
+      <c r="H11" t="str">
+        <v>report_first_canonical_payload_v1</v>
+      </c>
+      <c r="I11" t="str">
+        <v>pattern_level_score_shape_neutral</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v>[]</v>
+      </c>
+      <c r="L11" t="str">
+        <v>content/authoring/{{assessment_key}}/report-first/canonical-reports/signal_b_signal_c_signal_d_signal_a.md</v>
+      </c>
+      <c r="M11" t="str">
+        <v>{{source_content_hash}}</v>
+      </c>
+      <c r="N11" t="str">
+        <v>{{content_hash}}</v>
+      </c>
+      <c r="O11" t="str">
+        <v>{"metadata":{"contractName":"report_first_canonical_payload_v1","reportModel":"report_first_canonical"},"reportKey":"signal_b_signal_c_signal_d_signal_a","patternKey":"signal_b_signal_c_signal_d_signal_a","domainKey":"{{domain_key}}","report":{"reportKey":"signal_b_signal_c_signal_d_signal_a","patternKey":"signal_b_signal_c_signal_d_signal_a","reportTitle":"{{assessment_title}} report","hero":{"title":"{{fully_authored_report_title}}","resultStatement":"{{fully_authored_result_statement}}"},"opening":[{"type":"paragraph","text":"{{editorial_introduction}}"}],"patternSummary":{"title":"Pattern at a glance","blocks":[{"type":"paragraph","text":"{{pattern_summary}}"}]},"keyInsight":{"type":"paragraph","text":"{{key_insight}}"},"chapters":[{"chapterKey":"chapter_1","chapterNumber":1,"title":"{{chapter_1_title}}","blocks":[{"type":"paragraph","text":"{{chapter_1_body}}"}],"readerFacing":true},{"chapterKey":"chapter_2","chapterNumber":2,"title":"{{chapter_2_title}}","blocks":[{"type":"paragraph","text":"{{chapter_2_body}}"}],"readerFacing":true},{"chapterKey":"chapter_3","chapterNumber":3,"title":"{{chapter_3_title}}","blocks":[{"type":"paragraph","text":"{{chapter_3_body}}"}],"readerFacing":true},{"chapterKey":"chapter_4","chapterNumber":4,"title":"{{chapter_4_title}}","blocks":[{"type":"paragraph","text":"{{chapter_4_body}}"}],"readerFacing":true},{"chapterKey":"chapter_5","chapterNumber":5,"title":"{{chapter_5_title}}","blocks":[{"type":"paragraph","text":"{{chapter_5_body}}"}],"readerFacing":true},{"chapterKey":"chapter_6","chapterNumber":6,"title":"{{chapter_6_title}}","blocks":[{"type":"paragraph","text":"{{chapter_6_body}}"}],"readerFacing":true},{"chapterKey":"chapter_7","chapterNumber":7,"title":"{{chapter_7_title}}","blocks":[{"type":"paragraph","text":"{{chapter_7_body}}"}],"readerFacing":true},{"chapterKey":"chapter_8","chapterNumber":8,"title":"{{chapter_8_title}}","blocks":[{"type":"paragraph","text":"{{chapter_8_body}}"}],"readerFacing":true},{"chapterKey":"chapter_9","chapterNumber":9,"title":"{{chapter_9_title}}","blocks":[{"type":"paragraph","text":"{{chapter_9_body}}"}],"readerFacing":true},{"chapterKey":"chapter_10","chapterNumber":10,"title":"{{chapter_10_title}}","blocks":[{"type":"paragraph","text":"{{chapter_10_body}}"}],"readerFacing":true}],"closing":{"synthesis":[{"type":"paragraph","text":"{{closing_synthesis}}"}],"finalLine":"{{final_line}}"},"pdf":{"title":"Save this report","body":"{{reference_note}}"}},"evidenceTemplate":{"title":"Evidence behind your result","blocks":[{"type":"paragraph","text":"{{evidence_note}}"}]}}</v>
+      </c>
+      <c r="P11" t="str">
+        <v>active</v>
+      </c>
+      <c r="Q11" t="str">
+        <v>ready_for_import</v>
+      </c>
+      <c r="R11" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="S11" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="T11" t="str">
+        <v>{"generated_from":"fully_authored_report_first_template","deterministic":true}</v>
+      </c>
+      <c r="U11" t="str">
+        <v>report_first::signal_b_signal_c_signal_d_signal_a</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>{{assessment_key}}</v>
+      </c>
+      <c r="B12" t="str">
+        <v>{{package_version}}</v>
+      </c>
+      <c r="C12" t="str">
+        <v>{{assessment_key}}-report-first</v>
+      </c>
+      <c r="D12" t="str">
+        <v>{{package_version}}</v>
+      </c>
+      <c r="E12" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="F12" t="str">
+        <v>signal_b_signal_d_signal_a_signal_c</v>
+      </c>
+      <c r="G12" t="str">
+        <v>signal_b_signal_d_signal_a_signal_c</v>
+      </c>
+      <c r="H12" t="str">
+        <v>report_first_canonical_payload_v1</v>
+      </c>
+      <c r="I12" t="str">
+        <v>pattern_level_score_shape_neutral</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v>[]</v>
+      </c>
+      <c r="L12" t="str">
+        <v>content/authoring/{{assessment_key}}/report-first/canonical-reports/signal_b_signal_d_signal_a_signal_c.md</v>
+      </c>
+      <c r="M12" t="str">
+        <v>{{source_content_hash}}</v>
+      </c>
+      <c r="N12" t="str">
+        <v>{{content_hash}}</v>
+      </c>
+      <c r="O12" t="str">
+        <v>{"metadata":{"contractName":"report_first_canonical_payload_v1","reportModel":"report_first_canonical"},"reportKey":"signal_b_signal_d_signal_a_signal_c","patternKey":"signal_b_signal_d_signal_a_signal_c","domainKey":"{{domain_key}}","report":{"reportKey":"signal_b_signal_d_signal_a_signal_c","patternKey":"signal_b_signal_d_signal_a_signal_c","reportTitle":"{{assessment_title}} report","hero":{"title":"{{fully_authored_report_title}}","resultStatement":"{{fully_authored_result_statement}}"},"opening":[{"type":"paragraph","text":"{{editorial_introduction}}"}],"patternSummary":{"title":"Pattern at a glance","blocks":[{"type":"paragraph","text":"{{pattern_summary}}"}]},"keyInsight":{"type":"paragraph","text":"{{key_insight}}"},"chapters":[{"chapterKey":"chapter_1","chapterNumber":1,"title":"{{chapter_1_title}}","blocks":[{"type":"paragraph","text":"{{chapter_1_body}}"}],"readerFacing":true},{"chapterKey":"chapter_2","chapterNumber":2,"title":"{{chapter_2_title}}","blocks":[{"type":"paragraph","text":"{{chapter_2_body}}"}],"readerFacing":true},{"chapterKey":"chapter_3","chapterNumber":3,"title":"{{chapter_3_title}}","blocks":[{"type":"paragraph","text":"{{chapter_3_body}}"}],"readerFacing":true},{"chapterKey":"chapter_4","chapterNumber":4,"title":"{{chapter_4_title}}","blocks":[{"type":"paragraph","text":"{{chapter_4_body}}"}],"readerFacing":true},{"chapterKey":"chapter_5","chapterNumber":5,"title":"{{chapter_5_title}}","blocks":[{"type":"paragraph","text":"{{chapter_5_body}}"}],"readerFacing":true},{"chapterKey":"chapter_6","chapterNumber":6,"title":"{{chapter_6_title}}","blocks":[{"type":"paragraph","text":"{{chapter_6_body}}"}],"readerFacing":true},{"chapterKey":"chapter_7","chapterNumber":7,"title":"{{chapter_7_title}}","blocks":[{"type":"paragraph","text":"{{chapter_7_body}}"}],"readerFacing":true},{"chapterKey":"chapter_8","chapterNumber":8,"title":"{{chapter_8_title}}","blocks":[{"type":"paragraph","text":"{{chapter_8_body}}"}],"readerFacing":true},{"chapterKey":"chapter_9","chapterNumber":9,"title":"{{chapter_9_title}}","blocks":[{"type":"paragraph","text":"{{chapter_9_body}}"}],"readerFacing":true},{"chapterKey":"chapter_10","chapterNumber":10,"title":"{{chapter_10_title}}","blocks":[{"type":"paragraph","text":"{{chapter_10_body}}"}],"readerFacing":true}],"closing":{"synthesis":[{"type":"paragraph","text":"{{closing_synthesis}}"}],"finalLine":"{{final_line}}"},"pdf":{"title":"Save this report","body":"{{reference_note}}"}},"evidenceTemplate":{"title":"Evidence behind your result","blocks":[{"type":"paragraph","text":"{{evidence_note}}"}]}}</v>
+      </c>
+      <c r="P12" t="str">
+        <v>active</v>
+      </c>
+      <c r="Q12" t="str">
+        <v>ready_for_import</v>
+      </c>
+      <c r="R12" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="S12" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="T12" t="str">
+        <v>{"generated_from":"fully_authored_report_first_template","deterministic":true}</v>
+      </c>
+      <c r="U12" t="str">
+        <v>report_first::signal_b_signal_d_signal_a_signal_c</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>{{assessment_key}}</v>
+      </c>
+      <c r="B13" t="str">
+        <v>{{package_version}}</v>
+      </c>
+      <c r="C13" t="str">
+        <v>{{assessment_key}}-report-first</v>
+      </c>
+      <c r="D13" t="str">
+        <v>{{package_version}}</v>
+      </c>
+      <c r="E13" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="F13" t="str">
+        <v>signal_b_signal_d_signal_c_signal_a</v>
+      </c>
+      <c r="G13" t="str">
+        <v>signal_b_signal_d_signal_c_signal_a</v>
+      </c>
+      <c r="H13" t="str">
+        <v>report_first_canonical_payload_v1</v>
+      </c>
+      <c r="I13" t="str">
+        <v>pattern_level_score_shape_neutral</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v>[]</v>
+      </c>
+      <c r="L13" t="str">
+        <v>content/authoring/{{assessment_key}}/report-first/canonical-reports/signal_b_signal_d_signal_c_signal_a.md</v>
+      </c>
+      <c r="M13" t="str">
+        <v>{{source_content_hash}}</v>
+      </c>
+      <c r="N13" t="str">
+        <v>{{content_hash}}</v>
+      </c>
+      <c r="O13" t="str">
+        <v>{"metadata":{"contractName":"report_first_canonical_payload_v1","reportModel":"report_first_canonical"},"reportKey":"signal_b_signal_d_signal_c_signal_a","patternKey":"signal_b_signal_d_signal_c_signal_a","domainKey":"{{domain_key}}","report":{"reportKey":"signal_b_signal_d_signal_c_signal_a","patternKey":"signal_b_signal_d_signal_c_signal_a","reportTitle":"{{assessment_title}} report","hero":{"title":"{{fully_authored_report_title}}","resultStatement":"{{fully_authored_result_statement}}"},"opening":[{"type":"paragraph","text":"{{editorial_introduction}}"}],"patternSummary":{"title":"Pattern at a glance","blocks":[{"type":"paragraph","text":"{{pattern_summary}}"}]},"keyInsight":{"type":"paragraph","text":"{{key_insight}}"},"chapters":[{"chapterKey":"chapter_1","chapterNumber":1,"title":"{{chapter_1_title}}","blocks":[{"type":"paragraph","text":"{{chapter_1_body}}"}],"readerFacing":true},{"chapterKey":"chapter_2","chapterNumber":2,"title":"{{chapter_2_title}}","blocks":[{"type":"paragraph","text":"{{chapter_2_body}}"}],"readerFacing":true},{"chapterKey":"chapter_3","chapterNumber":3,"title":"{{chapter_3_title}}","blocks":[{"type":"paragraph","text":"{{chapter_3_body}}"}],"readerFacing":true},{"chapterKey":"chapter_4","chapterNumber":4,"title":"{{chapter_4_title}}","blocks":[{"type":"paragraph","text":"{{chapter_4_body}}"}],"readerFacing":true},{"chapterKey":"chapter_5","chapterNumber":5,"title":"{{chapter_5_title}}","blocks":[{"type":"paragraph","text":"{{chapter_5_body}}"}],"readerFacing":true},{"chapterKey":"chapter_6","chapterNumber":6,"title":"{{chapter_6_title}}","blocks":[{"type":"paragraph","text":"{{chapter_6_body}}"}],"readerFacing":true},{"chapterKey":"chapter_7","chapterNumber":7,"title":"{{chapter_7_title}}","blocks":[{"type":"paragraph","text":"{{chapter_7_body}}"}],"readerFacing":true},{"chapterKey":"chapter_8","chapterNumber":8,"title":"{{chapter_8_title}}","blocks":[{"type":"paragraph","text":"{{chapter_8_body}}"}],"readerFacing":true},{"chapterKey":"chapter_9","chapterNumber":9,"title":"{{chapter_9_title}}","blocks":[{"type":"paragraph","text":"{{chapter_9_body}}"}],"readerFacing":true},{"chapterKey":"chapter_10","chapterNumber":10,"title":"{{chapter_10_title}}","blocks":[{"type":"paragraph","text":"{{chapter_10_body}}"}],"readerFacing":true}],"closing":{"synthesis":[{"type":"paragraph","text":"{{closing_synthesis}}"}],"finalLine":"{{final_line}}"},"pdf":{"title":"Save this report","body":"{{reference_note}}"}},"evidenceTemplate":{"title":"Evidence behind your result","blocks":[{"type":"paragraph","text":"{{evidence_note}}"}]}}</v>
+      </c>
+      <c r="P13" t="str">
+        <v>active</v>
+      </c>
+      <c r="Q13" t="str">
+        <v>ready_for_import</v>
+      </c>
+      <c r="R13" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="S13" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="T13" t="str">
+        <v>{"generated_from":"fully_authored_report_first_template","deterministic":true}</v>
+      </c>
+      <c r="U13" t="str">
+        <v>report_first::signal_b_signal_d_signal_c_signal_a</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>{{assessment_key}}</v>
+      </c>
+      <c r="B14" t="str">
+        <v>{{package_version}}</v>
+      </c>
+      <c r="C14" t="str">
+        <v>{{assessment_key}}-report-first</v>
+      </c>
+      <c r="D14" t="str">
+        <v>{{package_version}}</v>
+      </c>
+      <c r="E14" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="F14" t="str">
+        <v>signal_c_signal_a_signal_b_signal_d</v>
+      </c>
+      <c r="G14" t="str">
+        <v>signal_c_signal_a_signal_b_signal_d</v>
+      </c>
+      <c r="H14" t="str">
+        <v>report_first_canonical_payload_v1</v>
+      </c>
+      <c r="I14" t="str">
+        <v>pattern_level_score_shape_neutral</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v>[]</v>
+      </c>
+      <c r="L14" t="str">
+        <v>content/authoring/{{assessment_key}}/report-first/canonical-reports/signal_c_signal_a_signal_b_signal_d.md</v>
+      </c>
+      <c r="M14" t="str">
+        <v>{{source_content_hash}}</v>
+      </c>
+      <c r="N14" t="str">
+        <v>{{content_hash}}</v>
+      </c>
+      <c r="O14" t="str">
+        <v>{"metadata":{"contractName":"report_first_canonical_payload_v1","reportModel":"report_first_canonical"},"reportKey":"signal_c_signal_a_signal_b_signal_d","patternKey":"signal_c_signal_a_signal_b_signal_d","domainKey":"{{domain_key}}","report":{"reportKey":"signal_c_signal_a_signal_b_signal_d","patternKey":"signal_c_signal_a_signal_b_signal_d","reportTitle":"{{assessment_title}} report","hero":{"title":"{{fully_authored_report_title}}","resultStatement":"{{fully_authored_result_statement}}"},"opening":[{"type":"paragraph","text":"{{editorial_introduction}}"}],"patternSummary":{"title":"Pattern at a glance","blocks":[{"type":"paragraph","text":"{{pattern_summary}}"}]},"keyInsight":{"type":"paragraph","text":"{{key_insight}}"},"chapters":[{"chapterKey":"chapter_1","chapterNumber":1,"title":"{{chapter_1_title}}","blocks":[{"type":"paragraph","text":"{{chapter_1_body}}"}],"readerFacing":true},{"chapterKey":"chapter_2","chapterNumber":2,"title":"{{chapter_2_title}}","blocks":[{"type":"paragraph","text":"{{chapter_2_body}}"}],"readerFacing":true},{"chapterKey":"chapter_3","chapterNumber":3,"title":"{{chapter_3_title}}","blocks":[{"type":"paragraph","text":"{{chapter_3_body}}"}],"readerFacing":true},{"chapterKey":"chapter_4","chapterNumber":4,"title":"{{chapter_4_title}}","blocks":[{"type":"paragraph","text":"{{chapter_4_body}}"}],"readerFacing":true},{"chapterKey":"chapter_5","chapterNumber":5,"title":"{{chapter_5_title}}","blocks":[{"type":"paragraph","text":"{{chapter_5_body}}"}],"readerFacing":true},{"chapterKey":"chapter_6","chapterNumber":6,"title":"{{chapter_6_title}}","blocks":[{"type":"paragraph","text":"{{chapter_6_body}}"}],"readerFacing":true},{"chapterKey":"chapter_7","chapterNumber":7,"title":"{{chapter_7_title}}","blocks":[{"type":"paragraph","text":"{{chapter_7_body}}"}],"readerFacing":true},{"chapterKey":"chapter_8","chapterNumber":8,"title":"{{chapter_8_title}}","blocks":[{"type":"paragraph","text":"{{chapter_8_body}}"}],"readerFacing":true},{"chapterKey":"chapter_9","chapterNumber":9,"title":"{{chapter_9_title}}","blocks":[{"type":"paragraph","text":"{{chapter_9_body}}"}],"readerFacing":true},{"chapterKey":"chapter_10","chapterNumber":10,"title":"{{chapter_10_title}}","blocks":[{"type":"paragraph","text":"{{chapter_10_body}}"}],"readerFacing":true}],"closing":{"synthesis":[{"type":"paragraph","text":"{{closing_synthesis}}"}],"finalLine":"{{final_line}}"},"pdf":{"title":"Save this report","body":"{{reference_note}}"}},"evidenceTemplate":{"title":"Evidence behind your result","blocks":[{"type":"paragraph","text":"{{evidence_note}}"}]}}</v>
+      </c>
+      <c r="P14" t="str">
+        <v>active</v>
+      </c>
+      <c r="Q14" t="str">
+        <v>ready_for_import</v>
+      </c>
+      <c r="R14" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="S14" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="T14" t="str">
+        <v>{"generated_from":"fully_authored_report_first_template","deterministic":true}</v>
+      </c>
+      <c r="U14" t="str">
+        <v>report_first::signal_c_signal_a_signal_b_signal_d</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>{{assessment_key}}</v>
+      </c>
+      <c r="B15" t="str">
+        <v>{{package_version}}</v>
+      </c>
+      <c r="C15" t="str">
+        <v>{{assessment_key}}-report-first</v>
+      </c>
+      <c r="D15" t="str">
+        <v>{{package_version}}</v>
+      </c>
+      <c r="E15" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="F15" t="str">
+        <v>signal_c_signal_a_signal_d_signal_b</v>
+      </c>
+      <c r="G15" t="str">
+        <v>signal_c_signal_a_signal_d_signal_b</v>
+      </c>
+      <c r="H15" t="str">
+        <v>report_first_canonical_payload_v1</v>
+      </c>
+      <c r="I15" t="str">
+        <v>pattern_level_score_shape_neutral</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v>[]</v>
+      </c>
+      <c r="L15" t="str">
+        <v>content/authoring/{{assessment_key}}/report-first/canonical-reports/signal_c_signal_a_signal_d_signal_b.md</v>
+      </c>
+      <c r="M15" t="str">
+        <v>{{source_content_hash}}</v>
+      </c>
+      <c r="N15" t="str">
+        <v>{{content_hash}}</v>
+      </c>
+      <c r="O15" t="str">
+        <v>{"metadata":{"contractName":"report_first_canonical_payload_v1","reportModel":"report_first_canonical"},"reportKey":"signal_c_signal_a_signal_d_signal_b","patternKey":"signal_c_signal_a_signal_d_signal_b","domainKey":"{{domain_key}}","report":{"reportKey":"signal_c_signal_a_signal_d_signal_b","patternKey":"signal_c_signal_a_signal_d_signal_b","reportTitle":"{{assessment_title}} report","hero":{"title":"{{fully_authored_report_title}}","resultStatement":"{{fully_authored_result_statement}}"},"opening":[{"type":"paragraph","text":"{{editorial_introduction}}"}],"patternSummary":{"title":"Pattern at a glance","blocks":[{"type":"paragraph","text":"{{pattern_summary}}"}]},"keyInsight":{"type":"paragraph","text":"{{key_insight}}"},"chapters":[{"chapterKey":"chapter_1","chapterNumber":1,"title":"{{chapter_1_title}}","blocks":[{"type":"paragraph","text":"{{chapter_1_body}}"}],"readerFacing":true},{"chapterKey":"chapter_2","chapterNumber":2,"title":"{{chapter_2_title}}","blocks":[{"type":"paragraph","text":"{{chapter_2_body}}"}],"readerFacing":true},{"chapterKey":"chapter_3","chapterNumber":3,"title":"{{chapter_3_title}}","blocks":[{"type":"paragraph","text":"{{chapter_3_body}}"}],"readerFacing":true},{"chapterKey":"chapter_4","chapterNumber":4,"title":"{{chapter_4_title}}","blocks":[{"type":"paragraph","text":"{{chapter_4_body}}"}],"readerFacing":true},{"chapterKey":"chapter_5","chapterNumber":5,"title":"{{chapter_5_title}}","blocks":[{"type":"paragraph","text":"{{chapter_5_body}}"}],"readerFacing":true},{"chapterKey":"chapter_6","chapterNumber":6,"title":"{{chapter_6_title}}","blocks":[{"type":"paragraph","text":"{{chapter_6_body}}"}],"readerFacing":true},{"chapterKey":"chapter_7","chapterNumber":7,"title":"{{chapter_7_title}}","blocks":[{"type":"paragraph","text":"{{chapter_7_body}}"}],"readerFacing":true},{"chapterKey":"chapter_8","chapterNumber":8,"title":"{{chapter_8_title}}","blocks":[{"type":"paragraph","text":"{{chapter_8_body}}"}],"readerFacing":true},{"chapterKey":"chapter_9","chapterNumber":9,"title":"{{chapter_9_title}}","blocks":[{"type":"paragraph","text":"{{chapter_9_body}}"}],"readerFacing":true},{"chapterKey":"chapter_10","chapterNumber":10,"title":"{{chapter_10_title}}","blocks":[{"type":"paragraph","text":"{{chapter_10_body}}"}],"readerFacing":true}],"closing":{"synthesis":[{"type":"paragraph","text":"{{closing_synthesis}}"}],"finalLine":"{{final_line}}"},"pdf":{"title":"Save this report","body":"{{reference_note}}"}},"evidenceTemplate":{"title":"Evidence behind your result","blocks":[{"type":"paragraph","text":"{{evidence_note}}"}]}}</v>
+      </c>
+      <c r="P15" t="str">
+        <v>active</v>
+      </c>
+      <c r="Q15" t="str">
+        <v>ready_for_import</v>
+      </c>
+      <c r="R15" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="S15" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="T15" t="str">
+        <v>{"generated_from":"fully_authored_report_first_template","deterministic":true}</v>
+      </c>
+      <c r="U15" t="str">
+        <v>report_first::signal_c_signal_a_signal_d_signal_b</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>{{assessment_key}}</v>
+      </c>
+      <c r="B16" t="str">
+        <v>{{package_version}}</v>
+      </c>
+      <c r="C16" t="str">
+        <v>{{assessment_key}}-report-first</v>
+      </c>
+      <c r="D16" t="str">
+        <v>{{package_version}}</v>
+      </c>
+      <c r="E16" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="F16" t="str">
+        <v>signal_c_signal_b_signal_a_signal_d</v>
+      </c>
+      <c r="G16" t="str">
+        <v>signal_c_signal_b_signal_a_signal_d</v>
+      </c>
+      <c r="H16" t="str">
+        <v>report_first_canonical_payload_v1</v>
+      </c>
+      <c r="I16" t="str">
+        <v>pattern_level_score_shape_neutral</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v>[]</v>
+      </c>
+      <c r="L16" t="str">
+        <v>content/authoring/{{assessment_key}}/report-first/canonical-reports/signal_c_signal_b_signal_a_signal_d.md</v>
+      </c>
+      <c r="M16" t="str">
+        <v>{{source_content_hash}}</v>
+      </c>
+      <c r="N16" t="str">
+        <v>{{content_hash}}</v>
+      </c>
+      <c r="O16" t="str">
+        <v>{"metadata":{"contractName":"report_first_canonical_payload_v1","reportModel":"report_first_canonical"},"reportKey":"signal_c_signal_b_signal_a_signal_d","patternKey":"signal_c_signal_b_signal_a_signal_d","domainKey":"{{domain_key}}","report":{"reportKey":"signal_c_signal_b_signal_a_signal_d","patternKey":"signal_c_signal_b_signal_a_signal_d","reportTitle":"{{assessment_title}} report","hero":{"title":"{{fully_authored_report_title}}","resultStatement":"{{fully_authored_result_statement}}"},"opening":[{"type":"paragraph","text":"{{editorial_introduction}}"}],"patternSummary":{"title":"Pattern at a glance","blocks":[{"type":"paragraph","text":"{{pattern_summary}}"}]},"keyInsight":{"type":"paragraph","text":"{{key_insight}}"},"chapters":[{"chapterKey":"chapter_1","chapterNumber":1,"title":"{{chapter_1_title}}","blocks":[{"type":"paragraph","text":"{{chapter_1_body}}"}],"readerFacing":true},{"chapterKey":"chapter_2","chapterNumber":2,"title":"{{chapter_2_title}}","blocks":[{"type":"paragraph","text":"{{chapter_2_body}}"}],"readerFacing":true},{"chapterKey":"chapter_3","chapterNumber":3,"title":"{{chapter_3_title}}","blocks":[{"type":"paragraph","text":"{{chapter_3_body}}"}],"readerFacing":true},{"chapterKey":"chapter_4","chapterNumber":4,"title":"{{chapter_4_title}}","blocks":[{"type":"paragraph","text":"{{chapter_4_body}}"}],"readerFacing":true},{"chapterKey":"chapter_5","chapterNumber":5,"title":"{{chapter_5_title}}","blocks":[{"type":"paragraph","text":"{{chapter_5_body}}"}],"readerFacing":true},{"chapterKey":"chapter_6","chapterNumber":6,"title":"{{chapter_6_title}}","blocks":[{"type":"paragraph","text":"{{chapter_6_body}}"}],"readerFacing":true},{"chapterKey":"chapter_7","chapterNumber":7,"title":"{{chapter_7_title}}","blocks":[{"type":"paragraph","text":"{{chapter_7_body}}"}],"readerFacing":true},{"chapterKey":"chapter_8","chapterNumber":8,"title":"{{chapter_8_title}}","blocks":[{"type":"paragraph","text":"{{chapter_8_body}}"}],"readerFacing":true},{"chapterKey":"chapter_9","chapterNumber":9,"title":"{{chapter_9_title}}","blocks":[{"type":"paragraph","text":"{{chapter_9_body}}"}],"readerFacing":true},{"chapterKey":"chapter_10","chapterNumber":10,"title":"{{chapter_10_title}}","blocks":[{"type":"paragraph","text":"{{chapter_10_body}}"}],"readerFacing":true}],"closing":{"synthesis":[{"type":"paragraph","text":"{{closing_synthesis}}"}],"finalLine":"{{final_line}}"},"pdf":{"title":"Save this report","body":"{{reference_note}}"}},"evidenceTemplate":{"title":"Evidence behind your result","blocks":[{"type":"paragraph","text":"{{evidence_note}}"}]}}</v>
+      </c>
+      <c r="P16" t="str">
+        <v>active</v>
+      </c>
+      <c r="Q16" t="str">
+        <v>ready_for_import</v>
+      </c>
+      <c r="R16" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="S16" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="T16" t="str">
+        <v>{"generated_from":"fully_authored_report_first_template","deterministic":true}</v>
+      </c>
+      <c r="U16" t="str">
+        <v>report_first::signal_c_signal_b_signal_a_signal_d</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>{{assessment_key}}</v>
+      </c>
+      <c r="B17" t="str">
+        <v>{{package_version}}</v>
+      </c>
+      <c r="C17" t="str">
+        <v>{{assessment_key}}-report-first</v>
+      </c>
+      <c r="D17" t="str">
+        <v>{{package_version}}</v>
+      </c>
+      <c r="E17" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="F17" t="str">
+        <v>signal_c_signal_b_signal_d_signal_a</v>
+      </c>
+      <c r="G17" t="str">
+        <v>signal_c_signal_b_signal_d_signal_a</v>
+      </c>
+      <c r="H17" t="str">
+        <v>report_first_canonical_payload_v1</v>
+      </c>
+      <c r="I17" t="str">
+        <v>pattern_level_score_shape_neutral</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v>[]</v>
+      </c>
+      <c r="L17" t="str">
+        <v>content/authoring/{{assessment_key}}/report-first/canonical-reports/signal_c_signal_b_signal_d_signal_a.md</v>
+      </c>
+      <c r="M17" t="str">
+        <v>{{source_content_hash}}</v>
+      </c>
+      <c r="N17" t="str">
+        <v>{{content_hash}}</v>
+      </c>
+      <c r="O17" t="str">
+        <v>{"metadata":{"contractName":"report_first_canonical_payload_v1","reportModel":"report_first_canonical"},"reportKey":"signal_c_signal_b_signal_d_signal_a","patternKey":"signal_c_signal_b_signal_d_signal_a","domainKey":"{{domain_key}}","report":{"reportKey":"signal_c_signal_b_signal_d_signal_a","patternKey":"signal_c_signal_b_signal_d_signal_a","reportTitle":"{{assessment_title}} report","hero":{"title":"{{fully_authored_report_title}}","resultStatement":"{{fully_authored_result_statement}}"},"opening":[{"type":"paragraph","text":"{{editorial_introduction}}"}],"patternSummary":{"title":"Pattern at a glance","blocks":[{"type":"paragraph","text":"{{pattern_summary}}"}]},"keyInsight":{"type":"paragraph","text":"{{key_insight}}"},"chapters":[{"chapterKey":"chapter_1","chapterNumber":1,"title":"{{chapter_1_title}}","blocks":[{"type":"paragraph","text":"{{chapter_1_body}}"}],"readerFacing":true},{"chapterKey":"chapter_2","chapterNumber":2,"title":"{{chapter_2_title}}","blocks":[{"type":"paragraph","text":"{{chapter_2_body}}"}],"readerFacing":true},{"chapterKey":"chapter_3","chapterNumber":3,"title":"{{chapter_3_title}}","blocks":[{"type":"paragraph","text":"{{chapter_3_body}}"}],"readerFacing":true},{"chapterKey":"chapter_4","chapterNumber":4,"title":"{{chapter_4_title}}","blocks":[{"type":"paragraph","text":"{{chapter_4_body}}"}],"readerFacing":true},{"chapterKey":"chapter_5","chapterNumber":5,"title":"{{chapter_5_title}}","blocks":[{"type":"paragraph","text":"{{chapter_5_body}}"}],"readerFacing":true},{"chapterKey":"chapter_6","chapterNumber":6,"title":"{{chapter_6_title}}","blocks":[{"type":"paragraph","text":"{{chapter_6_body}}"}],"readerFacing":true},{"chapterKey":"chapter_7","chapterNumber":7,"title":"{{chapter_7_title}}","blocks":[{"type":"paragraph","text":"{{chapter_7_body}}"}],"readerFacing":true},{"chapterKey":"chapter_8","chapterNumber":8,"title":"{{chapter_8_title}}","blocks":[{"type":"paragraph","text":"{{chapter_8_body}}"}],"readerFacing":true},{"chapterKey":"chapter_9","chapterNumber":9,"title":"{{chapter_9_title}}","blocks":[{"type":"paragraph","text":"{{chapter_9_body}}"}],"readerFacing":true},{"chapterKey":"chapter_10","chapterNumber":10,"title":"{{chapter_10_title}}","blocks":[{"type":"paragraph","text":"{{chapter_10_body}}"}],"readerFacing":true}],"closing":{"synthesis":[{"type":"paragraph","text":"{{closing_synthesis}}"}],"finalLine":"{{final_line}}"},"pdf":{"title":"Save this report","body":"{{reference_note}}"}},"evidenceTemplate":{"title":"Evidence behind your result","blocks":[{"type":"paragraph","text":"{{evidence_note}}"}]}}</v>
+      </c>
+      <c r="P17" t="str">
+        <v>active</v>
+      </c>
+      <c r="Q17" t="str">
+        <v>ready_for_import</v>
+      </c>
+      <c r="R17" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="S17" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="T17" t="str">
+        <v>{"generated_from":"fully_authored_report_first_template","deterministic":true}</v>
+      </c>
+      <c r="U17" t="str">
+        <v>report_first::signal_c_signal_b_signal_d_signal_a</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>{{assessment_key}}</v>
+      </c>
+      <c r="B18" t="str">
+        <v>{{package_version}}</v>
+      </c>
+      <c r="C18" t="str">
+        <v>{{assessment_key}}-report-first</v>
+      </c>
+      <c r="D18" t="str">
+        <v>{{package_version}}</v>
+      </c>
+      <c r="E18" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="F18" t="str">
+        <v>signal_c_signal_d_signal_a_signal_b</v>
+      </c>
+      <c r="G18" t="str">
+        <v>signal_c_signal_d_signal_a_signal_b</v>
+      </c>
+      <c r="H18" t="str">
+        <v>report_first_canonical_payload_v1</v>
+      </c>
+      <c r="I18" t="str">
+        <v>pattern_level_score_shape_neutral</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v>[]</v>
+      </c>
+      <c r="L18" t="str">
+        <v>content/authoring/{{assessment_key}}/report-first/canonical-reports/signal_c_signal_d_signal_a_signal_b.md</v>
+      </c>
+      <c r="M18" t="str">
+        <v>{{source_content_hash}}</v>
+      </c>
+      <c r="N18" t="str">
+        <v>{{content_hash}}</v>
+      </c>
+      <c r="O18" t="str">
+        <v>{"metadata":{"contractName":"report_first_canonical_payload_v1","reportModel":"report_first_canonical"},"reportKey":"signal_c_signal_d_signal_a_signal_b","patternKey":"signal_c_signal_d_signal_a_signal_b","domainKey":"{{domain_key}}","report":{"reportKey":"signal_c_signal_d_signal_a_signal_b","patternKey":"signal_c_signal_d_signal_a_signal_b","reportTitle":"{{assessment_title}} report","hero":{"title":"{{fully_authored_report_title}}","resultStatement":"{{fully_authored_result_statement}}"},"opening":[{"type":"paragraph","text":"{{editorial_introduction}}"}],"patternSummary":{"title":"Pattern at a glance","blocks":[{"type":"paragraph","text":"{{pattern_summary}}"}]},"keyInsight":{"type":"paragraph","text":"{{key_insight}}"},"chapters":[{"chapterKey":"chapter_1","chapterNumber":1,"title":"{{chapter_1_title}}","blocks":[{"type":"paragraph","text":"{{chapter_1_body}}"}],"readerFacing":true},{"chapterKey":"chapter_2","chapterNumber":2,"title":"{{chapter_2_title}}","blocks":[{"type":"paragraph","text":"{{chapter_2_body}}"}],"readerFacing":true},{"chapterKey":"chapter_3","chapterNumber":3,"title":"{{chapter_3_title}}","blocks":[{"type":"paragraph","text":"{{chapter_3_body}}"}],"readerFacing":true},{"chapterKey":"chapter_4","chapterNumber":4,"title":"{{chapter_4_title}}","blocks":[{"type":"paragraph","text":"{{chapter_4_body}}"}],"readerFacing":true},{"chapterKey":"chapter_5","chapterNumber":5,"title":"{{chapter_5_title}}","blocks":[{"type":"paragraph","text":"{{chapter_5_body}}"}],"readerFacing":true},{"chapterKey":"chapter_6","chapterNumber":6,"title":"{{chapter_6_title}}","blocks":[{"type":"paragraph","text":"{{chapter_6_body}}"}],"readerFacing":true},{"chapterKey":"chapter_7","chapterNumber":7,"title":"{{chapter_7_title}}","blocks":[{"type":"paragraph","text":"{{chapter_7_body}}"}],"readerFacing":true},{"chapterKey":"chapter_8","chapterNumber":8,"title":"{{chapter_8_title}}","blocks":[{"type":"paragraph","text":"{{chapter_8_body}}"}],"readerFacing":true},{"chapterKey":"chapter_9","chapterNumber":9,"title":"{{chapter_9_title}}","blocks":[{"type":"paragraph","text":"{{chapter_9_body}}"}],"readerFacing":true},{"chapterKey":"chapter_10","chapterNumber":10,"title":"{{chapter_10_title}}","blocks":[{"type":"paragraph","text":"{{chapter_10_body}}"}],"readerFacing":true}],"closing":{"synthesis":[{"type":"paragraph","text":"{{closing_synthesis}}"}],"finalLine":"{{final_line}}"},"pdf":{"title":"Save this report","body":"{{reference_note}}"}},"evidenceTemplate":{"title":"Evidence behind your result","blocks":[{"type":"paragraph","text":"{{evidence_note}}"}]}}</v>
+      </c>
+      <c r="P18" t="str">
+        <v>active</v>
+      </c>
+      <c r="Q18" t="str">
+        <v>ready_for_import</v>
+      </c>
+      <c r="R18" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="S18" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="T18" t="str">
+        <v>{"generated_from":"fully_authored_report_first_template","deterministic":true}</v>
+      </c>
+      <c r="U18" t="str">
+        <v>report_first::signal_c_signal_d_signal_a_signal_b</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>{{assessment_key}}</v>
+      </c>
+      <c r="B19" t="str">
+        <v>{{package_version}}</v>
+      </c>
+      <c r="C19" t="str">
+        <v>{{assessment_key}}-report-first</v>
+      </c>
+      <c r="D19" t="str">
+        <v>{{package_version}}</v>
+      </c>
+      <c r="E19" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="F19" t="str">
+        <v>signal_c_signal_d_signal_b_signal_a</v>
+      </c>
+      <c r="G19" t="str">
+        <v>signal_c_signal_d_signal_b_signal_a</v>
+      </c>
+      <c r="H19" t="str">
+        <v>report_first_canonical_payload_v1</v>
+      </c>
+      <c r="I19" t="str">
+        <v>pattern_level_score_shape_neutral</v>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v>[]</v>
+      </c>
+      <c r="L19" t="str">
+        <v>content/authoring/{{assessment_key}}/report-first/canonical-reports/signal_c_signal_d_signal_b_signal_a.md</v>
+      </c>
+      <c r="M19" t="str">
+        <v>{{source_content_hash}}</v>
+      </c>
+      <c r="N19" t="str">
+        <v>{{content_hash}}</v>
+      </c>
+      <c r="O19" t="str">
+        <v>{"metadata":{"contractName":"report_first_canonical_payload_v1","reportModel":"report_first_canonical"},"reportKey":"signal_c_signal_d_signal_b_signal_a","patternKey":"signal_c_signal_d_signal_b_signal_a","domainKey":"{{domain_key}}","report":{"reportKey":"signal_c_signal_d_signal_b_signal_a","patternKey":"signal_c_signal_d_signal_b_signal_a","reportTitle":"{{assessment_title}} report","hero":{"title":"{{fully_authored_report_title}}","resultStatement":"{{fully_authored_result_statement}}"},"opening":[{"type":"paragraph","text":"{{editorial_introduction}}"}],"patternSummary":{"title":"Pattern at a glance","blocks":[{"type":"paragraph","text":"{{pattern_summary}}"}]},"keyInsight":{"type":"paragraph","text":"{{key_insight}}"},"chapters":[{"chapterKey":"chapter_1","chapterNumber":1,"title":"{{chapter_1_title}}","blocks":[{"type":"paragraph","text":"{{chapter_1_body}}"}],"readerFacing":true},{"chapterKey":"chapter_2","chapterNumber":2,"title":"{{chapter_2_title}}","blocks":[{"type":"paragraph","text":"{{chapter_2_body}}"}],"readerFacing":true},{"chapterKey":"chapter_3","chapterNumber":3,"title":"{{chapter_3_title}}","blocks":[{"type":"paragraph","text":"{{chapter_3_body}}"}],"readerFacing":true},{"chapterKey":"chapter_4","chapterNumber":4,"title":"{{chapter_4_title}}","blocks":[{"type":"paragraph","text":"{{chapter_4_body}}"}],"readerFacing":true},{"chapterKey":"chapter_5","chapterNumber":5,"title":"{{chapter_5_title}}","blocks":[{"type":"paragraph","text":"{{chapter_5_body}}"}],"readerFacing":true},{"chapterKey":"chapter_6","chapterNumber":6,"title":"{{chapter_6_title}}","blocks":[{"type":"paragraph","text":"{{chapter_6_body}}"}],"readerFacing":true},{"chapterKey":"chapter_7","chapterNumber":7,"title":"{{chapter_7_title}}","blocks":[{"type":"paragraph","text":"{{chapter_7_body}}"}],"readerFacing":true},{"chapterKey":"chapter_8","chapterNumber":8,"title":"{{chapter_8_title}}","blocks":[{"type":"paragraph","text":"{{chapter_8_body}}"}],"readerFacing":true},{"chapterKey":"chapter_9","chapterNumber":9,"title":"{{chapter_9_title}}","blocks":[{"type":"paragraph","text":"{{chapter_9_body}}"}],"readerFacing":true},{"chapterKey":"chapter_10","chapterNumber":10,"title":"{{chapter_10_title}}","blocks":[{"type":"paragraph","text":"{{chapter_10_body}}"}],"readerFacing":true}],"closing":{"synthesis":[{"type":"paragraph","text":"{{closing_synthesis}}"}],"finalLine":"{{final_line}}"},"pdf":{"title":"Save this report","body":"{{reference_note}}"}},"evidenceTemplate":{"title":"Evidence behind your result","blocks":[{"type":"paragraph","text":"{{evidence_note}}"}]}}</v>
+      </c>
+      <c r="P19" t="str">
+        <v>active</v>
+      </c>
+      <c r="Q19" t="str">
+        <v>ready_for_import</v>
+      </c>
+      <c r="R19" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="S19" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="T19" t="str">
+        <v>{"generated_from":"fully_authored_report_first_template","deterministic":true}</v>
+      </c>
+      <c r="U19" t="str">
+        <v>report_first::signal_c_signal_d_signal_b_signal_a</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>{{assessment_key}}</v>
+      </c>
+      <c r="B20" t="str">
+        <v>{{package_version}}</v>
+      </c>
+      <c r="C20" t="str">
+        <v>{{assessment_key}}-report-first</v>
+      </c>
+      <c r="D20" t="str">
+        <v>{{package_version}}</v>
+      </c>
+      <c r="E20" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="F20" t="str">
+        <v>signal_d_signal_a_signal_b_signal_c</v>
+      </c>
+      <c r="G20" t="str">
+        <v>signal_d_signal_a_signal_b_signal_c</v>
+      </c>
+      <c r="H20" t="str">
+        <v>report_first_canonical_payload_v1</v>
+      </c>
+      <c r="I20" t="str">
+        <v>pattern_level_score_shape_neutral</v>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v>[]</v>
+      </c>
+      <c r="L20" t="str">
+        <v>content/authoring/{{assessment_key}}/report-first/canonical-reports/signal_d_signal_a_signal_b_signal_c.md</v>
+      </c>
+      <c r="M20" t="str">
+        <v>{{source_content_hash}}</v>
+      </c>
+      <c r="N20" t="str">
+        <v>{{content_hash}}</v>
+      </c>
+      <c r="O20" t="str">
+        <v>{"metadata":{"contractName":"report_first_canonical_payload_v1","reportModel":"report_first_canonical"},"reportKey":"signal_d_signal_a_signal_b_signal_c","patternKey":"signal_d_signal_a_signal_b_signal_c","domainKey":"{{domain_key}}","report":{"reportKey":"signal_d_signal_a_signal_b_signal_c","patternKey":"signal_d_signal_a_signal_b_signal_c","reportTitle":"{{assessment_title}} report","hero":{"title":"{{fully_authored_report_title}}","resultStatement":"{{fully_authored_result_statement}}"},"opening":[{"type":"paragraph","text":"{{editorial_introduction}}"}],"patternSummary":{"title":"Pattern at a glance","blocks":[{"type":"paragraph","text":"{{pattern_summary}}"}]},"keyInsight":{"type":"paragraph","text":"{{key_insight}}"},"chapters":[{"chapterKey":"chapter_1","chapterNumber":1,"title":"{{chapter_1_title}}","blocks":[{"type":"paragraph","text":"{{chapter_1_body}}"}],"readerFacing":true},{"chapterKey":"chapter_2","chapterNumber":2,"title":"{{chapter_2_title}}","blocks":[{"type":"paragraph","text":"{{chapter_2_body}}"}],"readerFacing":true},{"chapterKey":"chapter_3","chapterNumber":3,"title":"{{chapter_3_title}}","blocks":[{"type":"paragraph","text":"{{chapter_3_body}}"}],"readerFacing":true},{"chapterKey":"chapter_4","chapterNumber":4,"title":"{{chapter_4_title}}","blocks":[{"type":"paragraph","text":"{{chapter_4_body}}"}],"readerFacing":true},{"chapterKey":"chapter_5","chapterNumber":5,"title":"{{chapter_5_title}}","blocks":[{"type":"paragraph","text":"{{chapter_5_body}}"}],"readerFacing":true},{"chapterKey":"chapter_6","chapterNumber":6,"title":"{{chapter_6_title}}","blocks":[{"type":"paragraph","text":"{{chapter_6_body}}"}],"readerFacing":true},{"chapterKey":"chapter_7","chapterNumber":7,"title":"{{chapter_7_title}}","blocks":[{"type":"paragraph","text":"{{chapter_7_body}}"}],"readerFacing":true},{"chapterKey":"chapter_8","chapterNumber":8,"title":"{{chapter_8_title}}","blocks":[{"type":"paragraph","text":"{{chapter_8_body}}"}],"readerFacing":true},{"chapterKey":"chapter_9","chapterNumber":9,"title":"{{chapter_9_title}}","blocks":[{"type":"paragraph","text":"{{chapter_9_body}}"}],"readerFacing":true},{"chapterKey":"chapter_10","chapterNumber":10,"title":"{{chapter_10_title}}","blocks":[{"type":"paragraph","text":"{{chapter_10_body}}"}],"readerFacing":true}],"closing":{"synthesis":[{"type":"paragraph","text":"{{closing_synthesis}}"}],"finalLine":"{{final_line}}"},"pdf":{"title":"Save this report","body":"{{reference_note}}"}},"evidenceTemplate":{"title":"Evidence behind your result","blocks":[{"type":"paragraph","text":"{{evidence_note}}"}]}}</v>
+      </c>
+      <c r="P20" t="str">
+        <v>active</v>
+      </c>
+      <c r="Q20" t="str">
+        <v>ready_for_import</v>
+      </c>
+      <c r="R20" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="S20" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="T20" t="str">
+        <v>{"generated_from":"fully_authored_report_first_template","deterministic":true}</v>
+      </c>
+      <c r="U20" t="str">
+        <v>report_first::signal_d_signal_a_signal_b_signal_c</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>{{assessment_key}}</v>
+      </c>
+      <c r="B21" t="str">
+        <v>{{package_version}}</v>
+      </c>
+      <c r="C21" t="str">
+        <v>{{assessment_key}}-report-first</v>
+      </c>
+      <c r="D21" t="str">
+        <v>{{package_version}}</v>
+      </c>
+      <c r="E21" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="F21" t="str">
+        <v>signal_d_signal_a_signal_c_signal_b</v>
+      </c>
+      <c r="G21" t="str">
+        <v>signal_d_signal_a_signal_c_signal_b</v>
+      </c>
+      <c r="H21" t="str">
+        <v>report_first_canonical_payload_v1</v>
+      </c>
+      <c r="I21" t="str">
+        <v>pattern_level_score_shape_neutral</v>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <v>[]</v>
+      </c>
+      <c r="L21" t="str">
+        <v>content/authoring/{{assessment_key}}/report-first/canonical-reports/signal_d_signal_a_signal_c_signal_b.md</v>
+      </c>
+      <c r="M21" t="str">
+        <v>{{source_content_hash}}</v>
+      </c>
+      <c r="N21" t="str">
+        <v>{{content_hash}}</v>
+      </c>
+      <c r="O21" t="str">
+        <v>{"metadata":{"contractName":"report_first_canonical_payload_v1","reportModel":"report_first_canonical"},"reportKey":"signal_d_signal_a_signal_c_signal_b","patternKey":"signal_d_signal_a_signal_c_signal_b","domainKey":"{{domain_key}}","report":{"reportKey":"signal_d_signal_a_signal_c_signal_b","patternKey":"signal_d_signal_a_signal_c_signal_b","reportTitle":"{{assessment_title}} report","hero":{"title":"{{fully_authored_report_title}}","resultStatement":"{{fully_authored_result_statement}}"},"opening":[{"type":"paragraph","text":"{{editorial_introduction}}"}],"patternSummary":{"title":"Pattern at a glance","blocks":[{"type":"paragraph","text":"{{pattern_summary}}"}]},"keyInsight":{"type":"paragraph","text":"{{key_insight}}"},"chapters":[{"chapterKey":"chapter_1","chapterNumber":1,"title":"{{chapter_1_title}}","blocks":[{"type":"paragraph","text":"{{chapter_1_body}}"}],"readerFacing":true},{"chapterKey":"chapter_2","chapterNumber":2,"title":"{{chapter_2_title}}","blocks":[{"type":"paragraph","text":"{{chapter_2_body}}"}],"readerFacing":true},{"chapterKey":"chapter_3","chapterNumber":3,"title":"{{chapter_3_title}}","blocks":[{"type":"paragraph","text":"{{chapter_3_body}}"}],"readerFacing":true},{"chapterKey":"chapter_4","chapterNumber":4,"title":"{{chapter_4_title}}","blocks":[{"type":"paragraph","text":"{{chapter_4_body}}"}],"readerFacing":true},{"chapterKey":"chapter_5","chapterNumber":5,"title":"{{chapter_5_title}}","blocks":[{"type":"paragraph","text":"{{chapter_5_body}}"}],"readerFacing":true},{"chapterKey":"chapter_6","chapterNumber":6,"title":"{{chapter_6_title}}","blocks":[{"type":"paragraph","text":"{{chapter_6_body}}"}],"readerFacing":true},{"chapterKey":"chapter_7","chapterNumber":7,"title":"{{chapter_7_title}}","blocks":[{"type":"paragraph","text":"{{chapter_7_body}}"}],"readerFacing":true},{"chapterKey":"chapter_8","chapterNumber":8,"title":"{{chapter_8_title}}","blocks":[{"type":"paragraph","text":"{{chapter_8_body}}"}],"readerFacing":true},{"chapterKey":"chapter_9","chapterNumber":9,"title":"{{chapter_9_title}}","blocks":[{"type":"paragraph","text":"{{chapter_9_body}}"}],"readerFacing":true},{"chapterKey":"chapter_10","chapterNumber":10,"title":"{{chapter_10_title}}","blocks":[{"type":"paragraph","text":"{{chapter_10_body}}"}],"readerFacing":true}],"closing":{"synthesis":[{"type":"paragraph","text":"{{closing_synthesis}}"}],"finalLine":"{{final_line}}"},"pdf":{"title":"Save this report","body":"{{reference_note}}"}},"evidenceTemplate":{"title":"Evidence behind your result","blocks":[{"type":"paragraph","text":"{{evidence_note}}"}]}}</v>
+      </c>
+      <c r="P21" t="str">
+        <v>active</v>
+      </c>
+      <c r="Q21" t="str">
+        <v>ready_for_import</v>
+      </c>
+      <c r="R21" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="S21" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="T21" t="str">
+        <v>{"generated_from":"fully_authored_report_first_template","deterministic":true}</v>
+      </c>
+      <c r="U21" t="str">
+        <v>report_first::signal_d_signal_a_signal_c_signal_b</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>{{assessment_key}}</v>
+      </c>
+      <c r="B22" t="str">
+        <v>{{package_version}}</v>
+      </c>
+      <c r="C22" t="str">
+        <v>{{assessment_key}}-report-first</v>
+      </c>
+      <c r="D22" t="str">
+        <v>{{package_version}}</v>
+      </c>
+      <c r="E22" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="F22" t="str">
+        <v>signal_d_signal_b_signal_a_signal_c</v>
+      </c>
+      <c r="G22" t="str">
+        <v>signal_d_signal_b_signal_a_signal_c</v>
+      </c>
+      <c r="H22" t="str">
+        <v>report_first_canonical_payload_v1</v>
+      </c>
+      <c r="I22" t="str">
+        <v>pattern_level_score_shape_neutral</v>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v>[]</v>
+      </c>
+      <c r="L22" t="str">
+        <v>content/authoring/{{assessment_key}}/report-first/canonical-reports/signal_d_signal_b_signal_a_signal_c.md</v>
+      </c>
+      <c r="M22" t="str">
+        <v>{{source_content_hash}}</v>
+      </c>
+      <c r="N22" t="str">
+        <v>{{content_hash}}</v>
+      </c>
+      <c r="O22" t="str">
+        <v>{"metadata":{"contractName":"report_first_canonical_payload_v1","reportModel":"report_first_canonical"},"reportKey":"signal_d_signal_b_signal_a_signal_c","patternKey":"signal_d_signal_b_signal_a_signal_c","domainKey":"{{domain_key}}","report":{"reportKey":"signal_d_signal_b_signal_a_signal_c","patternKey":"signal_d_signal_b_signal_a_signal_c","reportTitle":"{{assessment_title}} report","hero":{"title":"{{fully_authored_report_title}}","resultStatement":"{{fully_authored_result_statement}}"},"opening":[{"type":"paragraph","text":"{{editorial_introduction}}"}],"patternSummary":{"title":"Pattern at a glance","blocks":[{"type":"paragraph","text":"{{pattern_summary}}"}]},"keyInsight":{"type":"paragraph","text":"{{key_insight}}"},"chapters":[{"chapterKey":"chapter_1","chapterNumber":1,"title":"{{chapter_1_title}}","blocks":[{"type":"paragraph","text":"{{chapter_1_body}}"}],"readerFacing":true},{"chapterKey":"chapter_2","chapterNumber":2,"title":"{{chapter_2_title}}","blocks":[{"type":"paragraph","text":"{{chapter_2_body}}"}],"readerFacing":true},{"chapterKey":"chapter_3","chapterNumber":3,"title":"{{chapter_3_title}}","blocks":[{"type":"paragraph","text":"{{chapter_3_body}}"}],"readerFacing":true},{"chapterKey":"chapter_4","chapterNumber":4,"title":"{{chapter_4_title}}","blocks":[{"type":"paragraph","text":"{{chapter_4_body}}"}],"readerFacing":true},{"chapterKey":"chapter_5","chapterNumber":5,"title":"{{chapter_5_title}}","blocks":[{"type":"paragraph","text":"{{chapter_5_body}}"}],"readerFacing":true},{"chapterKey":"chapter_6","chapterNumber":6,"title":"{{chapter_6_title}}","blocks":[{"type":"paragraph","text":"{{chapter_6_body}}"}],"readerFacing":true},{"chapterKey":"chapter_7","chapterNumber":7,"title":"{{chapter_7_title}}","blocks":[{"type":"paragraph","text":"{{chapter_7_body}}"}],"readerFacing":true},{"chapterKey":"chapter_8","chapterNumber":8,"title":"{{chapter_8_title}}","blocks":[{"type":"paragraph","text":"{{chapter_8_body}}"}],"readerFacing":true},{"chapterKey":"chapter_9","chapterNumber":9,"title":"{{chapter_9_title}}","blocks":[{"type":"paragraph","text":"{{chapter_9_body}}"}],"readerFacing":true},{"chapterKey":"chapter_10","chapterNumber":10,"title":"{{chapter_10_title}}","blocks":[{"type":"paragraph","text":"{{chapter_10_body}}"}],"readerFacing":true}],"closing":{"synthesis":[{"type":"paragraph","text":"{{closing_synthesis}}"}],"finalLine":"{{final_line}}"},"pdf":{"title":"Save this report","body":"{{reference_note}}"}},"evidenceTemplate":{"title":"Evidence behind your result","blocks":[{"type":"paragraph","text":"{{evidence_note}}"}]}}</v>
+      </c>
+      <c r="P22" t="str">
+        <v>active</v>
+      </c>
+      <c r="Q22" t="str">
+        <v>ready_for_import</v>
+      </c>
+      <c r="R22" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="S22" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="T22" t="str">
+        <v>{"generated_from":"fully_authored_report_first_template","deterministic":true}</v>
+      </c>
+      <c r="U22" t="str">
+        <v>report_first::signal_d_signal_b_signal_a_signal_c</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>{{assessment_key}}</v>
+      </c>
+      <c r="B23" t="str">
+        <v>{{package_version}}</v>
+      </c>
+      <c r="C23" t="str">
+        <v>{{assessment_key}}-report-first</v>
+      </c>
+      <c r="D23" t="str">
+        <v>{{package_version}}</v>
+      </c>
+      <c r="E23" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="F23" t="str">
+        <v>signal_d_signal_b_signal_c_signal_a</v>
+      </c>
+      <c r="G23" t="str">
+        <v>signal_d_signal_b_signal_c_signal_a</v>
+      </c>
+      <c r="H23" t="str">
+        <v>report_first_canonical_payload_v1</v>
+      </c>
+      <c r="I23" t="str">
+        <v>pattern_level_score_shape_neutral</v>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <v>[]</v>
+      </c>
+      <c r="L23" t="str">
+        <v>content/authoring/{{assessment_key}}/report-first/canonical-reports/signal_d_signal_b_signal_c_signal_a.md</v>
+      </c>
+      <c r="M23" t="str">
+        <v>{{source_content_hash}}</v>
+      </c>
+      <c r="N23" t="str">
+        <v>{{content_hash}}</v>
+      </c>
+      <c r="O23" t="str">
+        <v>{"metadata":{"contractName":"report_first_canonical_payload_v1","reportModel":"report_first_canonical"},"reportKey":"signal_d_signal_b_signal_c_signal_a","patternKey":"signal_d_signal_b_signal_c_signal_a","domainKey":"{{domain_key}}","report":{"reportKey":"signal_d_signal_b_signal_c_signal_a","patternKey":"signal_d_signal_b_signal_c_signal_a","reportTitle":"{{assessment_title}} report","hero":{"title":"{{fully_authored_report_title}}","resultStatement":"{{fully_authored_result_statement}}"},"opening":[{"type":"paragraph","text":"{{editorial_introduction}}"}],"patternSummary":{"title":"Pattern at a glance","blocks":[{"type":"paragraph","text":"{{pattern_summary}}"}]},"keyInsight":{"type":"paragraph","text":"{{key_insight}}"},"chapters":[{"chapterKey":"chapter_1","chapterNumber":1,"title":"{{chapter_1_title}}","blocks":[{"type":"paragraph","text":"{{chapter_1_body}}"}],"readerFacing":true},{"chapterKey":"chapter_2","chapterNumber":2,"title":"{{chapter_2_title}}","blocks":[{"type":"paragraph","text":"{{chapter_2_body}}"}],"readerFacing":true},{"chapterKey":"chapter_3","chapterNumber":3,"title":"{{chapter_3_title}}","blocks":[{"type":"paragraph","text":"{{chapter_3_body}}"}],"readerFacing":true},{"chapterKey":"chapter_4","chapterNumber":4,"title":"{{chapter_4_title}}","blocks":[{"type":"paragraph","text":"{{chapter_4_body}}"}],"readerFacing":true},{"chapterKey":"chapter_5","chapterNumber":5,"title":"{{chapter_5_title}}","blocks":[{"type":"paragraph","text":"{{chapter_5_body}}"}],"readerFacing":true},{"chapterKey":"chapter_6","chapterNumber":6,"title":"{{chapter_6_title}}","blocks":[{"type":"paragraph","text":"{{chapter_6_body}}"}],"readerFacing":true},{"chapterKey":"chapter_7","chapterNumber":7,"title":"{{chapter_7_title}}","blocks":[{"type":"paragraph","text":"{{chapter_7_body}}"}],"readerFacing":true},{"chapterKey":"chapter_8","chapterNumber":8,"title":"{{chapter_8_title}}","blocks":[{"type":"paragraph","text":"{{chapter_8_body}}"}],"readerFacing":true},{"chapterKey":"chapter_9","chapterNumber":9,"title":"{{chapter_9_title}}","blocks":[{"type":"paragraph","text":"{{chapter_9_body}}"}],"readerFacing":true},{"chapterKey":"chapter_10","chapterNumber":10,"title":"{{chapter_10_title}}","blocks":[{"type":"paragraph","text":"{{chapter_10_body}}"}],"readerFacing":true}],"closing":{"synthesis":[{"type":"paragraph","text":"{{closing_synthesis}}"}],"finalLine":"{{final_line}}"},"pdf":{"title":"Save this report","body":"{{reference_note}}"}},"evidenceTemplate":{"title":"Evidence behind your result","blocks":[{"type":"paragraph","text":"{{evidence_note}}"}]}}</v>
+      </c>
+      <c r="P23" t="str">
+        <v>active</v>
+      </c>
+      <c r="Q23" t="str">
+        <v>ready_for_import</v>
+      </c>
+      <c r="R23" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="S23" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="T23" t="str">
+        <v>{"generated_from":"fully_authored_report_first_template","deterministic":true}</v>
+      </c>
+      <c r="U23" t="str">
+        <v>report_first::signal_d_signal_b_signal_c_signal_a</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>{{assessment_key}}</v>
+      </c>
+      <c r="B24" t="str">
+        <v>{{package_version}}</v>
+      </c>
+      <c r="C24" t="str">
+        <v>{{assessment_key}}-report-first</v>
+      </c>
+      <c r="D24" t="str">
+        <v>{{package_version}}</v>
+      </c>
+      <c r="E24" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="F24" t="str">
+        <v>signal_d_signal_c_signal_a_signal_b</v>
+      </c>
+      <c r="G24" t="str">
+        <v>signal_d_signal_c_signal_a_signal_b</v>
+      </c>
+      <c r="H24" t="str">
+        <v>report_first_canonical_payload_v1</v>
+      </c>
+      <c r="I24" t="str">
+        <v>pattern_level_score_shape_neutral</v>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <v>[]</v>
+      </c>
+      <c r="L24" t="str">
+        <v>content/authoring/{{assessment_key}}/report-first/canonical-reports/signal_d_signal_c_signal_a_signal_b.md</v>
+      </c>
+      <c r="M24" t="str">
+        <v>{{source_content_hash}}</v>
+      </c>
+      <c r="N24" t="str">
+        <v>{{content_hash}}</v>
+      </c>
+      <c r="O24" t="str">
+        <v>{"metadata":{"contractName":"report_first_canonical_payload_v1","reportModel":"report_first_canonical"},"reportKey":"signal_d_signal_c_signal_a_signal_b","patternKey":"signal_d_signal_c_signal_a_signal_b","domainKey":"{{domain_key}}","report":{"reportKey":"signal_d_signal_c_signal_a_signal_b","patternKey":"signal_d_signal_c_signal_a_signal_b","reportTitle":"{{assessment_title}} report","hero":{"title":"{{fully_authored_report_title}}","resultStatement":"{{fully_authored_result_statement}}"},"opening":[{"type":"paragraph","text":"{{editorial_introduction}}"}],"patternSummary":{"title":"Pattern at a glance","blocks":[{"type":"paragraph","text":"{{pattern_summary}}"}]},"keyInsight":{"type":"paragraph","text":"{{key_insight}}"},"chapters":[{"chapterKey":"chapter_1","chapterNumber":1,"title":"{{chapter_1_title}}","blocks":[{"type":"paragraph","text":"{{chapter_1_body}}"}],"readerFacing":true},{"chapterKey":"chapter_2","chapterNumber":2,"title":"{{chapter_2_title}}","blocks":[{"type":"paragraph","text":"{{chapter_2_body}}"}],"readerFacing":true},{"chapterKey":"chapter_3","chapterNumber":3,"title":"{{chapter_3_title}}","blocks":[{"type":"paragraph","text":"{{chapter_3_body}}"}],"readerFacing":true},{"chapterKey":"chapter_4","chapterNumber":4,"title":"{{chapter_4_title}}","blocks":[{"type":"paragraph","text":"{{chapter_4_body}}"}],"readerFacing":true},{"chapterKey":"chapter_5","chapterNumber":5,"title":"{{chapter_5_title}}","blocks":[{"type":"paragraph","text":"{{chapter_5_body}}"}],"readerFacing":true},{"chapterKey":"chapter_6","chapterNumber":6,"title":"{{chapter_6_title}}","blocks":[{"type":"paragraph","text":"{{chapter_6_body}}"}],"readerFacing":true},{"chapterKey":"chapter_7","chapterNumber":7,"title":"{{chapter_7_title}}","blocks":[{"type":"paragraph","text":"{{chapter_7_body}}"}],"readerFacing":true},{"chapterKey":"chapter_8","chapterNumber":8,"title":"{{chapter_8_title}}","blocks":[{"type":"paragraph","text":"{{chapter_8_body}}"}],"readerFacing":true},{"chapterKey":"chapter_9","chapterNumber":9,"title":"{{chapter_9_title}}","blocks":[{"type":"paragraph","text":"{{chapter_9_body}}"}],"readerFacing":true},{"chapterKey":"chapter_10","chapterNumber":10,"title":"{{chapter_10_title}}","blocks":[{"type":"paragraph","text":"{{chapter_10_body}}"}],"readerFacing":true}],"closing":{"synthesis":[{"type":"paragraph","text":"{{closing_synthesis}}"}],"finalLine":"{{final_line}}"},"pdf":{"title":"Save this report","body":"{{reference_note}}"}},"evidenceTemplate":{"title":"Evidence behind your result","blocks":[{"type":"paragraph","text":"{{evidence_note}}"}]}}</v>
+      </c>
+      <c r="P24" t="str">
+        <v>active</v>
+      </c>
+      <c r="Q24" t="str">
+        <v>ready_for_import</v>
+      </c>
+      <c r="R24" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="S24" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="T24" t="str">
+        <v>{"generated_from":"fully_authored_report_first_template","deterministic":true}</v>
+      </c>
+      <c r="U24" t="str">
+        <v>report_first::signal_d_signal_c_signal_a_signal_b</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>{{assessment_key}}</v>
+      </c>
+      <c r="B25" t="str">
+        <v>{{package_version}}</v>
+      </c>
+      <c r="C25" t="str">
+        <v>{{assessment_key}}-report-first</v>
+      </c>
+      <c r="D25" t="str">
+        <v>{{package_version}}</v>
+      </c>
+      <c r="E25" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="F25" t="str">
+        <v>signal_d_signal_c_signal_b_signal_a</v>
+      </c>
+      <c r="G25" t="str">
+        <v>signal_d_signal_c_signal_b_signal_a</v>
+      </c>
+      <c r="H25" t="str">
+        <v>report_first_canonical_payload_v1</v>
+      </c>
+      <c r="I25" t="str">
+        <v>pattern_level_score_shape_neutral</v>
+      </c>
+      <c r="J25" t="str">
+        <v/>
+      </c>
+      <c r="K25" t="str">
+        <v>[]</v>
+      </c>
+      <c r="L25" t="str">
+        <v>content/authoring/{{assessment_key}}/report-first/canonical-reports/signal_d_signal_c_signal_b_signal_a.md</v>
+      </c>
+      <c r="M25" t="str">
+        <v>{{source_content_hash}}</v>
+      </c>
+      <c r="N25" t="str">
+        <v>{{content_hash}}</v>
+      </c>
+      <c r="O25" t="str">
+        <v>{"metadata":{"contractName":"report_first_canonical_payload_v1","reportModel":"report_first_canonical"},"reportKey":"signal_d_signal_c_signal_b_signal_a","patternKey":"signal_d_signal_c_signal_b_signal_a","domainKey":"{{domain_key}}","report":{"reportKey":"signal_d_signal_c_signal_b_signal_a","patternKey":"signal_d_signal_c_signal_b_signal_a","reportTitle":"{{assessment_title}} report","hero":{"title":"{{fully_authored_report_title}}","resultStatement":"{{fully_authored_result_statement}}"},"opening":[{"type":"paragraph","text":"{{editorial_introduction}}"}],"patternSummary":{"title":"Pattern at a glance","blocks":[{"type":"paragraph","text":"{{pattern_summary}}"}]},"keyInsight":{"type":"paragraph","text":"{{key_insight}}"},"chapters":[{"chapterKey":"chapter_1","chapterNumber":1,"title":"{{chapter_1_title}}","blocks":[{"type":"paragraph","text":"{{chapter_1_body}}"}],"readerFacing":true},{"chapterKey":"chapter_2","chapterNumber":2,"title":"{{chapter_2_title}}","blocks":[{"type":"paragraph","text":"{{chapter_2_body}}"}],"readerFacing":true},{"chapterKey":"chapter_3","chapterNumber":3,"title":"{{chapter_3_title}}","blocks":[{"type":"paragraph","text":"{{chapter_3_body}}"}],"readerFacing":true},{"chapterKey":"chapter_4","chapterNumber":4,"title":"{{chapter_4_title}}","blocks":[{"type":"paragraph","text":"{{chapter_4_body}}"}],"readerFacing":true},{"chapterKey":"chapter_5","chapterNumber":5,"title":"{{chapter_5_title}}","blocks":[{"type":"paragraph","text":"{{chapter_5_body}}"}],"readerFacing":true},{"chapterKey":"chapter_6","chapterNumber":6,"title":"{{chapter_6_title}}","blocks":[{"type":"paragraph","text":"{{chapter_6_body}}"}],"readerFacing":true},{"chapterKey":"chapter_7","chapterNumber":7,"title":"{{chapter_7_title}}","blocks":[{"type":"paragraph","text":"{{chapter_7_body}}"}],"readerFacing":true},{"chapterKey":"chapter_8","chapterNumber":8,"title":"{{chapter_8_title}}","blocks":[{"type":"paragraph","text":"{{chapter_8_body}}"}],"readerFacing":true},{"chapterKey":"chapter_9","chapterNumber":9,"title":"{{chapter_9_title}}","blocks":[{"type":"paragraph","text":"{{chapter_9_body}}"}],"readerFacing":true},{"chapterKey":"chapter_10","chapterNumber":10,"title":"{{chapter_10_title}}","blocks":[{"type":"paragraph","text":"{{chapter_10_body}}"}],"readerFacing":true}],"closing":{"synthesis":[{"type":"paragraph","text":"{{closing_synthesis}}"}],"finalLine":"{{final_line}}"},"pdf":{"title":"Save this report","body":"{{reference_note}}"}},"evidenceTemplate":{"title":"Evidence behind your result","blocks":[{"type":"paragraph","text":"{{evidence_note}}"}]}}</v>
+      </c>
+      <c r="P25" t="str">
+        <v>active</v>
+      </c>
+      <c r="Q25" t="str">
+        <v>ready_for_import</v>
+      </c>
+      <c r="R25" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="S25" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="T25" t="str">
+        <v>{"generated_from":"fully_authored_report_first_template","deterministic":true}</v>
+      </c>
+      <c r="U25" t="str">
+        <v>report_first::signal_d_signal_c_signal_b_signal_a</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:U25"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:U25"/>
+  </ignoredErrors>
+</worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="UTF-8" standalone="yes"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"><dimension ref="A1:F2"/><cols><col min="1" max="1" width="14.83203125" customWidth="1"/><col min="2" max="2" width="16.83203125" customWidth="1"/><col min="3" max="3" width="18.83203125" customWidth="1"/><col min="4" max="4" width="17.83203125" customWidth="1"/><col min="5" max="5" width="14.83203125" customWidth="1"/><col min="6" max="6" width="14.83203125" customWidth="1"/></cols><sheetData><row r="1"><c r="A1" s="1" s="1" t="str"><v>domain_key</v></c><c r="B1" s="1" s="1" t="str"><v>question_key</v></c><c r="C1" s="1" s="1" t="str"><v>question_order</v></c><c r="D1" s="1" s="1" t="str"><v>question_text</v></c><c r="E1" s="1" s="1" t="str"><v>status</v></c><c r="F1" s="1" s="1" t="str"><v>lookup_key</v></c></row><row r="2"><c r="A2" t="str"><v>{{domain_key}}</v></c><c r="B2" t="str"><v>{{question_key}}</v></c><c r="C2"><v>1</v></c><c r="D2" t="str"><v>{{question_text}}</v></c><c r="E2" t="str"><v>active</v></c><c r="F2" t="str"><v>question::{{question_key}}</v></c></row></sheetData><autoFilter ref="A1:F2"/><ignoredErrors><ignoredError numberStoredAsText="1" sqref="A1:F2"/></ignoredErrors></worksheet>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <cols>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="18.83203125" customWidth="1"/>
+    <col min="4" max="4" width="17.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>domain_key</v>
+      </c>
+      <c r="B1" t="str">
+        <v>question_key</v>
+      </c>
+      <c r="C1" t="str">
+        <v>question_order</v>
+      </c>
+      <c r="D1" t="str">
+        <v>question_text</v>
+      </c>
+      <c r="E1" t="str">
+        <v>status</v>
+      </c>
+      <c r="F1" t="str">
+        <v>lookup_key</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="B2" t="str">
+        <v>{{question_key}}</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="str">
+        <v>{{question_text}}</v>
+      </c>
+      <c r="E2" t="str">
+        <v>active</v>
+      </c>
+      <c r="F2" t="str">
+        <v>question::{{question_key}}</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F2"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F2"/>
+  </ignoredErrors>
+</worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="UTF-8" standalone="yes"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"><dimension ref="A1:H5"/><cols><col min="1" max="1" width="14.83203125" customWidth="1"/><col min="2" max="2" width="16.83203125" customWidth="1"/><col min="3" max="3" width="14.83203125" customWidth="1"/><col min="4" max="4" width="16.83203125" customWidth="1"/><col min="5" max="5" width="15.83203125" customWidth="1"/><col min="6" max="6" width="14.83203125" customWidth="1"/><col min="7" max="7" width="14.83203125" customWidth="1"/><col min="8" max="8" width="14.83203125" customWidth="1"/></cols><sheetData><row r="1"><c r="A1" s="1" s="1" t="str"><v>domain_key</v></c><c r="B1" s="1" s="1" t="str"><v>question_key</v></c><c r="C1" s="1" s="1" t="str"><v>option_key</v></c><c r="D1" s="1" s="1" t="str"><v>option_order</v></c><c r="E1" s="1" s="1" t="str"><v>option_text</v></c><c r="F1" s="1" s="1" t="str"><v>is_scored</v></c><c r="G1" s="1" s="1" t="str"><v>status</v></c><c r="H1" s="1" s="1" t="str"><v>lookup_key</v></c></row><row r="2"><c r="A2" t="str"><v>{{domain_key}}</v></c><c r="B2" t="str"><v>{{question_key}}</v></c><c r="C2" t="str"><v>{{option_1_key}}</v></c><c r="D2"><v>1</v></c><c r="E2" t="str"><v>{{option_1_text}}</v></c><c r="F2" t="str"><v>TRUE</v></c><c r="G2" t="str"><v>active</v></c><c r="H2" t="str"><v>option::{{question_key}}::1</v></c></row><row r="3"><c r="A3" t="str"><v>{{domain_key}}</v></c><c r="B3" t="str"><v>{{question_key}}</v></c><c r="C3" t="str"><v>{{option_2_key}}</v></c><c r="D3"><v>2</v></c><c r="E3" t="str"><v>{{option_2_text}}</v></c><c r="F3" t="str"><v>TRUE</v></c><c r="G3" t="str"><v>active</v></c><c r="H3" t="str"><v>option::{{question_key}}::2</v></c></row><row r="4"><c r="A4" t="str"><v>{{domain_key}}</v></c><c r="B4" t="str"><v>{{question_key}}</v></c><c r="C4" t="str"><v>{{option_3_key}}</v></c><c r="D4"><v>3</v></c><c r="E4" t="str"><v>{{option_3_text}}</v></c><c r="F4" t="str"><v>TRUE</v></c><c r="G4" t="str"><v>active</v></c><c r="H4" t="str"><v>option::{{question_key}}::3</v></c></row><row r="5"><c r="A5" t="str"><v>{{domain_key}}</v></c><c r="B5" t="str"><v>{{question_key}}</v></c><c r="C5" t="str"><v>{{option_4_key}}</v></c><c r="D5"><v>4</v></c><c r="E5" t="str"><v>{{option_4_text}}</v></c><c r="F5" t="str"><v>TRUE</v></c><c r="G5" t="str"><v>active</v></c><c r="H5" t="str"><v>option::{{question_key}}::4</v></c></row></sheetData><autoFilter ref="A1:H5"/><ignoredErrors><ignoredError numberStoredAsText="1" sqref="A1:H5"/></ignoredErrors></worksheet>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H5"/>
+  <cols>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="16.83203125" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>domain_key</v>
+      </c>
+      <c r="B1" t="str">
+        <v>question_key</v>
+      </c>
+      <c r="C1" t="str">
+        <v>option_key</v>
+      </c>
+      <c r="D1" t="str">
+        <v>option_order</v>
+      </c>
+      <c r="E1" t="str">
+        <v>option_text</v>
+      </c>
+      <c r="F1" t="str">
+        <v>is_scored</v>
+      </c>
+      <c r="G1" t="str">
+        <v>status</v>
+      </c>
+      <c r="H1" t="str">
+        <v>lookup_key</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="B2" t="str">
+        <v>{{question_key}}</v>
+      </c>
+      <c r="C2" t="str">
+        <v>{{option_1_key}}</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="str">
+        <v>{{option_1_text}}</v>
+      </c>
+      <c r="F2" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G2" t="str">
+        <v>active</v>
+      </c>
+      <c r="H2" t="str">
+        <v>option::{{question_key}}::1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="B3" t="str">
+        <v>{{question_key}}</v>
+      </c>
+      <c r="C3" t="str">
+        <v>{{option_2_key}}</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3" t="str">
+        <v>{{option_2_text}}</v>
+      </c>
+      <c r="F3" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G3" t="str">
+        <v>active</v>
+      </c>
+      <c r="H3" t="str">
+        <v>option::{{question_key}}::2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="B4" t="str">
+        <v>{{question_key}}</v>
+      </c>
+      <c r="C4" t="str">
+        <v>{{option_3_key}}</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4" t="str">
+        <v>{{option_3_text}}</v>
+      </c>
+      <c r="F4" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G4" t="str">
+        <v>active</v>
+      </c>
+      <c r="H4" t="str">
+        <v>option::{{question_key}}::3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="B5" t="str">
+        <v>{{question_key}}</v>
+      </c>
+      <c r="C5" t="str">
+        <v>{{option_4_key}}</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5" t="str">
+        <v>{{option_4_text}}</v>
+      </c>
+      <c r="F5" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="G5" t="str">
+        <v>active</v>
+      </c>
+      <c r="H5" t="str">
+        <v>option::{{question_key}}::4</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H5"/>
+  </ignoredErrors>
+</worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="UTF-8" standalone="yes"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"><dimension ref="A1:G5"/><cols><col min="1" max="1" width="14.83203125" customWidth="1"/><col min="2" max="2" width="16.83203125" customWidth="1"/><col min="3" max="3" width="14.83203125" customWidth="1"/><col min="4" max="4" width="14.83203125" customWidth="1"/><col min="5" max="5" width="14.83203125" customWidth="1"/><col min="6" max="6" width="14.83203125" customWidth="1"/><col min="7" max="7" width="14.83203125" customWidth="1"/></cols><sheetData><row r="1"><c r="A1" s="1" s="1" t="str"><v>domain_key</v></c><c r="B1" s="1" s="1" t="str"><v>question_key</v></c><c r="C1" s="1" s="1" t="str"><v>option_key</v></c><c r="D1" s="1" s="1" t="str"><v>signal_key</v></c><c r="E1" s="1" s="1" t="str"><v>weight</v></c><c r="F1" s="1" s="1" t="str"><v>status</v></c><c r="G1" s="1" s="1" t="str"><v>lookup_key</v></c></row><row r="2"><c r="A2" t="str"><v>{{domain_key}}</v></c><c r="B2" t="str"><v>{{question_key}}</v></c><c r="C2" t="str"><v>{{option_1_key}}</v></c><c r="D2" t="str"><v>signal_a</v></c><c r="E2"><v>1</v></c><c r="F2" t="str"><v>active</v></c><c r="G2" t="str"><v>weight::{{question_key}}::1::signal_a</v></c></row><row r="3"><c r="A3" t="str"><v>{{domain_key}}</v></c><c r="B3" t="str"><v>{{question_key}}</v></c><c r="C3" t="str"><v>{{option_2_key}}</v></c><c r="D3" t="str"><v>signal_b</v></c><c r="E3"><v>1</v></c><c r="F3" t="str"><v>active</v></c><c r="G3" t="str"><v>weight::{{question_key}}::2::signal_b</v></c></row><row r="4"><c r="A4" t="str"><v>{{domain_key}}</v></c><c r="B4" t="str"><v>{{question_key}}</v></c><c r="C4" t="str"><v>{{option_3_key}}</v></c><c r="D4" t="str"><v>signal_c</v></c><c r="E4"><v>1</v></c><c r="F4" t="str"><v>active</v></c><c r="G4" t="str"><v>weight::{{question_key}}::3::signal_c</v></c></row><row r="5"><c r="A5" t="str"><v>{{domain_key}}</v></c><c r="B5" t="str"><v>{{question_key}}</v></c><c r="C5" t="str"><v>{{option_4_key}}</v></c><c r="D5" t="str"><v>signal_d</v></c><c r="E5"><v>1</v></c><c r="F5" t="str"><v>active</v></c><c r="G5" t="str"><v>weight::{{question_key}}::4::signal_d</v></c></row></sheetData><autoFilter ref="A1:G5"/><ignoredErrors><ignoredError numberStoredAsText="1" sqref="A1:G5"/></ignoredErrors></worksheet>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G5"/>
+  <cols>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>domain_key</v>
+      </c>
+      <c r="B1" t="str">
+        <v>question_key</v>
+      </c>
+      <c r="C1" t="str">
+        <v>option_key</v>
+      </c>
+      <c r="D1" t="str">
+        <v>signal_key</v>
+      </c>
+      <c r="E1" t="str">
+        <v>weight</v>
+      </c>
+      <c r="F1" t="str">
+        <v>status</v>
+      </c>
+      <c r="G1" t="str">
+        <v>lookup_key</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="B2" t="str">
+        <v>{{question_key}}</v>
+      </c>
+      <c r="C2" t="str">
+        <v>{{option_1_key}}</v>
+      </c>
+      <c r="D2" t="str">
+        <v>signal_a</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" t="str">
+        <v>active</v>
+      </c>
+      <c r="G2" t="str">
+        <v>weight::{{question_key}}::1::signal_a</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="B3" t="str">
+        <v>{{question_key}}</v>
+      </c>
+      <c r="C3" t="str">
+        <v>{{option_2_key}}</v>
+      </c>
+      <c r="D3" t="str">
+        <v>signal_b</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3" t="str">
+        <v>active</v>
+      </c>
+      <c r="G3" t="str">
+        <v>weight::{{question_key}}::2::signal_b</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="B4" t="str">
+        <v>{{question_key}}</v>
+      </c>
+      <c r="C4" t="str">
+        <v>{{option_3_key}}</v>
+      </c>
+      <c r="D4" t="str">
+        <v>signal_c</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4" t="str">
+        <v>active</v>
+      </c>
+      <c r="G4" t="str">
+        <v>weight::{{question_key}}::3::signal_c</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="B5" t="str">
+        <v>{{question_key}}</v>
+      </c>
+      <c r="C5" t="str">
+        <v>{{option_4_key}}</v>
+      </c>
+      <c r="D5" t="str">
+        <v>signal_d</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5" t="str">
+        <v>active</v>
+      </c>
+      <c r="G5" t="str">
+        <v>weight::{{question_key}}::4::signal_d</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G5"/>
+  </ignoredErrors>
+</worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="UTF-8" standalone="yes"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"><dimension ref="A1:I2"/><cols><col min="1" max="1" width="14.83203125" customWidth="1"/><col min="2" max="2" width="15.83203125" customWidth="1"/><col min="3" max="3" width="16.83203125" customWidth="1"/><col min="4" max="4" width="21.83203125" customWidth="1"/><col min="5" max="5" width="16.83203125" customWidth="1"/><col min="6" max="6" width="27.83203125" customWidth="1"/><col min="7" max="7" width="14.83203125" customWidth="1"/><col min="8" max="8" width="14.83203125" customWidth="1"/><col min="9" max="9" width="14.83203125" customWidth="1"/></cols><sheetData><row r="1"><c r="A1" s="1" s="1" t="str"><v>domain_key</v></c><c r="B1" s="1" s="1" t="str"><v>section_key</v></c><c r="C1" s="1" s="1" t="str"><v>domain_title</v></c><c r="D1" s="1" s="1" t="str"><v>domain_definition</v></c><c r="E1" s="1" s="1" t="str"><v>domain_scope</v></c><c r="F1" s="1" s="1" t="str"><v>interpretation_guidance</v></c><c r="G1" s="1" s="1" t="str"><v>intro_note</v></c><c r="H1" s="1" s="1" t="str"><v>status</v></c><c r="I1" s="1" s="1" t="str"><v>lookup_key</v></c></row><row r="2"><c r="A2" t="str"><v>{{domain_key}}</v></c><c r="B2" t="str"><v>context</v></c><c r="C2" t="str"><v>{{domain_title}}</v></c><c r="D2" t="str"><v>{{domain_definition}}</v></c><c r="E2" t="str"><v>{{domain_scope}}</v></c><c r="F2" t="str"><v>{{interpretation_guidance}}</v></c><c r="G2" t="str"><v>{{intro_note}}</v></c><c r="H2" t="str"><v>active</v></c><c r="I2" t="str"><v>context::{{domain_key}}</v></c></row></sheetData><autoFilter ref="A1:I2"/><ignoredErrors><ignoredError numberStoredAsText="1" sqref="A1:I2"/></ignoredErrors></worksheet>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I2"/>
+  <cols>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" customWidth="1"/>
+    <col min="4" max="4" width="21.83203125" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1"/>
+    <col min="6" max="6" width="27.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>domain_key</v>
+      </c>
+      <c r="B1" t="str">
+        <v>section_key</v>
+      </c>
+      <c r="C1" t="str">
+        <v>domain_title</v>
+      </c>
+      <c r="D1" t="str">
+        <v>domain_definition</v>
+      </c>
+      <c r="E1" t="str">
+        <v>domain_scope</v>
+      </c>
+      <c r="F1" t="str">
+        <v>interpretation_guidance</v>
+      </c>
+      <c r="G1" t="str">
+        <v>intro_note</v>
+      </c>
+      <c r="H1" t="str">
+        <v>status</v>
+      </c>
+      <c r="I1" t="str">
+        <v>lookup_key</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="B2" t="str">
+        <v>context</v>
+      </c>
+      <c r="C2" t="str">
+        <v>{{domain_title}}</v>
+      </c>
+      <c r="D2" t="str">
+        <v>{{domain_definition}}</v>
+      </c>
+      <c r="E2" t="str">
+        <v>{{domain_scope}}</v>
+      </c>
+      <c r="F2" t="str">
+        <v>{{interpretation_guidance}}</v>
+      </c>
+      <c r="G2" t="str">
+        <v>{{intro_note}}</v>
+      </c>
+      <c r="H2" t="str">
+        <v>active</v>
+      </c>
+      <c r="I2" t="str">
+        <v>context::{{domain_key}}</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I2"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I2"/>
+  </ignoredErrors>
+</worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="UTF-8" standalone="yes"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"><dimension ref="A1:P1"/><cols><col min="1" max="1" width="14.83203125" customWidth="1"/><col min="2" max="2" width="15.83203125" customWidth="1"/><col min="3" max="3" width="15.83203125" customWidth="1"/><col min="4" max="4" width="21.83203125" customWidth="1"/><col min="5" max="5" width="21.83203125" customWidth="1"/><col min="6" max="6" width="21.83203125" customWidth="1"/><col min="7" max="7" width="21.83203125" customWidth="1"/><col min="8" max="8" width="21.83203125" customWidth="1"/><col min="9" max="9" width="23.83203125" customWidth="1"/><col min="10" max="10" width="23.83203125" customWidth="1"/><col min="11" max="11" width="17.83203125" customWidth="1"/><col min="12" max="12" width="17.83203125" customWidth="1"/><col min="13" max="13" width="17.83203125" customWidth="1"/><col min="14" max="14" width="17.83203125" customWidth="1"/><col min="15" max="15" width="14.83203125" customWidth="1"/><col min="16" max="16" width="14.83203125" customWidth="1"/></cols><sheetData><row r="1"><c r="A1" s="1" s="1" t="str"><v>domain_key</v></c><c r="B1" s="1" s="1" t="str"><v>pattern_key</v></c><c r="C1" s="1" s="1" t="str"><v>score_shape</v></c><c r="D1" s="1" s="1" t="str"><v>rank_1_signal_key</v></c><c r="E1" s="1" s="1" t="str"><v>rank_2_signal_key</v></c><c r="F1" s="1" s="1" t="str"><v>rank_3_signal_key</v></c><c r="G1" s="1" s="1" t="str"><v>rank_4_signal_key</v></c><c r="H1" s="1" s="1" t="str"><v>orientation_title</v></c><c r="I1" s="1" s="1" t="str"><v>orientation_summary</v></c><c r="J1" s="1" s="1" t="str"><v>score_shape_summary</v></c><c r="K1" s="1" s="1" t="str"><v>rank_1_phrase</v></c><c r="L1" s="1" s="1" t="str"><v>rank_2_phrase</v></c><c r="M1" s="1" s="1" t="str"><v>rank_3_phrase</v></c><c r="N1" s="1" s="1" t="str"><v>rank_4_phrase</v></c><c r="O1" s="1" s="1" t="str"><v>status</v></c><c r="P1" s="1" s="1" t="str"><v>lookup_key</v></c></row></sheetData><autoFilter ref="A1:P1"/><ignoredErrors><ignoredError numberStoredAsText="1" sqref="A1:P1"/></ignoredErrors></worksheet>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P1"/>
+  <cols>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="21.83203125" customWidth="1"/>
+    <col min="5" max="5" width="21.83203125" customWidth="1"/>
+    <col min="6" max="6" width="21.83203125" customWidth="1"/>
+    <col min="7" max="7" width="21.83203125" customWidth="1"/>
+    <col min="8" max="8" width="21.83203125" customWidth="1"/>
+    <col min="9" max="9" width="23.83203125" customWidth="1"/>
+    <col min="10" max="10" width="23.83203125" customWidth="1"/>
+    <col min="11" max="11" width="17.83203125" customWidth="1"/>
+    <col min="12" max="12" width="17.83203125" customWidth="1"/>
+    <col min="13" max="13" width="17.83203125" customWidth="1"/>
+    <col min="14" max="14" width="17.83203125" customWidth="1"/>
+    <col min="15" max="15" width="14.83203125" customWidth="1"/>
+    <col min="16" max="16" width="14.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>domain_key</v>
+      </c>
+      <c r="B1" t="str">
+        <v>pattern_key</v>
+      </c>
+      <c r="C1" t="str">
+        <v>score_shape</v>
+      </c>
+      <c r="D1" t="str">
+        <v>rank_1_signal_key</v>
+      </c>
+      <c r="E1" t="str">
+        <v>rank_2_signal_key</v>
+      </c>
+      <c r="F1" t="str">
+        <v>rank_3_signal_key</v>
+      </c>
+      <c r="G1" t="str">
+        <v>rank_4_signal_key</v>
+      </c>
+      <c r="H1" t="str">
+        <v>orientation_title</v>
+      </c>
+      <c r="I1" t="str">
+        <v>orientation_summary</v>
+      </c>
+      <c r="J1" t="str">
+        <v>score_shape_summary</v>
+      </c>
+      <c r="K1" t="str">
+        <v>rank_1_phrase</v>
+      </c>
+      <c r="L1" t="str">
+        <v>rank_2_phrase</v>
+      </c>
+      <c r="M1" t="str">
+        <v>rank_3_phrase</v>
+      </c>
+      <c r="N1" t="str">
+        <v>rank_4_phrase</v>
+      </c>
+      <c r="O1" t="str">
+        <v>status</v>
+      </c>
+      <c r="P1" t="str">
+        <v>lookup_key</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:P1"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:P1"/>
+  </ignoredErrors>
+</worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="UTF-8" standalone="yes"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"><dimension ref="A1:L1"/><cols><col min="1" max="1" width="14.83203125" customWidth="1"/><col min="2" max="2" width="15.83203125" customWidth="1"/><col min="3" max="3" width="15.83203125" customWidth="1"/><col min="4" max="4" width="21.83203125" customWidth="1"/><col min="5" max="5" width="21.83203125" customWidth="1"/><col min="6" max="6" width="21.83203125" customWidth="1"/><col min="7" max="7" width="21.83203125" customWidth="1"/><col min="8" max="8" width="14.83203125" customWidth="1"/><col min="9" max="9" width="25.83203125" customWidth="1"/><col min="10" max="10" width="25.83203125" customWidth="1"/><col min="11" max="11" width="14.83203125" customWidth="1"/><col min="12" max="12" width="14.83203125" customWidth="1"/></cols><sheetData><row r="1"><c r="A1" s="1" s="1" t="str"><v>domain_key</v></c><c r="B1" s="1" s="1" t="str"><v>pattern_key</v></c><c r="C1" s="1" s="1" t="str"><v>score_shape</v></c><c r="D1" s="1" s="1" t="str"><v>rank_1_signal_key</v></c><c r="E1" s="1" s="1" t="str"><v>rank_2_signal_key</v></c><c r="F1" s="1" s="1" t="str"><v>rank_3_signal_key</v></c><c r="G1" s="1" s="1" t="str"><v>rank_4_signal_key</v></c><c r="H1" s="1" s="1" t="str"><v>headline</v></c><c r="I1" s="1" s="1" t="str"><v>recognition_statement</v></c><c r="J1" s="1" s="1" t="str"><v>recognition_expansion</v></c><c r="K1" s="1" s="1" t="str"><v>status</v></c><c r="L1" s="1" s="1" t="str"><v>lookup_key</v></c></row></sheetData><autoFilter ref="A1:L1"/><ignoredErrors><ignoredError numberStoredAsText="1" sqref="A1:L1"/></ignoredErrors></worksheet>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L1"/>
+  <cols>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="21.83203125" customWidth="1"/>
+    <col min="5" max="5" width="21.83203125" customWidth="1"/>
+    <col min="6" max="6" width="21.83203125" customWidth="1"/>
+    <col min="7" max="7" width="21.83203125" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" customWidth="1"/>
+    <col min="9" max="9" width="25.83203125" customWidth="1"/>
+    <col min="10" max="10" width="25.83203125" customWidth="1"/>
+    <col min="11" max="11" width="14.83203125" customWidth="1"/>
+    <col min="12" max="12" width="14.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>domain_key</v>
+      </c>
+      <c r="B1" t="str">
+        <v>pattern_key</v>
+      </c>
+      <c r="C1" t="str">
+        <v>score_shape</v>
+      </c>
+      <c r="D1" t="str">
+        <v>rank_1_signal_key</v>
+      </c>
+      <c r="E1" t="str">
+        <v>rank_2_signal_key</v>
+      </c>
+      <c r="F1" t="str">
+        <v>rank_3_signal_key</v>
+      </c>
+      <c r="G1" t="str">
+        <v>rank_4_signal_key</v>
+      </c>
+      <c r="H1" t="str">
+        <v>headline</v>
+      </c>
+      <c r="I1" t="str">
+        <v>recognition_statement</v>
+      </c>
+      <c r="J1" t="str">
+        <v>recognition_expansion</v>
+      </c>
+      <c r="K1" t="str">
+        <v>status</v>
+      </c>
+      <c r="L1" t="str">
+        <v>lookup_key</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:L1"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:L1"/>
+  </ignoredErrors>
+</worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="UTF-8" standalone="yes"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"><dimension ref="A1:L17"/><cols><col min="1" max="1" width="14.83203125" customWidth="1"/><col min="2" max="2" width="14.83203125" customWidth="1"/><col min="3" max="3" width="16.83203125" customWidth="1"/><col min="4" max="4" width="17.83203125" customWidth="1"/><col min="5" max="5" width="14.83203125" customWidth="1"/><col min="6" max="6" width="14.83203125" customWidth="1"/><col min="7" max="7" width="15.83203125" customWidth="1"/><col min="8" max="8" width="25.83203125" customWidth="1"/><col min="9" max="9" width="16.83203125" customWidth="1"/><col min="10" max="10" width="20.83203125" customWidth="1"/><col min="11" max="11" width="14.83203125" customWidth="1"/><col min="12" max="12" width="14.83203125" customWidth="1"/></cols><sheetData><row r="1"><c r="A1" s="1" s="1" t="str"><v>domain_key</v></c><c r="B1" s="1" s="1" t="str"><v>signal_key</v></c><c r="C1" s="1" s="1" t="str"><v>signal_label</v></c><c r="D1" s="1" s="1" t="str"><v>rank_position</v></c><c r="E1" s="1" s="1" t="str"><v>rank_role</v></c><c r="F1" s="1" s="1" t="str"><v>title</v></c><c r="G1" s="1" s="1" t="str"><v>description</v></c><c r="H1" s="1" s="1" t="str"><v>productive_expression</v></c><c r="I1" s="1" s="1" t="str"><v>risk_pattern</v></c><c r="J1" s="1" s="1" t="str"><v>development_note</v></c><c r="K1" s="1" s="1" t="str"><v>status</v></c><c r="L1" s="1" s="1" t="str"><v>lookup_key</v></c></row><row r="2"><c r="A2" t="str"><v>{{domain_key}}</v></c><c r="B2" t="str"><v>signal_a</v></c><c r="C2" t="str"><v>{{signal_a_label}}</v></c><c r="D2"><v>1</v></c><c r="E2" t="str"><v>rank_1</v></c><c r="F2" t="str"><v>{{signal_a_rank_1_title}}</v></c><c r="G2" t="str"><v>{{signal_a_rank_1_description}}</v></c><c r="H2" t="str"><v>{{signal_a_rank_1_productive_expression}}</v></c><c r="I2" t="str"><v>{{signal_a_rank_1_risk_pattern}}</v></c><c r="J2" t="str"><v>{{signal_a_rank_1_development_note}}</v></c><c r="K2" t="str"><v>active</v></c><c r="L2" t="str"><v>signal_role::signal_a::1</v></c></row><row r="3"><c r="A3" t="str"><v>{{domain_key}}</v></c><c r="B3" t="str"><v>signal_a</v></c><c r="C3" t="str"><v>{{signal_a_label}}</v></c><c r="D3"><v>2</v></c><c r="E3" t="str"><v>rank_2</v></c><c r="F3" t="str"><v>{{signal_a_rank_2_title}}</v></c><c r="G3" t="str"><v>{{signal_a_rank_2_description}}</v></c><c r="H3" t="str"><v>{{signal_a_rank_2_productive_expression}}</v></c><c r="I3" t="str"><v>{{signal_a_rank_2_risk_pattern}}</v></c><c r="J3" t="str"><v>{{signal_a_rank_2_development_note}}</v></c><c r="K3" t="str"><v>active</v></c><c r="L3" t="str"><v>signal_role::signal_a::2</v></c></row><row r="4"><c r="A4" t="str"><v>{{domain_key}}</v></c><c r="B4" t="str"><v>signal_a</v></c><c r="C4" t="str"><v>{{signal_a_label}}</v></c><c r="D4"><v>3</v></c><c r="E4" t="str"><v>rank_3</v></c><c r="F4" t="str"><v>{{signal_a_rank_3_title}}</v></c><c r="G4" t="str"><v>{{signal_a_rank_3_description}}</v></c><c r="H4" t="str"><v>{{signal_a_rank_3_productive_expression}}</v></c><c r="I4" t="str"><v>{{signal_a_rank_3_risk_pattern}}</v></c><c r="J4" t="str"><v>{{signal_a_rank_3_development_note}}</v></c><c r="K4" t="str"><v>active</v></c><c r="L4" t="str"><v>signal_role::signal_a::3</v></c></row><row r="5"><c r="A5" t="str"><v>{{domain_key}}</v></c><c r="B5" t="str"><v>signal_a</v></c><c r="C5" t="str"><v>{{signal_a_label}}</v></c><c r="D5"><v>4</v></c><c r="E5" t="str"><v>rank_4</v></c><c r="F5" t="str"><v>{{signal_a_rank_4_title}}</v></c><c r="G5" t="str"><v>{{signal_a_rank_4_description}}</v></c><c r="H5" t="str"><v>{{signal_a_rank_4_productive_expression}}</v></c><c r="I5" t="str"><v>{{signal_a_rank_4_risk_pattern}}</v></c><c r="J5" t="str"><v>{{signal_a_rank_4_development_note}}</v></c><c r="K5" t="str"><v>active</v></c><c r="L5" t="str"><v>signal_role::signal_a::4</v></c></row><row r="6"><c r="A6" t="str"><v>{{domain_key}}</v></c><c r="B6" t="str"><v>signal_b</v></c><c r="C6" t="str"><v>{{signal_b_label}}</v></c><c r="D6"><v>1</v></c><c r="E6" t="str"><v>rank_1</v></c><c r="F6" t="str"><v>{{signal_b_rank_1_title}}</v></c><c r="G6" t="str"><v>{{signal_b_rank_1_description}}</v></c><c r="H6" t="str"><v>{{signal_b_rank_1_productive_expression}}</v></c><c r="I6" t="str"><v>{{signal_b_rank_1_risk_pattern}}</v></c><c r="J6" t="str"><v>{{signal_b_rank_1_development_note}}</v></c><c r="K6" t="str"><v>active</v></c><c r="L6" t="str"><v>signal_role::signal_b::1</v></c></row><row r="7"><c r="A7" t="str"><v>{{domain_key}}</v></c><c r="B7" t="str"><v>signal_b</v></c><c r="C7" t="str"><v>{{signal_b_label}}</v></c><c r="D7"><v>2</v></c><c r="E7" t="str"><v>rank_2</v></c><c r="F7" t="str"><v>{{signal_b_rank_2_title}}</v></c><c r="G7" t="str"><v>{{signal_b_rank_2_description}}</v></c><c r="H7" t="str"><v>{{signal_b_rank_2_productive_expression}}</v></c><c r="I7" t="str"><v>{{signal_b_rank_2_risk_pattern}}</v></c><c r="J7" t="str"><v>{{signal_b_rank_2_development_note}}</v></c><c r="K7" t="str"><v>active</v></c><c r="L7" t="str"><v>signal_role::signal_b::2</v></c></row><row r="8"><c r="A8" t="str"><v>{{domain_key}}</v></c><c r="B8" t="str"><v>signal_b</v></c><c r="C8" t="str"><v>{{signal_b_label}}</v></c><c r="D8"><v>3</v></c><c r="E8" t="str"><v>rank_3</v></c><c r="F8" t="str"><v>{{signal_b_rank_3_title}}</v></c><c r="G8" t="str"><v>{{signal_b_rank_3_description}}</v></c><c r="H8" t="str"><v>{{signal_b_rank_3_productive_expression}}</v></c><c r="I8" t="str"><v>{{signal_b_rank_3_risk_pattern}}</v></c><c r="J8" t="str"><v>{{signal_b_rank_3_development_note}}</v></c><c r="K8" t="str"><v>active</v></c><c r="L8" t="str"><v>signal_role::signal_b::3</v></c></row><row r="9"><c r="A9" t="str"><v>{{domain_key}}</v></c><c r="B9" t="str"><v>signal_b</v></c><c r="C9" t="str"><v>{{signal_b_label}}</v></c><c r="D9"><v>4</v></c><c r="E9" t="str"><v>rank_4</v></c><c r="F9" t="str"><v>{{signal_b_rank_4_title}}</v></c><c r="G9" t="str"><v>{{signal_b_rank_4_description}}</v></c><c r="H9" t="str"><v>{{signal_b_rank_4_productive_expression}}</v></c><c r="I9" t="str"><v>{{signal_b_rank_4_risk_pattern}}</v></c><c r="J9" t="str"><v>{{signal_b_rank_4_development_note}}</v></c><c r="K9" t="str"><v>active</v></c><c r="L9" t="str"><v>signal_role::signal_b::4</v></c></row><row r="10"><c r="A10" t="str"><v>{{domain_key}}</v></c><c r="B10" t="str"><v>signal_c</v></c><c r="C10" t="str"><v>{{signal_c_label}}</v></c><c r="D10"><v>1</v></c><c r="E10" t="str"><v>rank_1</v></c><c r="F10" t="str"><v>{{signal_c_rank_1_title}}</v></c><c r="G10" t="str"><v>{{signal_c_rank_1_description}}</v></c><c r="H10" t="str"><v>{{signal_c_rank_1_productive_expression}}</v></c><c r="I10" t="str"><v>{{signal_c_rank_1_risk_pattern}}</v></c><c r="J10" t="str"><v>{{signal_c_rank_1_development_note}}</v></c><c r="K10" t="str"><v>active</v></c><c r="L10" t="str"><v>signal_role::signal_c::1</v></c></row><row r="11"><c r="A11" t="str"><v>{{domain_key}}</v></c><c r="B11" t="str"><v>signal_c</v></c><c r="C11" t="str"><v>{{signal_c_label}}</v></c><c r="D11"><v>2</v></c><c r="E11" t="str"><v>rank_2</v></c><c r="F11" t="str"><v>{{signal_c_rank_2_title}}</v></c><c r="G11" t="str"><v>{{signal_c_rank_2_description}}</v></c><c r="H11" t="str"><v>{{signal_c_rank_2_productive_expression}}</v></c><c r="I11" t="str"><v>{{signal_c_rank_2_risk_pattern}}</v></c><c r="J11" t="str"><v>{{signal_c_rank_2_development_note}}</v></c><c r="K11" t="str"><v>active</v></c><c r="L11" t="str"><v>signal_role::signal_c::2</v></c></row><row r="12"><c r="A12" t="str"><v>{{domain_key}}</v></c><c r="B12" t="str"><v>signal_c</v></c><c r="C12" t="str"><v>{{signal_c_label}}</v></c><c r="D12"><v>3</v></c><c r="E12" t="str"><v>rank_3</v></c><c r="F12" t="str"><v>{{signal_c_rank_3_title}}</v></c><c r="G12" t="str"><v>{{signal_c_rank_3_description}}</v></c><c r="H12" t="str"><v>{{signal_c_rank_3_productive_expression}}</v></c><c r="I12" t="str"><v>{{signal_c_rank_3_risk_pattern}}</v></c><c r="J12" t="str"><v>{{signal_c_rank_3_development_note}}</v></c><c r="K12" t="str"><v>active</v></c><c r="L12" t="str"><v>signal_role::signal_c::3</v></c></row><row r="13"><c r="A13" t="str"><v>{{domain_key}}</v></c><c r="B13" t="str"><v>signal_c</v></c><c r="C13" t="str"><v>{{signal_c_label}}</v></c><c r="D13"><v>4</v></c><c r="E13" t="str"><v>rank_4</v></c><c r="F13" t="str"><v>{{signal_c_rank_4_title}}</v></c><c r="G13" t="str"><v>{{signal_c_rank_4_description}}</v></c><c r="H13" t="str"><v>{{signal_c_rank_4_productive_expression}}</v></c><c r="I13" t="str"><v>{{signal_c_rank_4_risk_pattern}}</v></c><c r="J13" t="str"><v>{{signal_c_rank_4_development_note}}</v></c><c r="K13" t="str"><v>active</v></c><c r="L13" t="str"><v>signal_role::signal_c::4</v></c></row><row r="14"><c r="A14" t="str"><v>{{domain_key}}</v></c><c r="B14" t="str"><v>signal_d</v></c><c r="C14" t="str"><v>{{signal_d_label}}</v></c><c r="D14"><v>1</v></c><c r="E14" t="str"><v>rank_1</v></c><c r="F14" t="str"><v>{{signal_d_rank_1_title}}</v></c><c r="G14" t="str"><v>{{signal_d_rank_1_description}}</v></c><c r="H14" t="str"><v>{{signal_d_rank_1_productive_expression}}</v></c><c r="I14" t="str"><v>{{signal_d_rank_1_risk_pattern}}</v></c><c r="J14" t="str"><v>{{signal_d_rank_1_development_note}}</v></c><c r="K14" t="str"><v>active</v></c><c r="L14" t="str"><v>signal_role::signal_d::1</v></c></row><row r="15"><c r="A15" t="str"><v>{{domain_key}}</v></c><c r="B15" t="str"><v>signal_d</v></c><c r="C15" t="str"><v>{{signal_d_label}}</v></c><c r="D15"><v>2</v></c><c r="E15" t="str"><v>rank_2</v></c><c r="F15" t="str"><v>{{signal_d_rank_2_title}}</v></c><c r="G15" t="str"><v>{{signal_d_rank_2_description}}</v></c><c r="H15" t="str"><v>{{signal_d_rank_2_productive_expression}}</v></c><c r="I15" t="str"><v>{{signal_d_rank_2_risk_pattern}}</v></c><c r="J15" t="str"><v>{{signal_d_rank_2_development_note}}</v></c><c r="K15" t="str"><v>active</v></c><c r="L15" t="str"><v>signal_role::signal_d::2</v></c></row><row r="16"><c r="A16" t="str"><v>{{domain_key}}</v></c><c r="B16" t="str"><v>signal_d</v></c><c r="C16" t="str"><v>{{signal_d_label}}</v></c><c r="D16"><v>3</v></c><c r="E16" t="str"><v>rank_3</v></c><c r="F16" t="str"><v>{{signal_d_rank_3_title}}</v></c><c r="G16" t="str"><v>{{signal_d_rank_3_description}}</v></c><c r="H16" t="str"><v>{{signal_d_rank_3_productive_expression}}</v></c><c r="I16" t="str"><v>{{signal_d_rank_3_risk_pattern}}</v></c><c r="J16" t="str"><v>{{signal_d_rank_3_development_note}}</v></c><c r="K16" t="str"><v>active</v></c><c r="L16" t="str"><v>signal_role::signal_d::3</v></c></row><row r="17"><c r="A17" t="str"><v>{{domain_key}}</v></c><c r="B17" t="str"><v>signal_d</v></c><c r="C17" t="str"><v>{{signal_d_label}}</v></c><c r="D17"><v>4</v></c><c r="E17" t="str"><v>rank_4</v></c><c r="F17" t="str"><v>{{signal_d_rank_4_title}}</v></c><c r="G17" t="str"><v>{{signal_d_rank_4_description}}</v></c><c r="H17" t="str"><v>{{signal_d_rank_4_productive_expression}}</v></c><c r="I17" t="str"><v>{{signal_d_rank_4_risk_pattern}}</v></c><c r="J17" t="str"><v>{{signal_d_rank_4_development_note}}</v></c><c r="K17" t="str"><v>active</v></c><c r="L17" t="str"><v>signal_role::signal_d::4</v></c></row></sheetData><autoFilter ref="A1:L17"/><ignoredErrors><ignoredError numberStoredAsText="1" sqref="A1:L17"/></ignoredErrors></worksheet>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L17"/>
+  <cols>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" customWidth="1"/>
+    <col min="4" max="4" width="17.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" customWidth="1"/>
+    <col min="8" max="8" width="25.83203125" customWidth="1"/>
+    <col min="9" max="9" width="16.83203125" customWidth="1"/>
+    <col min="10" max="10" width="20.83203125" customWidth="1"/>
+    <col min="11" max="11" width="14.83203125" customWidth="1"/>
+    <col min="12" max="12" width="14.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>domain_key</v>
+      </c>
+      <c r="B1" t="str">
+        <v>signal_key</v>
+      </c>
+      <c r="C1" t="str">
+        <v>signal_label</v>
+      </c>
+      <c r="D1" t="str">
+        <v>rank_position</v>
+      </c>
+      <c r="E1" t="str">
+        <v>rank_role</v>
+      </c>
+      <c r="F1" t="str">
+        <v>title</v>
+      </c>
+      <c r="G1" t="str">
+        <v>description</v>
+      </c>
+      <c r="H1" t="str">
+        <v>productive_expression</v>
+      </c>
+      <c r="I1" t="str">
+        <v>risk_pattern</v>
+      </c>
+      <c r="J1" t="str">
+        <v>development_note</v>
+      </c>
+      <c r="K1" t="str">
+        <v>status</v>
+      </c>
+      <c r="L1" t="str">
+        <v>lookup_key</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="B2" t="str">
+        <v>signal_a</v>
+      </c>
+      <c r="C2" t="str">
+        <v>{{signal_a_label}}</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="str">
+        <v>rank_1</v>
+      </c>
+      <c r="F2" t="str">
+        <v>{{signal_a_rank_1_title}}</v>
+      </c>
+      <c r="G2" t="str">
+        <v>{{signal_a_rank_1_description}}</v>
+      </c>
+      <c r="H2" t="str">
+        <v>{{signal_a_rank_1_productive_expression}}</v>
+      </c>
+      <c r="I2" t="str">
+        <v>{{signal_a_rank_1_risk_pattern}}</v>
+      </c>
+      <c r="J2" t="str">
+        <v>{{signal_a_rank_1_development_note}}</v>
+      </c>
+      <c r="K2" t="str">
+        <v>active</v>
+      </c>
+      <c r="L2" t="str">
+        <v>signal_role::signal_a::1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="B3" t="str">
+        <v>signal_a</v>
+      </c>
+      <c r="C3" t="str">
+        <v>{{signal_a_label}}</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3" t="str">
+        <v>rank_2</v>
+      </c>
+      <c r="F3" t="str">
+        <v>{{signal_a_rank_2_title}}</v>
+      </c>
+      <c r="G3" t="str">
+        <v>{{signal_a_rank_2_description}}</v>
+      </c>
+      <c r="H3" t="str">
+        <v>{{signal_a_rank_2_productive_expression}}</v>
+      </c>
+      <c r="I3" t="str">
+        <v>{{signal_a_rank_2_risk_pattern}}</v>
+      </c>
+      <c r="J3" t="str">
+        <v>{{signal_a_rank_2_development_note}}</v>
+      </c>
+      <c r="K3" t="str">
+        <v>active</v>
+      </c>
+      <c r="L3" t="str">
+        <v>signal_role::signal_a::2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="B4" t="str">
+        <v>signal_a</v>
+      </c>
+      <c r="C4" t="str">
+        <v>{{signal_a_label}}</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4" t="str">
+        <v>rank_3</v>
+      </c>
+      <c r="F4" t="str">
+        <v>{{signal_a_rank_3_title}}</v>
+      </c>
+      <c r="G4" t="str">
+        <v>{{signal_a_rank_3_description}}</v>
+      </c>
+      <c r="H4" t="str">
+        <v>{{signal_a_rank_3_productive_expression}}</v>
+      </c>
+      <c r="I4" t="str">
+        <v>{{signal_a_rank_3_risk_pattern}}</v>
+      </c>
+      <c r="J4" t="str">
+        <v>{{signal_a_rank_3_development_note}}</v>
+      </c>
+      <c r="K4" t="str">
+        <v>active</v>
+      </c>
+      <c r="L4" t="str">
+        <v>signal_role::signal_a::3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="B5" t="str">
+        <v>signal_a</v>
+      </c>
+      <c r="C5" t="str">
+        <v>{{signal_a_label}}</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5" t="str">
+        <v>rank_4</v>
+      </c>
+      <c r="F5" t="str">
+        <v>{{signal_a_rank_4_title}}</v>
+      </c>
+      <c r="G5" t="str">
+        <v>{{signal_a_rank_4_description}}</v>
+      </c>
+      <c r="H5" t="str">
+        <v>{{signal_a_rank_4_productive_expression}}</v>
+      </c>
+      <c r="I5" t="str">
+        <v>{{signal_a_rank_4_risk_pattern}}</v>
+      </c>
+      <c r="J5" t="str">
+        <v>{{signal_a_rank_4_development_note}}</v>
+      </c>
+      <c r="K5" t="str">
+        <v>active</v>
+      </c>
+      <c r="L5" t="str">
+        <v>signal_role::signal_a::4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="B6" t="str">
+        <v>signal_b</v>
+      </c>
+      <c r="C6" t="str">
+        <v>{{signal_b_label}}</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="str">
+        <v>rank_1</v>
+      </c>
+      <c r="F6" t="str">
+        <v>{{signal_b_rank_1_title}}</v>
+      </c>
+      <c r="G6" t="str">
+        <v>{{signal_b_rank_1_description}}</v>
+      </c>
+      <c r="H6" t="str">
+        <v>{{signal_b_rank_1_productive_expression}}</v>
+      </c>
+      <c r="I6" t="str">
+        <v>{{signal_b_rank_1_risk_pattern}}</v>
+      </c>
+      <c r="J6" t="str">
+        <v>{{signal_b_rank_1_development_note}}</v>
+      </c>
+      <c r="K6" t="str">
+        <v>active</v>
+      </c>
+      <c r="L6" t="str">
+        <v>signal_role::signal_b::1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="B7" t="str">
+        <v>signal_b</v>
+      </c>
+      <c r="C7" t="str">
+        <v>{{signal_b_label}}</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7" t="str">
+        <v>rank_2</v>
+      </c>
+      <c r="F7" t="str">
+        <v>{{signal_b_rank_2_title}}</v>
+      </c>
+      <c r="G7" t="str">
+        <v>{{signal_b_rank_2_description}}</v>
+      </c>
+      <c r="H7" t="str">
+        <v>{{signal_b_rank_2_productive_expression}}</v>
+      </c>
+      <c r="I7" t="str">
+        <v>{{signal_b_rank_2_risk_pattern}}</v>
+      </c>
+      <c r="J7" t="str">
+        <v>{{signal_b_rank_2_development_note}}</v>
+      </c>
+      <c r="K7" t="str">
+        <v>active</v>
+      </c>
+      <c r="L7" t="str">
+        <v>signal_role::signal_b::2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="B8" t="str">
+        <v>signal_b</v>
+      </c>
+      <c r="C8" t="str">
+        <v>{{signal_b_label}}</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8" t="str">
+        <v>rank_3</v>
+      </c>
+      <c r="F8" t="str">
+        <v>{{signal_b_rank_3_title}}</v>
+      </c>
+      <c r="G8" t="str">
+        <v>{{signal_b_rank_3_description}}</v>
+      </c>
+      <c r="H8" t="str">
+        <v>{{signal_b_rank_3_productive_expression}}</v>
+      </c>
+      <c r="I8" t="str">
+        <v>{{signal_b_rank_3_risk_pattern}}</v>
+      </c>
+      <c r="J8" t="str">
+        <v>{{signal_b_rank_3_development_note}}</v>
+      </c>
+      <c r="K8" t="str">
+        <v>active</v>
+      </c>
+      <c r="L8" t="str">
+        <v>signal_role::signal_b::3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="B9" t="str">
+        <v>signal_b</v>
+      </c>
+      <c r="C9" t="str">
+        <v>{{signal_b_label}}</v>
+      </c>
+      <c r="D9">
+        <v>4</v>
+      </c>
+      <c r="E9" t="str">
+        <v>rank_4</v>
+      </c>
+      <c r="F9" t="str">
+        <v>{{signal_b_rank_4_title}}</v>
+      </c>
+      <c r="G9" t="str">
+        <v>{{signal_b_rank_4_description}}</v>
+      </c>
+      <c r="H9" t="str">
+        <v>{{signal_b_rank_4_productive_expression}}</v>
+      </c>
+      <c r="I9" t="str">
+        <v>{{signal_b_rank_4_risk_pattern}}</v>
+      </c>
+      <c r="J9" t="str">
+        <v>{{signal_b_rank_4_development_note}}</v>
+      </c>
+      <c r="K9" t="str">
+        <v>active</v>
+      </c>
+      <c r="L9" t="str">
+        <v>signal_role::signal_b::4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="B10" t="str">
+        <v>signal_c</v>
+      </c>
+      <c r="C10" t="str">
+        <v>{{signal_c_label}}</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10" t="str">
+        <v>rank_1</v>
+      </c>
+      <c r="F10" t="str">
+        <v>{{signal_c_rank_1_title}}</v>
+      </c>
+      <c r="G10" t="str">
+        <v>{{signal_c_rank_1_description}}</v>
+      </c>
+      <c r="H10" t="str">
+        <v>{{signal_c_rank_1_productive_expression}}</v>
+      </c>
+      <c r="I10" t="str">
+        <v>{{signal_c_rank_1_risk_pattern}}</v>
+      </c>
+      <c r="J10" t="str">
+        <v>{{signal_c_rank_1_development_note}}</v>
+      </c>
+      <c r="K10" t="str">
+        <v>active</v>
+      </c>
+      <c r="L10" t="str">
+        <v>signal_role::signal_c::1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="B11" t="str">
+        <v>signal_c</v>
+      </c>
+      <c r="C11" t="str">
+        <v>{{signal_c_label}}</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11" t="str">
+        <v>rank_2</v>
+      </c>
+      <c r="F11" t="str">
+        <v>{{signal_c_rank_2_title}}</v>
+      </c>
+      <c r="G11" t="str">
+        <v>{{signal_c_rank_2_description}}</v>
+      </c>
+      <c r="H11" t="str">
+        <v>{{signal_c_rank_2_productive_expression}}</v>
+      </c>
+      <c r="I11" t="str">
+        <v>{{signal_c_rank_2_risk_pattern}}</v>
+      </c>
+      <c r="J11" t="str">
+        <v>{{signal_c_rank_2_development_note}}</v>
+      </c>
+      <c r="K11" t="str">
+        <v>active</v>
+      </c>
+      <c r="L11" t="str">
+        <v>signal_role::signal_c::2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="B12" t="str">
+        <v>signal_c</v>
+      </c>
+      <c r="C12" t="str">
+        <v>{{signal_c_label}}</v>
+      </c>
+      <c r="D12">
+        <v>3</v>
+      </c>
+      <c r="E12" t="str">
+        <v>rank_3</v>
+      </c>
+      <c r="F12" t="str">
+        <v>{{signal_c_rank_3_title}}</v>
+      </c>
+      <c r="G12" t="str">
+        <v>{{signal_c_rank_3_description}}</v>
+      </c>
+      <c r="H12" t="str">
+        <v>{{signal_c_rank_3_productive_expression}}</v>
+      </c>
+      <c r="I12" t="str">
+        <v>{{signal_c_rank_3_risk_pattern}}</v>
+      </c>
+      <c r="J12" t="str">
+        <v>{{signal_c_rank_3_development_note}}</v>
+      </c>
+      <c r="K12" t="str">
+        <v>active</v>
+      </c>
+      <c r="L12" t="str">
+        <v>signal_role::signal_c::3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="B13" t="str">
+        <v>signal_c</v>
+      </c>
+      <c r="C13" t="str">
+        <v>{{signal_c_label}}</v>
+      </c>
+      <c r="D13">
+        <v>4</v>
+      </c>
+      <c r="E13" t="str">
+        <v>rank_4</v>
+      </c>
+      <c r="F13" t="str">
+        <v>{{signal_c_rank_4_title}}</v>
+      </c>
+      <c r="G13" t="str">
+        <v>{{signal_c_rank_4_description}}</v>
+      </c>
+      <c r="H13" t="str">
+        <v>{{signal_c_rank_4_productive_expression}}</v>
+      </c>
+      <c r="I13" t="str">
+        <v>{{signal_c_rank_4_risk_pattern}}</v>
+      </c>
+      <c r="J13" t="str">
+        <v>{{signal_c_rank_4_development_note}}</v>
+      </c>
+      <c r="K13" t="str">
+        <v>active</v>
+      </c>
+      <c r="L13" t="str">
+        <v>signal_role::signal_c::4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="B14" t="str">
+        <v>signal_d</v>
+      </c>
+      <c r="C14" t="str">
+        <v>{{signal_d_label}}</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14" t="str">
+        <v>rank_1</v>
+      </c>
+      <c r="F14" t="str">
+        <v>{{signal_d_rank_1_title}}</v>
+      </c>
+      <c r="G14" t="str">
+        <v>{{signal_d_rank_1_description}}</v>
+      </c>
+      <c r="H14" t="str">
+        <v>{{signal_d_rank_1_productive_expression}}</v>
+      </c>
+      <c r="I14" t="str">
+        <v>{{signal_d_rank_1_risk_pattern}}</v>
+      </c>
+      <c r="J14" t="str">
+        <v>{{signal_d_rank_1_development_note}}</v>
+      </c>
+      <c r="K14" t="str">
+        <v>active</v>
+      </c>
+      <c r="L14" t="str">
+        <v>signal_role::signal_d::1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="B15" t="str">
+        <v>signal_d</v>
+      </c>
+      <c r="C15" t="str">
+        <v>{{signal_d_label}}</v>
+      </c>
+      <c r="D15">
+        <v>2</v>
+      </c>
+      <c r="E15" t="str">
+        <v>rank_2</v>
+      </c>
+      <c r="F15" t="str">
+        <v>{{signal_d_rank_2_title}}</v>
+      </c>
+      <c r="G15" t="str">
+        <v>{{signal_d_rank_2_description}}</v>
+      </c>
+      <c r="H15" t="str">
+        <v>{{signal_d_rank_2_productive_expression}}</v>
+      </c>
+      <c r="I15" t="str">
+        <v>{{signal_d_rank_2_risk_pattern}}</v>
+      </c>
+      <c r="J15" t="str">
+        <v>{{signal_d_rank_2_development_note}}</v>
+      </c>
+      <c r="K15" t="str">
+        <v>active</v>
+      </c>
+      <c r="L15" t="str">
+        <v>signal_role::signal_d::2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="B16" t="str">
+        <v>signal_d</v>
+      </c>
+      <c r="C16" t="str">
+        <v>{{signal_d_label}}</v>
+      </c>
+      <c r="D16">
+        <v>3</v>
+      </c>
+      <c r="E16" t="str">
+        <v>rank_3</v>
+      </c>
+      <c r="F16" t="str">
+        <v>{{signal_d_rank_3_title}}</v>
+      </c>
+      <c r="G16" t="str">
+        <v>{{signal_d_rank_3_description}}</v>
+      </c>
+      <c r="H16" t="str">
+        <v>{{signal_d_rank_3_productive_expression}}</v>
+      </c>
+      <c r="I16" t="str">
+        <v>{{signal_d_rank_3_risk_pattern}}</v>
+      </c>
+      <c r="J16" t="str">
+        <v>{{signal_d_rank_3_development_note}}</v>
+      </c>
+      <c r="K16" t="str">
+        <v>active</v>
+      </c>
+      <c r="L16" t="str">
+        <v>signal_role::signal_d::3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>{{domain_key}}</v>
+      </c>
+      <c r="B17" t="str">
+        <v>signal_d</v>
+      </c>
+      <c r="C17" t="str">
+        <v>{{signal_d_label}}</v>
+      </c>
+      <c r="D17">
+        <v>4</v>
+      </c>
+      <c r="E17" t="str">
+        <v>rank_4</v>
+      </c>
+      <c r="F17" t="str">
+        <v>{{signal_d_rank_4_title}}</v>
+      </c>
+      <c r="G17" t="str">
+        <v>{{signal_d_rank_4_description}}</v>
+      </c>
+      <c r="H17" t="str">
+        <v>{{signal_d_rank_4_productive_expression}}</v>
+      </c>
+      <c r="I17" t="str">
+        <v>{{signal_d_rank_4_risk_pattern}}</v>
+      </c>
+      <c r="J17" t="str">
+        <v>{{signal_d_rank_4_development_note}}</v>
+      </c>
+      <c r="K17" t="str">
+        <v>active</v>
+      </c>
+      <c r="L17" t="str">
+        <v>signal_role::signal_d::4</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:L17"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:L17"/>
+  </ignoredErrors>
+</worksheet>
 </file>